--- a/Excel/4_1_ManureManagement_Feedlot_WIP_v03.xlsx
+++ b/Excel/4_1_ManureManagement_Feedlot_WIP_v03.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F680E60-9DDF-469B-876B-29017869FE59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{989364AF-C5F1-48CF-B6A3-8C9680A50B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="615" yWindow="240" windowWidth="37755" windowHeight="20445" activeTab="7" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="630" yWindow="210" windowWidth="37755" windowHeight="20445" activeTab="4" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -457,7 +457,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="851" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="852" uniqueCount="344">
   <si>
     <t>Home</t>
   </si>
@@ -850,9 +850,6 @@
     <t>kg DM/head/day</t>
   </si>
   <si>
-    <t>No MMS</t>
-  </si>
-  <si>
     <t>MMS m</t>
   </si>
   <si>
@@ -995,12 +992,6 @@
   </si>
   <si>
     <t>2020-2023 Converted to fraction</t>
-  </si>
-  <si>
-    <t>Method 1 default values</t>
-  </si>
-  <si>
-    <t>Method 2 custom values</t>
   </si>
   <si>
     <t>Characteristic</t>
@@ -1714,6 +1705,15 @@
   </si>
   <si>
     <t>4.1 Manure management: Beef Feedlot: Results</t>
+  </si>
+  <si>
+    <t>Method 1 default values (Do not edit)</t>
+  </si>
+  <si>
+    <t>Method 2 custom values (Edit if known)</t>
+  </si>
+  <si>
+    <t>Applied to farm soils as fertiliser</t>
   </si>
 </sst>
 </file>
@@ -3134,32 +3134,6 @@
   <dxfs count="57">
     <dxf>
       <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFB2D498"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -3565,6 +3539,32 @@
           <bgColor indexed="65"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFB2D498"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -10666,34 +10666,34 @@
     <tableColumn id="1" xr3:uid="{3885FE93-299E-44EB-B503-99C305BD6F41}" name="Treatment stage T">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{D0E12F95-AC29-47D0-913A-0A0B02931616}" name="MMS m" dataDxfId="27" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{D0E12F95-AC29-47D0-913A-0A0B02931616}" name="MMS m" dataDxfId="44" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{E17BE7AB-8FAD-4B5C-9F86-E70E6A00B9B1}" name="NSW" dataDxfId="26" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{E17BE7AB-8FAD-4B5C-9F86-E70E6A00B9B1}" name="NSW" dataDxfId="43" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{D4C6F922-2719-4479-B7CC-26C5286F73ED}" name="ACT" dataDxfId="25" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{D4C6F922-2719-4479-B7CC-26C5286F73ED}" name="ACT" dataDxfId="42" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{5034DCA1-F046-43BC-A94F-832832E6D634}" name="QLD" dataDxfId="24" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{5034DCA1-F046-43BC-A94F-832832E6D634}" name="QLD" dataDxfId="41" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{186521AB-DFC2-4E3B-A674-A5382DCC5ACD}" name="NT" dataDxfId="23" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{186521AB-DFC2-4E3B-A674-A5382DCC5ACD}" name="NT" dataDxfId="40" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{95F9E197-F85F-424A-B68D-774604116729}" name="SA" dataDxfId="22" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{95F9E197-F85F-424A-B68D-774604116729}" name="SA" dataDxfId="39" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{A6DDF652-660B-4C41-982D-FECC3B1142AF}" name="VIC" dataDxfId="21" dataCellStyle="Content normal">
+    <tableColumn id="8" xr3:uid="{A6DDF652-660B-4C41-982D-FECC3B1142AF}" name="VIC" dataDxfId="38" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{5163E1D2-D984-4DBA-95A9-1667F628B2D9}" name="WA" dataDxfId="20" dataCellStyle="Content normal">
+    <tableColumn id="9" xr3:uid="{5163E1D2-D984-4DBA-95A9-1667F628B2D9}" name="WA" dataDxfId="37" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{A0E67108-978C-4849-A310-69F8E4739C6D}" name="TAS" dataDxfId="19" dataCellStyle="Content normal">
+    <tableColumn id="10" xr3:uid="{A0E67108-978C-4849-A310-69F8E4739C6D}" name="TAS" dataDxfId="36" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{27E929DD-0554-43B8-A58C-34B0A39F2EBA}" name="NIR definition" dataDxfId="18" dataCellStyle="Content normal">
+    <tableColumn id="11" xr3:uid="{27E929DD-0554-43B8-A58C-34B0A39F2EBA}" name="NIR definition" dataDxfId="35" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -10809,49 +10809,49 @@
     <tableColumn id="1" xr3:uid="{29672771-6091-4FA5-86EA-395E240FF5D2}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{7E0CB869-00AE-4755-8478-34C0A24DACCC}" name="MAT" totalsRowDxfId="44" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{7E0CB869-00AE-4755-8478-34C0A24DACCC}" name="MAT" totalsRowDxfId="16" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{EEBB7F36-38AB-43CA-89EE-CBF9D2B12C70}" name="MAP" totalsRowDxfId="43" totalsRowCellStyle="Content bold">
+    <tableColumn id="3" xr3:uid="{EEBB7F36-38AB-43CA-89EE-CBF9D2B12C70}" name="MAP" totalsRowDxfId="15" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{3010F3BA-675E-4D83-9AAD-FBE9EC6F9CF0}" name="Frost days per year" totalsRowDxfId="42" totalsRowCellStyle="Content bold">
+    <tableColumn id="4" xr3:uid="{3010F3BA-675E-4D83-9AAD-FBE9EC6F9CF0}" name="Frost days per year" totalsRowDxfId="14" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{3F1B2FE9-64D5-41E9-9332-E943400478C4}" name="Elevation" totalsRowDxfId="41" totalsRowCellStyle="Content bold">
+    <tableColumn id="5" xr3:uid="{3F1B2FE9-64D5-41E9-9332-E943400478C4}" name="Elevation" totalsRowDxfId="13" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{C4BB9839-93FF-42DA-A517-F34E10C70484}" name="MAP:PET" totalsRowDxfId="40" totalsRowCellStyle="Content bold">
+    <tableColumn id="6" xr3:uid="{C4BB9839-93FF-42DA-A517-F34E10C70484}" name="MAP:PET" totalsRowDxfId="12" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{A01F6B36-D801-484C-A91E-3EFD0F4A77C0}" name="Min temp" totalsRowDxfId="39" totalsRowCellStyle="Content bold">
+    <tableColumn id="7" xr3:uid="{A01F6B36-D801-484C-A91E-3EFD0F4A77C0}" name="Min temp" totalsRowDxfId="11" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{033C9484-1852-4D2B-88A9-02D24D40BB22}" name="Max temp" totalsRowDxfId="38" totalsRowCellStyle="Content bold">
+    <tableColumn id="8" xr3:uid="{033C9484-1852-4D2B-88A9-02D24D40BB22}" name="Max temp" totalsRowDxfId="10" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{C54AFCDF-470B-41E8-8CB5-A1938A000F27}" name="Min rainfall" totalsRowDxfId="37" totalsRowCellStyle="Content bold">
+    <tableColumn id="9" xr3:uid="{C54AFCDF-470B-41E8-8CB5-A1938A000F27}" name="Min rainfall" totalsRowDxfId="9" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{E235B24A-0205-4131-BBC7-FD5B69336BB5}" name="Max rainfall" totalsRowDxfId="36" totalsRowCellStyle="Content bold">
+    <tableColumn id="10" xr3:uid="{E235B24A-0205-4131-BBC7-FD5B69336BB5}" name="Max rainfall" totalsRowDxfId="8" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{2236A619-E104-4738-8E09-41B8930DF78A}" name="Min frost days" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
+    <tableColumn id="11" xr3:uid="{2236A619-E104-4738-8E09-41B8930DF78A}" name="Min frost days" totalsRowDxfId="7" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{85D18FF3-E59D-404A-A2E0-032D9A5E0B84}" name="Max frost days" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
+    <tableColumn id="15" xr3:uid="{85D18FF3-E59D-404A-A2E0-032D9A5E0B84}" name="Max frost days" totalsRowDxfId="6" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{82A7ECE5-EF70-4355-AA39-B204B086F753}" name="Min elevation" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
+    <tableColumn id="12" xr3:uid="{82A7ECE5-EF70-4355-AA39-B204B086F753}" name="Min elevation" totalsRowDxfId="5" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{D75C68D2-6308-4B32-BFEC-DFF390DB8E53}" name="Max elevation" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
+    <tableColumn id="16" xr3:uid="{D75C68D2-6308-4B32-BFEC-DFF390DB8E53}" name="Max elevation" totalsRowDxfId="4" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{36486A17-D0A0-48BD-A954-F404E9596B7F}" name="Min MAP:PET" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
+    <tableColumn id="13" xr3:uid="{36486A17-D0A0-48BD-A954-F404E9596B7F}" name="Min MAP:PET" totalsRowDxfId="3" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{99A2031C-68A9-4CB7-9470-3CF073E8938E}" name="Max MAP:PET" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
+    <tableColumn id="17" xr3:uid="{99A2031C-68A9-4CB7-9470-3CF073E8938E}" name="Max MAP:PET" totalsRowDxfId="2" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -10869,7 +10869,7 @@
     <tableColumn id="1" xr3:uid="{2BBF6521-99F9-49EC-9C13-C6835493D245}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{0DDE2867-2EF4-48CD-8D28-92B0EFFA35E5}" name="Wet or Dry Zone" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{0DDE2867-2EF4-48CD-8D28-92B0EFFA35E5}" name="Wet or Dry Zone" totalsRowDxfId="1" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -10966,14 +10966,14 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="98" xr:uid="{D5C443B2-EDE2-4250-B2EE-016878D19AD9}" name="Table_SourceData_FeedlotMMS" displayName="Table_SourceData_FeedlotMMS" ref="D27:E33" totalsRowShown="0">
-  <autoFilter ref="D27:E33" xr:uid="{D5C443B2-EDE2-4250-B2EE-016878D19AD9}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="98" xr:uid="{D5C443B2-EDE2-4250-B2EE-016878D19AD9}" name="Table_SourceData_FeedlotMMS" displayName="Table_SourceData_FeedlotMMS" ref="D27:E32" totalsRowShown="0">
+  <autoFilter ref="D27:E32" xr:uid="{D5C443B2-EDE2-4250-B2EE-016878D19AD9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{F2B173A3-CADE-4DCA-988D-39EE2392D8DB}" name="MMS"/>
-    <tableColumn id="2" xr3:uid="{67006656-167A-4452-9820-88D798B88ADD}" name="Symbol and MMS" dataDxfId="17" dataCellStyle="Content normal"/>
+    <tableColumn id="2" xr3:uid="{67006656-167A-4452-9820-88D798B88ADD}" name="Symbol and MMS" dataDxfId="34" dataCellStyle="Content normal"/>
   </tableColumns>
   <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -10989,7 +10989,7 @@
     <tableColumn id="1" xr3:uid="{7CC796C2-63D2-47F7-9053-D908618080F5}" name="Is in leaching zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{DAA00D67-052D-437D-8304-FCF408B01074}" name="FracWET" dataDxfId="28">
+    <tableColumn id="2" xr3:uid="{DAA00D67-052D-437D-8304-FCF408B01074}" name="FracWET" dataDxfId="0">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -11064,22 +11064,22 @@
     <tableColumn id="1" xr3:uid="{FDCB848C-205F-48EA-BACF-F54BCD324E05}" name="Feedlot type">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_DietProperties_Data(), Table_SourceData_Feedlot_DietProperties[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{3306F917-B06C-4CC9-B1B1-D97D858E6DAA}" name="Nutrient analysis" dataDxfId="16" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{3306F917-B06C-4CC9-B1B1-D97D858E6DAA}" name="Nutrient analysis" dataDxfId="33" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_DietProperties_Data(), Table_SourceData_Feedlot_DietProperties[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{F162F7C2-B0FA-499A-BD58-855C4DF97FA8}" name="Unit" dataDxfId="15" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{F162F7C2-B0FA-499A-BD58-855C4DF97FA8}" name="Unit" dataDxfId="32" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_DietProperties_Data(), Table_SourceData_Feedlot_DietProperties[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{D395A9F5-9A85-4032-A7C1-EC470516DD87}" name="2010-2014" dataDxfId="14" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{D395A9F5-9A85-4032-A7C1-EC470516DD87}" name="2010-2014" dataDxfId="31" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_DietProperties_Data(), Table_SourceData_Feedlot_DietProperties[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{B149E561-7044-4839-B850-C751ABC364C9}" name="2015-2019" dataDxfId="13" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{B149E561-7044-4839-B850-C751ABC364C9}" name="2015-2019" dataDxfId="30" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_DietProperties_Data(), Table_SourceData_Feedlot_DietProperties[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{ECEB8E53-4880-43AE-9D36-F969D05BCB18}" name="2020-2023" dataDxfId="12" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{ECEB8E53-4880-43AE-9D36-F969D05BCB18}" name="2020-2023" dataDxfId="29" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_DietProperties_Data(), Table_SourceData_Feedlot_DietProperties[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{3B7FAEA4-08D7-48B2-9062-7D93639222CC}" name="2020-2023 Converted to fraction" dataDxfId="11" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{3B7FAEA4-08D7-48B2-9062-7D93639222CC}" name="2020-2023 Converted to fraction" dataDxfId="28" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_DietProperties_Data(), Table_SourceData_Feedlot_DietProperties[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -11102,22 +11102,22 @@
     <tableColumn id="1" xr3:uid="{96F6B4E3-E1EE-445F-9BCE-628B89FC3727}" name="Feedlot type">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_AnimalCharacteristics_Data(), Table_SourceData_Feedlot_AnimalCharacteristics[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{6B651FD0-BCF6-4081-8A93-6B21A1D6CA99}" name="Characteristic" dataDxfId="10" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{6B651FD0-BCF6-4081-8A93-6B21A1D6CA99}" name="Characteristic" dataDxfId="27" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_AnimalCharacteristics_Data(), Table_SourceData_Feedlot_AnimalCharacteristics[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{3F266A2B-76EA-4E95-B049-75B8E4AB351F}" name="Unit" dataDxfId="9" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{3F266A2B-76EA-4E95-B049-75B8E4AB351F}" name="Unit" dataDxfId="26" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_AnimalCharacteristics_Data(), Table_SourceData_Feedlot_AnimalCharacteristics[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{15472767-3F72-4A65-88AC-C3242A8E1662}" name="2005-2009" dataDxfId="8" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{15472767-3F72-4A65-88AC-C3242A8E1662}" name="2005-2009" dataDxfId="25" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_AnimalCharacteristics_Data(), Table_SourceData_Feedlot_AnimalCharacteristics[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{5F74A8B9-7EFB-4457-8ADA-5E1ABA9DA889}" name="2010-2014" dataDxfId="7" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{5F74A8B9-7EFB-4457-8ADA-5E1ABA9DA889}" name="2010-2014" dataDxfId="24" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_AnimalCharacteristics_Data(), Table_SourceData_Feedlot_AnimalCharacteristics[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{E54F2812-2E8B-41EB-98A8-46890B5B4E13}" name="2015-2019" dataDxfId="6" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{E54F2812-2E8B-41EB-98A8-46890B5B4E13}" name="2015-2019" dataDxfId="23" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_AnimalCharacteristics_Data(), Table_SourceData_Feedlot_AnimalCharacteristics[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{88EEE0E3-F5D0-41DF-80EF-59472377C29A}" name="2020-2023" dataDxfId="5" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{88EEE0E3-F5D0-41DF-80EF-59472377C29A}" name="2020-2023" dataDxfId="22" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_AnimalCharacteristics_Data(), Table_SourceData_Feedlot_AnimalCharacteristics[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -11135,7 +11135,7 @@
     <tableColumn id="1" xr3:uid="{9D472457-4D8B-44ED-9567-B889D058C2F1}" name="Feedlot type">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_DurationOfStay_Data(), Table_SourceData_Feedlot_LengthOfStay[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{DA3DA009-634B-4C70-926B-C8FB255EB4DC}" name="Length of stay" dataDxfId="4" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{DA3DA009-634B-4C70-926B-C8FB255EB4DC}" name="Length of stay" dataDxfId="21" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_DurationOfStay_Data(), Table_SourceData_Feedlot_LengthOfStay[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -11155,13 +11155,13 @@
     <tableColumn id="1" xr3:uid="{C80C08D8-3F48-4E18-98E3-9B53ACB6C6D9}" name="Treatment stage T">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_NitrousOxideEFs_Data(), Table_SourceData_Feedlot_NO2EFs[[#Headers],[Treatment stage T]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{2BCD8589-5CB8-4ED1-AF2B-2866CEF779A8}" name="MMS m" dataDxfId="3" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{2BCD8589-5CB8-4ED1-AF2B-2866CEF779A8}" name="MMS m" dataDxfId="20" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_NitrousOxideEFs_Data(), Table_SourceData_Feedlot_NO2EFs[[#Headers],[Treatment stage T]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{51E876CD-83B6-49C8-85DD-E2F427A3DCD0}" name="EF mT" dataDxfId="2" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{51E876CD-83B6-49C8-85DD-E2F427A3DCD0}" name="EF mT" dataDxfId="19" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_NitrousOxideEFs_Data(), Table_SourceData_Feedlot_NO2EFs[[#Headers],[Treatment stage T]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{BEDEE6BB-8013-495A-8D74-2C8D37558C98}" name="NIR definition" dataDxfId="1" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{BEDEE6BB-8013-495A-8D74-2C8D37558C98}" name="NIR definition" dataDxfId="18" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_NitrousOxideEFs_Data(), Table_SourceData_Feedlot_NO2EFs[[#Headers],[Treatment stage T]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -11170,7 +11170,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{100A8309-C0D3-4638-A47B-72840A042D9A}" name="Table_SourceData_Feedlot_FracGASMmT" displayName="Table_SourceData_Feedlot_FracGASMmT" ref="D112:G117" totalsRowShown="0" headerRowDxfId="0" headerRowCellStyle="Content normal" dataCellStyle="Content normal">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{100A8309-C0D3-4638-A47B-72840A042D9A}" name="Table_SourceData_Feedlot_FracGASMmT" displayName="Table_SourceData_Feedlot_FracGASMmT" ref="D112:G117" totalsRowShown="0" headerRowDxfId="17" headerRowCellStyle="Content normal" dataCellStyle="Content normal">
   <autoFilter ref="D112:G117" xr:uid="{100A8309-C0D3-4638-A47B-72840A042D9A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -13476,22 +13476,22 @@
     </row>
     <row r="175" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D175" s="39" t="s">
+        <v>304</v>
+      </c>
+      <c r="E175" s="39" t="s">
+        <v>305</v>
+      </c>
+      <c r="F175" s="39" t="s">
+        <v>306</v>
+      </c>
+      <c r="G175" s="39" t="s">
         <v>307</v>
-      </c>
-      <c r="E175" s="39" t="s">
-        <v>308</v>
-      </c>
-      <c r="F175" s="39" t="s">
-        <v>309</v>
-      </c>
-      <c r="G175" s="39" t="s">
-        <v>310</v>
       </c>
       <c r="H175" s="39" t="s">
         <v>36</v>
       </c>
       <c r="J175" s="1" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="BM175" s="7"/>
       <c r="BN175" s="7"/>
@@ -13519,7 +13519,7 @@
         <v>Any</v>
       </c>
       <c r="J176" s="1" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="BM176" s="7"/>
       <c r="BN176" s="7"/>
@@ -13547,7 +13547,7 @@
         <v>Any</v>
       </c>
       <c r="J177" s="1" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="BM177" s="7"/>
       <c r="BN177" s="7"/>
@@ -14659,7 +14659,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="C1" s="137" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -14716,19 +14716,19 @@
       </c>
       <c r="C6" s="24"/>
       <c r="D6" s="135" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="E6" s="135" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="F6" s="135" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="G6" s="135" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="H6" s="135" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="I6" s="1"/>
       <c r="J6" s="24"/>
@@ -14741,7 +14741,7 @@
       </c>
       <c r="C7" s="24"/>
       <c r="D7" s="1" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="E7" s="128">
         <f>'4.1.1.1-2 Methane'!E164</f>
@@ -14770,7 +14770,7 @@
       </c>
       <c r="C8" s="24"/>
       <c r="D8" s="1" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="E8" s="128">
         <f>'4.1.1.1-2 Methane'!N164</f>
@@ -14796,7 +14796,7 @@
       <c r="A9" s="17"/>
       <c r="C9" s="24"/>
       <c r="D9" s="1" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="E9" s="128">
         <f>'4.1.1.3-4 Direct N20'!E207</f>
@@ -14824,7 +14824,7 @@
       </c>
       <c r="C10" s="24"/>
       <c r="D10" s="1" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="E10" s="128">
         <f>'4.1.1.3-4 Direct N20'!M207</f>
@@ -14853,7 +14853,7 @@
       </c>
       <c r="C11" s="24"/>
       <c r="D11" s="1" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="E11" s="128">
         <f>'4.1.1.5-6 Atmos Deposition'!$E$60</f>
@@ -14882,7 +14882,7 @@
       </c>
       <c r="C12" s="24"/>
       <c r="D12" s="1" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="E12" s="128">
         <f>'4.1.1.5-6 Atmos Deposition'!$M$60</f>
@@ -14911,19 +14911,19 @@
       </c>
       <c r="C13" s="24"/>
       <c r="D13" s="1" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="E13" s="128" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="F13" s="57" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="G13" s="128">
         <v>0</v>
       </c>
       <c r="H13" s="57" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="I13" s="1"/>
       <c r="J13" s="24"/>
@@ -14936,19 +14936,19 @@
       </c>
       <c r="C14" s="24"/>
       <c r="D14" s="1" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="E14" s="128" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="F14" s="57" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="G14" s="128">
         <v>0</v>
       </c>
       <c r="H14" s="57" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="I14" s="1"/>
       <c r="J14" s="24"/>
@@ -14957,7 +14957,7 @@
     <row r="15" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C15" s="24"/>
       <c r="D15" s="31" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E15" s="25"/>
       <c r="F15" s="31"/>
@@ -14994,7 +14994,7 @@
       </c>
       <c r="C17" s="24"/>
       <c r="D17" s="115" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
@@ -15011,7 +15011,7 @@
       </c>
       <c r="C18" s="24"/>
       <c r="D18" s="133" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
@@ -15043,19 +15043,19 @@
       </c>
       <c r="C20" s="24"/>
       <c r="D20" s="135" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="E20" s="135" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="F20" s="135" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G20" s="135" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="H20" s="135" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="I20" s="1"/>
       <c r="J20" s="24"/>
@@ -15064,7 +15064,7 @@
     <row r="21" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C21" s="24"/>
       <c r="D21" s="1" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="E21" s="134">
         <f>'4.1.1.9 Manure applied to soils'!$E$56</f>
@@ -15075,10 +15075,10 @@
         <v>kg N</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="I21" s="1"/>
       <c r="J21" s="24"/>
@@ -15087,7 +15087,7 @@
     <row r="22" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C22" s="24"/>
       <c r="D22" s="1" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="E22" s="134">
         <f>'4.1.1.9 Manure applied to soils'!$E$104</f>
@@ -15098,10 +15098,10 @@
         <v>kg N</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="I22" s="1"/>
       <c r="J22" s="24"/>
@@ -15110,7 +15110,7 @@
     <row r="23" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C23" s="24"/>
       <c r="D23" s="1" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="E23" s="134">
         <f>'4.1.1.9 Manure applied to soils'!$E$123</f>
@@ -15121,10 +15121,10 @@
         <v>kg N</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="I23" s="1"/>
       <c r="J23" s="24"/>
@@ -16084,7 +16084,7 @@
         <v>8</v>
       </c>
       <c r="E21" s="42" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>11</v>
@@ -16676,7 +16676,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="C1" s="71" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="K1" s="59"/>
       <c r="L1" s="59"/>
@@ -16719,7 +16719,7 @@
     <row r="5" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="16"/>
       <c r="D5" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -16734,13 +16734,13 @@
       </c>
       <c r="D7" s="66"/>
       <c r="E7" s="41" t="s">
+        <v>148</v>
+      </c>
+      <c r="F7" s="41" t="s">
         <v>149</v>
       </c>
-      <c r="F7" s="41" t="s">
+      <c r="G7" s="41" t="s">
         <v>150</v>
-      </c>
-      <c r="G7" s="41" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -16762,7 +16762,7 @@
         <v>100</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -16810,16 +16810,16 @@
         <v>4.1.1.5-6 Atmospheric deposition</v>
       </c>
       <c r="D13" s="66" t="s">
-        <v>153</v>
+        <v>341</v>
       </c>
       <c r="E13" s="41" t="s">
+        <v>148</v>
+      </c>
+      <c r="F13" s="41" t="s">
         <v>149</v>
       </c>
-      <c r="F13" s="41" t="s">
+      <c r="G13" s="41" t="s">
         <v>150</v>
-      </c>
-      <c r="G13" s="41" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -16828,7 +16828,7 @@
         <v>4.1.1.9 Manure applied to soils</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E14" s="55" cm="1">
         <f t="array" ref="E14">_xlfn.XLOOKUP(1, (Table_SourceData_Feedlot_AnimalCharacteristics[Feedlot type] = E$13) * (Table_SourceData_Feedlot_AnimalCharacteristics[Characteristic] = $D$14), Table_SourceData_Feedlot_AnimalCharacteristics[2020-2023], "Not Found")</f>
@@ -16843,7 +16843,7 @@
         <v>8.1999999999999993</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -16871,7 +16871,7 @@
         <v>4</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E16" s="55" cm="1">
         <f t="array" ref="E16">_xlfn.XLOOKUP(1, (Table_SourceData_Feedlot_DietProperties[Feedlot type] = E$13) * (Table_SourceData_Feedlot_DietProperties[Nutrient analysis] = $D$16), Table_SourceData_Feedlot_DietProperties[2020-2023 Converted to fraction], "Not Found")</f>
@@ -16895,7 +16895,7 @@
         <v>Constants - Feedlot</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E17" s="55" cm="1">
         <f t="array" ref="E17">_xlfn.XLOOKUP(1, (Table_SourceData_Feedlot_AnimalCharacteristics[Feedlot type] = E$13) * (Table_SourceData_Feedlot_AnimalCharacteristics[Characteristic] = $D$17), Table_SourceData_Feedlot_AnimalCharacteristics[2020-2023], "Not Found")</f>
@@ -16910,7 +16910,7 @@
         <v>7</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -16925,16 +16925,16 @@
         <v>Constants - Common</v>
       </c>
       <c r="D19" s="66" t="s">
-        <v>154</v>
+        <v>342</v>
       </c>
       <c r="E19" s="41" t="s">
+        <v>148</v>
+      </c>
+      <c r="F19" s="41" t="s">
         <v>149</v>
       </c>
-      <c r="F19" s="41" t="s">
+      <c r="G19" s="41" t="s">
         <v>150</v>
-      </c>
-      <c r="G19" s="41" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -16943,7 +16943,7 @@
         <v>Acknowledgements</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E20" s="69" cm="1">
         <f t="array" ref="E20">_xlfn.XLOOKUP(1, (Table_SourceData_Feedlot_AnimalCharacteristics[Feedlot type] = E$19) * (Table_SourceData_Feedlot_AnimalCharacteristics[Characteristic] = $D$20), Table_SourceData_Feedlot_AnimalCharacteristics[2020-2023], "Not Found")</f>
@@ -16958,7 +16958,7 @@
         <v>8.1999999999999993</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -16983,7 +16983,7 @@
     </row>
     <row r="22" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D22" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E22" s="69" cm="1">
         <f t="array" ref="E22">_xlfn.XLOOKUP(1, (Table_SourceData_Feedlot_DietProperties[Feedlot type] = E$19) * (Table_SourceData_Feedlot_DietProperties[Nutrient analysis] = $D$22), Table_SourceData_Feedlot_DietProperties[2020-2023 Converted to fraction], "Not Found")</f>
@@ -17003,7 +17003,7 @@
     </row>
     <row r="23" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D23" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E23" s="69" cm="1">
         <f t="array" ref="E23">_xlfn.XLOOKUP(1, (Table_SourceData_Feedlot_AnimalCharacteristics[Feedlot type] = E$19) * (Table_SourceData_Feedlot_AnimalCharacteristics[Characteristic] = $D$23), Table_SourceData_Feedlot_AnimalCharacteristics[2020-2023], "Not Found")</f>
@@ -17018,14 +17018,14 @@
         <v>7</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="25" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="17"/>
       <c r="D25" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -17034,22 +17034,22 @@
     <row r="27" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="17"/>
       <c r="D27" s="51" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="17"/>
       <c r="D28" s="66" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E28" s="101" t="s">
+        <v>148</v>
+      </c>
+      <c r="F28" s="101" t="s">
         <v>149</v>
       </c>
-      <c r="F28" s="101" t="s">
+      <c r="G28" s="101" t="s">
         <v>150</v>
-      </c>
-      <c r="G28" s="101" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -17079,7 +17079,7 @@
     <row r="32" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="70"/>
       <c r="D32" s="51" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -17088,13 +17088,13 @@
         <v>105</v>
       </c>
       <c r="E33" s="101" t="s">
+        <v>148</v>
+      </c>
+      <c r="F33" s="101" t="s">
         <v>149</v>
       </c>
-      <c r="F33" s="101" t="s">
+      <c r="G33" s="101" t="s">
         <v>150</v>
-      </c>
-      <c r="G33" s="101" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -17148,21 +17148,21 @@
     <row r="39" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="17"/>
       <c r="D39" s="51" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D40" s="66" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E40" s="101" t="s">
+        <v>148</v>
+      </c>
+      <c r="F40" s="101" t="s">
         <v>149</v>
       </c>
-      <c r="F40" s="101" t="s">
+      <c r="G40" s="101" t="s">
         <v>150</v>
-      </c>
-      <c r="G40" s="101" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -17196,16 +17196,16 @@
     </row>
     <row r="45" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D45" s="66" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E45" s="101" t="s">
+        <v>148</v>
+      </c>
+      <c r="F45" s="101" t="s">
         <v>149</v>
       </c>
-      <c r="F45" s="101" t="s">
+      <c r="G45" s="101" t="s">
         <v>150</v>
-      </c>
-      <c r="G45" s="101" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -17217,7 +17217,7 @@
     </row>
     <row r="47" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D47" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E47" s="49">
         <v>0.25</v>
@@ -17233,9 +17233,8 @@
       </c>
     </row>
     <row r="48" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D48" s="1" t="str">
-        <f>"Applied to farm soils as fertiliser" &amp; IF(SUM($E$48:$G$48)&gt;0, "⚠️", "")</f>
-        <v>Applied to farm soils as fertiliser⚠️</v>
+      <c r="D48" s="1" t="s">
+        <v>343</v>
       </c>
       <c r="E48" s="49">
         <v>0.25</v>
@@ -17252,7 +17251,7 @@
     </row>
     <row r="49" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D49" s="1" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="E49" s="102">
         <f t="shared" ref="E49:G49" si="1">1-SUM(E47:E48)</f>
@@ -17279,7 +17278,7 @@
     </row>
     <row r="52" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D52" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E52" s="49">
         <v>0.25</v>
@@ -17295,9 +17294,8 @@
       </c>
     </row>
     <row r="53" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D53" s="1" t="str">
-        <f>"Applied to farm soils as fertiliser" &amp; IF(SUM($E$53:$G$53)&gt;0, "⚠️", "")</f>
-        <v>Applied to farm soils as fertiliser⚠️</v>
+      <c r="D53" s="1" t="s">
+        <v>343</v>
       </c>
       <c r="E53" s="49">
         <v>0.25</v>
@@ -17314,7 +17312,7 @@
     </row>
     <row r="54" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D54" s="1" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="E54" s="102">
         <f>1-SUM(E52:E53)</f>
@@ -17341,7 +17339,7 @@
     </row>
     <row r="57" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D57" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E57" s="49">
         <v>0.25</v>
@@ -17357,9 +17355,8 @@
       </c>
     </row>
     <row r="58" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D58" s="1" t="str">
-        <f>"Applied to farm soils as fertiliser" &amp; IF(SUM($E$53:$G$53)&gt;0, "⚠️", "")</f>
-        <v>Applied to farm soils as fertiliser⚠️</v>
+      <c r="D58" s="1" t="s">
+        <v>343</v>
       </c>
       <c r="E58" s="49">
         <v>0.25</v>
@@ -17376,7 +17373,7 @@
     </row>
     <row r="59" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D59" s="1" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="E59" s="102">
         <f>1-SUM(E57:E58)</f>
@@ -17395,32 +17392,29 @@
       </c>
     </row>
     <row r="60" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D60" s="115" t="str">
-        <f>IF((SUM(E48:G48)+SUM($E$53:$G$53)+SUM($E$58:$G$58))&gt;0,"⚠️ Alert: manure applied to farm soils as fertiliser needs to be accounted for against the relevant crop or herd","")</f>
-        <v>⚠️ Alert: manure applied to farm soils as fertiliser needs to be accounted for against the relevant crop or herd</v>
-      </c>
+      <c r="D60" s="115"/>
     </row>
     <row r="61" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D62" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="E62" s="42" t="s">
+        <v>308</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
     <row r="63" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D63" s="1" t="s">
-        <v>305</v>
-      </c>
       <c r="E63" s="42" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="64" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E64" s="42" t="s">
-        <v>315</v>
-      </c>
-      <c r="F64" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
+    <row r="64" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -17531,10 +17525,10 @@
       <formula1>1</formula1>
     </dataValidation>
     <dataValidation operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E41:G41" xr:uid="{C4745536-8208-45E9-8F7A-99B1E2C94379}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E63" xr:uid="{AF94BFC8-A9BD-4286-932B-111409BF1EB6}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E62" xr:uid="{AF94BFC8-A9BD-4286-932B-111409BF1EB6}">
       <formula1>INDIRECT("Table_SourceData_Feedlot_CropProdSystems[Production system]")</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E64" xr:uid="{20E9D9A1-CABD-46A5-B149-02F06B30AA0E}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E63" xr:uid="{20E9D9A1-CABD-46A5-B149-02F06B30AA0E}">
       <formula1>INDIRECT("Table_SourceData_Feedlot_IrrigationMethods[Irrigation method]")</formula1>
     </dataValidation>
   </dataValidations>
@@ -17563,7 +17557,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEFC1CB6-2463-438A-90A4-6F54247DF8D8}">
-  <dimension ref="A1:X169"/>
+  <dimension ref="A1:S169"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -17573,27 +17567,27 @@
     <col min="10" max="10" width="4.7109375" style="1" customWidth="1"/>
     <col min="11" max="11" width="4.7109375" customWidth="1"/>
     <col min="12" max="12" width="4.7109375" style="1" customWidth="1"/>
-    <col min="13" max="23" width="30.7109375" style="1" customWidth="1"/>
-    <col min="24" max="24" width="4.7109375" style="1" customWidth="1"/>
+    <col min="13" max="18" width="30.7109375" style="1" customWidth="1"/>
+    <col min="19" max="19" width="4.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="8" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:19" s="8" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="71" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="2" spans="1:24" s="9" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" s="9" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
@@ -17603,7 +17597,7 @@
       <c r="J3" s="4"/>
       <c r="L3" s="4"/>
       <c r="M3" s="4" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="N3" s="4"/>
       <c r="O3" s="4"/>
@@ -17611,26 +17605,21 @@
       <c r="Q3" s="4"/>
       <c r="R3" s="4"/>
       <c r="S3" s="4"/>
-      <c r="T3" s="4"/>
-      <c r="U3" s="4"/>
-      <c r="V3" s="4"/>
-      <c r="W3" s="4"/>
-      <c r="X3" s="4"/>
-    </row>
-    <row r="4" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="str">
         <f>HYPERLINK("#'Results'!A1", "Results")</f>
         <v>Results</v>
       </c>
     </row>
-    <row r="5" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="16"/>
       <c r="D5" s="6" t="str" cm="1">
         <f t="array" ref="D5">MMS_Feedlot_Methane_Equations.VEERG_4_1_1_1__5_VolatileSolidProduction_Title()</f>
         <v>Volatile solid production</v>
       </c>
     </row>
-    <row r="6" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="20" t="s">
         <v>3</v>
       </c>
@@ -17639,7 +17628,7 @@
         <v>VEERG 2026: 4.1.1.1, Equation (5)</v>
       </c>
     </row>
-    <row r="7" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="17" t="str">
         <f>HYPERLINK("#'Input - Site'!A1", "Site")</f>
         <v>Site</v>
@@ -17652,16 +17641,16 @@
         <v>=MMS_Feedlot_Methane_Equations.VEERG_4_1_1_1__5_VolatileSolidProduction</v>
       </c>
     </row>
-    <row r="8" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="str">
         <f>HYPERLINK("#'Input - Feedlot'!A1", "Feedlot")</f>
         <v>Feedlot</v>
       </c>
     </row>
-    <row r="9" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="17"/>
     </row>
-    <row r="10" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>77</v>
       </c>
@@ -17673,7 +17662,7 @@
         <v>VS_j</v>
       </c>
     </row>
-    <row r="11" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="22" t="str">
         <f>HYPERLINK("#'4.1.1.1-2 Methane'!A1", "4.1.1.1-2 Methane")</f>
         <v>4.1.1.1-2 Methane</v>
@@ -17686,13 +17675,13 @@
         <v>kg/head/day</v>
       </c>
     </row>
-    <row r="12" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="str">
         <f>HYPERLINK("#'4.1.1.3-4 Direct N20'!A1", "4.1.1.3-4 Direct N2O")</f>
         <v>4.1.1.3-4 Direct N2O</v>
       </c>
     </row>
-    <row r="13" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="17" t="str">
         <f>HYPERLINK("#'4.1.1.5-6 Atmos Deposition'!A1", "4.1.1.5-6 Atmospheric deposition")</f>
         <v>4.1.1.5-6 Atmospheric deposition</v>
@@ -17710,7 +17699,7 @@
         <v>See M1_Table_I_j</v>
       </c>
     </row>
-    <row r="14" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="str">
         <f>HYPERLINK("#'4.1.1.9 Manure applied to soils'!A1", "4.1.1.9 Manure applied to soils")</f>
         <v>4.1.1.9 Manure applied to soils</v>
@@ -17727,7 +17716,7 @@
         <v>See M1_Table_DMD_j</v>
       </c>
     </row>
-    <row r="15" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D15" s="60" t="str">
         <v>A</v>
       </c>
@@ -17740,7 +17729,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="16" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="18" t="s">
         <v>4</v>
       </c>
@@ -17751,10 +17740,10 @@
         <v>Constants - Feedlot</v>
       </c>
       <c r="D17" s="105" t="s">
+        <v>160</v>
+      </c>
+      <c r="M17" s="105" t="s">
         <v>163</v>
-      </c>
-      <c r="M17" s="105" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="18" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -17763,10 +17752,10 @@
         <v>Constants - Livestock</v>
       </c>
       <c r="D18" s="104" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="M18" s="104" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="19" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -17775,22 +17764,22 @@
         <v>Constants - Common</v>
       </c>
       <c r="D19" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="E19" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="E19" s="54" t="s">
+      <c r="F19" s="54" t="s">
         <v>150</v>
       </c>
-      <c r="F19" s="54" t="s">
-        <v>151</v>
-      </c>
       <c r="M19" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="N19" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="N19" s="54" t="s">
+      <c r="O19" s="54" t="s">
         <v>150</v>
-      </c>
-      <c r="O19" s="54" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="20" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -17832,38 +17821,38 @@
     <row r="21" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="22" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D22" s="105" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="M22" s="105" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="23" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D23" s="104" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="M23" s="104" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="24" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D24" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="E24" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="E24" s="54" t="s">
+      <c r="F24" s="54" t="s">
         <v>150</v>
       </c>
-      <c r="F24" s="54" t="s">
-        <v>151</v>
-      </c>
       <c r="M24" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="N24" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="N24" s="54" t="s">
+      <c r="O24" s="54" t="s">
         <v>150</v>
-      </c>
-      <c r="O24" s="54" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="25" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -17901,38 +17890,38 @@
     <row r="26" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="27" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D27" s="105" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="M27" s="105" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
     </row>
     <row r="28" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D28" s="104" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="M28" s="104" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
     </row>
     <row r="29" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D29" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="E29" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="E29" s="54" t="s">
+      <c r="F29" s="54" t="s">
         <v>150</v>
       </c>
-      <c r="F29" s="54" t="s">
-        <v>151</v>
-      </c>
       <c r="M29" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="N29" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="N29" s="54" t="s">
+      <c r="O29" s="54" t="s">
         <v>150</v>
-      </c>
-      <c r="O29" s="54" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="30" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -17971,7 +17960,7 @@
     </row>
     <row r="31" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="32" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="33" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C33" s="48"/>
       <c r="D33" s="48"/>
       <c r="E33" s="48"/>
@@ -17987,21 +17976,20 @@
       <c r="P33" s="48"/>
       <c r="Q33" s="48"/>
       <c r="R33" s="48"/>
-      <c r="S33" s="48"/>
-    </row>
-    <row r="34" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D34" s="6" t="str" cm="1">
         <f t="array" ref="D34">MMS_Feedlot_Methane_Equations.VEERG_4_1_1_1__2_Stage1MethaneProductionDrylot_Title()</f>
         <v>Production of methane in treatment stage 1 MMS</v>
       </c>
     </row>
-    <row r="35" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D35" s="5" t="str" cm="1">
         <f t="array" ref="D35">MMS_Feedlot_Methane_Equations.VEERG_4_1_1_1__2_Stage1MethaneProductionDrylot_Source()</f>
         <v>VEERG 2026: 4.1.1.1, Equation (2)</v>
       </c>
     </row>
-    <row r="36" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D36" s="13" t="s">
         <v>27</v>
       </c>
@@ -18010,9 +17998,9 @@
         <v>=MMS_Feedlot_Methane_Equations.VEERG_4_1_1_1__2_Stage1MethaneProductionDrylot</v>
       </c>
     </row>
-    <row r="37" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="38" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="39" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D39" s="56" t="s">
         <v>30</v>
       </c>
@@ -18021,7 +18009,7 @@
         <v>M_jm5T1</v>
       </c>
     </row>
-    <row r="40" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D40" s="56" t="s">
         <v>20</v>
       </c>
@@ -18030,8 +18018,8 @@
         <v>kg CH4/head/day</v>
       </c>
     </row>
-    <row r="41" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="42" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D42" s="60" t="str" cm="1">
         <f t="array" ref="D42:E47">MMS_Feedlot_Methane_Equations.VEERG_4_1_1_1__2_Stage1MethaneProductionDrylot_Arguments()</f>
         <v>VS_j</v>
@@ -18045,7 +18033,7 @@
         <v>See M1_Table_VS_j</v>
       </c>
     </row>
-    <row r="43" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D43" s="60" t="str">
         <v>BO</v>
       </c>
@@ -18058,7 +18046,7 @@
         <v>0.19</v>
       </c>
     </row>
-    <row r="44" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D44" s="60" t="str">
         <v>MMS_m5T1</v>
       </c>
@@ -18071,7 +18059,7 @@
         <v>SeeTable_MMS_m-5_T-1</v>
       </c>
     </row>
-    <row r="45" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D45" s="60" t="str">
         <v>MCF_im5</v>
       </c>
@@ -18084,7 +18072,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="46" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D46" s="60" t="str">
         <v>rho</v>
       </c>
@@ -18097,7 +18085,7 @@
         <v>0.6784</v>
       </c>
     </row>
-    <row r="47" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D47" s="60" t="str">
         <v>i</v>
       </c>
@@ -18110,32 +18098,32 @@
         <v>NSW</v>
       </c>
     </row>
-    <row r="48" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="49" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D49" s="105" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="50" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D50" s="104" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="51" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D51" s="54" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E51" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="F51" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="F51" s="54" t="s">
+      <c r="G51" s="54" t="s">
         <v>150</v>
       </c>
-      <c r="G51" s="54" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="52" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="52" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D52" s="55" t="str">
         <f>'Input - Feedlot'!$D$29</f>
         <v>Drylot (feed pad)</v>
@@ -18156,50 +18144,50 @@
         <v>101</v>
       </c>
     </row>
-    <row r="53" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="54" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D54" s="105" t="s">
+        <v>219</v>
+      </c>
+      <c r="M54" s="105" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="55" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D55" s="104" t="s">
+        <v>220</v>
+      </c>
+      <c r="M55" s="104" t="s">
         <v>222</v>
       </c>
-      <c r="M54" s="105" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="55" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D55" s="104" t="s">
-        <v>223</v>
-      </c>
-      <c r="M55" s="104" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="56" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="56" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D56" s="54" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E56" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="F56" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="F56" s="54" t="s">
+      <c r="G56" s="54" t="s">
         <v>150</v>
       </c>
-      <c r="G56" s="54" t="s">
-        <v>151</v>
-      </c>
       <c r="M56" s="54" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="N56" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="O56" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="O56" s="54" t="s">
+      <c r="P56" s="54" t="s">
         <v>150</v>
       </c>
-      <c r="P56" s="54" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="57" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="57" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D57" s="55" t="str">
         <f>'Input - Feedlot'!$D$29</f>
         <v>Drylot (feed pad)</v>
@@ -18241,14 +18229,14 @@
         <v>kg CH4/head/day</v>
       </c>
     </row>
-    <row r="58" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D58" s="106" t="str">
         <f>IF(ISNUMBER($G$45),"", "⚠️ ALERT: No MCFim5 data provided. Zero is used instead.")</f>
         <v/>
       </c>
     </row>
-    <row r="59" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C60" s="48"/>
       <c r="D60" s="48"/>
       <c r="E60" s="48"/>
@@ -18264,22 +18252,20 @@
       <c r="P60" s="48"/>
       <c r="Q60" s="48"/>
       <c r="R60" s="48"/>
-      <c r="S60" s="48"/>
-      <c r="T60" s="48"/>
-    </row>
-    <row r="61" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="61" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D61" s="6" t="str" cm="1">
         <f t="array" ref="D61">MMS_Feedlot_Methane_Equations.VEERG_4_1_1_1__3_Stage2MethaneProduction_Title()</f>
         <v>Production of methane in treatment stage 2 MMS</v>
       </c>
     </row>
-    <row r="62" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D62" s="5" t="str" cm="1">
         <f t="array" ref="D62">MMS_Feedlot_Methane_Equations.VEERG_4_1_1_1__3_Stage2MethaneProduction_Source()</f>
         <v>VEERG 2026: 4.1.1.1, Equation (3)</v>
       </c>
     </row>
-    <row r="63" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D63" s="13" t="s">
         <v>27</v>
       </c>
@@ -18288,7 +18274,7 @@
         <v>=MMS_Feedlot_Methane_Equations.VEERG_4_1_1_1__3_Stage2MethaneProduction</v>
       </c>
     </row>
-    <row r="64" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="65" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D65" s="6"/>
     </row>
@@ -18364,7 +18350,7 @@
         <v>See Table_MMS_m_T-2</v>
       </c>
       <c r="H72" s="117" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="73" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -18409,29 +18395,29 @@
     <row r="76" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="77" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D77" s="105" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="78" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D78" s="104" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="79" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D79" s="54" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E79" s="54" t="s">
         <v>105</v>
       </c>
       <c r="F79" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="G79" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="G79" s="54" t="s">
+      <c r="H79" s="54" t="s">
         <v>150</v>
-      </c>
-      <c r="H79" s="54" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="80" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -18459,7 +18445,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="81" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D81" s="55" t="str">
         <f>'Input - Feedlot'!$D$29</f>
         <v>Drylot (feed pad)</v>
@@ -18484,20 +18470,20 @@
         <v>101</v>
       </c>
     </row>
-    <row r="82" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="83" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D83" s="105" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="84" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D84" s="104" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="85" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D85" s="54" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E85" s="54" t="s">
         <v>105</v>
@@ -18506,7 +18492,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="86" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D86" s="55" t="str">
         <f>'Input - Feedlot'!$D$29</f>
         <v>Drylot (feed pad)</v>
@@ -18523,7 +18509,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="87" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D87" s="55" t="str">
         <f>'Input - Feedlot'!$D$29</f>
         <v>Drylot (feed pad)</v>
@@ -18540,50 +18526,50 @@
         <v>101</v>
       </c>
     </row>
-    <row r="88" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D89" s="105" t="s">
+        <v>223</v>
+      </c>
+      <c r="M89" s="105" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="90" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D90" s="104" t="s">
+        <v>224</v>
+      </c>
+      <c r="M90" s="104" t="s">
         <v>226</v>
       </c>
-      <c r="M89" s="105" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="90" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D90" s="104" t="s">
-        <v>227</v>
-      </c>
-      <c r="M90" s="104" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="91" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="91" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D91" s="54" t="s">
         <v>105</v>
       </c>
       <c r="E91" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="F91" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="F91" s="54" t="s">
+      <c r="G91" s="54" t="s">
         <v>150</v>
-      </c>
-      <c r="G91" s="54" t="s">
-        <v>151</v>
       </c>
       <c r="M91" s="54" t="s">
         <v>105</v>
       </c>
       <c r="N91" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="O91" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="O91" s="54" t="s">
+      <c r="P91" s="54" t="s">
         <v>150</v>
       </c>
-      <c r="P91" s="54" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="92" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="92" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D92" s="55" t="str">
         <f>'Input - Feedlot'!$D$35</f>
         <v>Solid storage</v>
@@ -18625,7 +18611,7 @@
         <v>kg CH4/head/day</v>
       </c>
     </row>
-    <row r="93" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D93" s="55" t="str">
         <f>'Input - Feedlot'!$D$36</f>
         <v>Composting (passive windrow)</v>
@@ -18667,9 +18653,9 @@
         <v>kg CH4/head/day</v>
       </c>
     </row>
-    <row r="94" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C96" s="48"/>
       <c r="D96" s="48"/>
       <c r="E96" s="48"/>
@@ -18685,7 +18671,6 @@
       <c r="P96" s="48"/>
       <c r="Q96" s="48"/>
       <c r="R96" s="48"/>
-      <c r="S96" s="48"/>
     </row>
     <row r="97" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D97" s="6" t="str" cm="1">
@@ -18819,29 +18804,29 @@
     <row r="111" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="112" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D112" s="105" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="113" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D113" s="104" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="114" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D114" s="54" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="113" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D113" s="104" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="114" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D114" s="54" t="s">
-        <v>123</v>
-      </c>
       <c r="E114" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="F114" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="F114" s="54" t="s">
+      <c r="G114" s="54" t="s">
         <v>150</v>
       </c>
-      <c r="G114" s="54" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="115" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="115" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D115" s="55" t="str">
         <f>'Input - Feedlot'!$D$41</f>
         <v>Anaerobic lagoon</v>
@@ -18862,50 +18847,50 @@
         <v>101</v>
       </c>
     </row>
-    <row r="116" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="117" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D117" s="105" t="s">
+        <v>227</v>
+      </c>
+      <c r="M117" s="105" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="118" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D118" s="104" t="s">
+        <v>228</v>
+      </c>
+      <c r="M118" s="104" t="s">
         <v>230</v>
       </c>
-      <c r="M117" s="105" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="118" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D118" s="104" t="s">
-        <v>231</v>
-      </c>
-      <c r="M118" s="104" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="119" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="119" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D119" s="54" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E119" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="F119" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="F119" s="54" t="s">
+      <c r="G119" s="54" t="s">
         <v>150</v>
       </c>
-      <c r="G119" s="54" t="s">
-        <v>151</v>
-      </c>
       <c r="M119" s="54" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N119" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="O119" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="O119" s="54" t="s">
+      <c r="P119" s="54" t="s">
         <v>150</v>
       </c>
-      <c r="P119" s="54" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="120" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="120" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D120" s="55" t="str">
         <f>'Input - Feedlot'!$D$41</f>
         <v>Anaerobic lagoon</v>
@@ -18947,9 +18932,9 @@
         <v>kg CH4/head/day</v>
       </c>
     </row>
-    <row r="121" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="122" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="123" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C123" s="48"/>
       <c r="D123" s="48"/>
       <c r="E123" s="48"/>
@@ -18965,22 +18950,20 @@
       <c r="P123" s="48"/>
       <c r="Q123" s="48"/>
       <c r="R123" s="48"/>
-      <c r="S123" s="48"/>
-      <c r="T123" s="48"/>
-    </row>
-    <row r="124" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="124" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D124" s="6" t="str" cm="1">
         <f t="array" ref="D124">MMS_Feedlot_Methane_Equations.VEERG_4_1_1_1__1_TotalAnnualMethaneEmissions_Title()</f>
         <v>Total annual methane emissions from manure management</v>
       </c>
     </row>
-    <row r="125" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D125" s="5" t="str" cm="1">
         <f t="array" ref="D125">MMS_Feedlot_Methane_Equations.VEERG_4_1_1_1__1_TotalAnnualMethaneEmissions_Source()</f>
         <v>VEERG 2026: 4.1.1.1, Equation (1)</v>
       </c>
     </row>
-    <row r="126" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D126" s="13" t="s">
         <v>27</v>
       </c>
@@ -18989,8 +18972,8 @@
         <v>=MMS_Feedlot_Methane_Equations.VEERG_4_1_1_1__1_TotalAnnualMethaneEmissions</v>
       </c>
     </row>
-    <row r="127" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="128" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D128" s="6"/>
     </row>
     <row r="129" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -19059,23 +19042,23 @@
     <row r="136" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="137" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D137" s="105" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="138" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D138" s="104" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="139" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D139" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="E139" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="E139" s="54" t="s">
+      <c r="F139" s="54" t="s">
         <v>150</v>
-      </c>
-      <c r="F139" s="54" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="140" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -19098,50 +19081,50 @@
     <row r="141" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="142" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D142" s="105" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="M142" s="105" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
     </row>
     <row r="143" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D143" s="104" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="M143" s="104" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
     </row>
     <row r="144" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D144" s="54" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E144" s="54" t="s">
         <v>68</v>
       </c>
       <c r="F144" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="G144" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="G144" s="54" t="s">
+      <c r="H144" s="54" t="s">
         <v>150</v>
       </c>
-      <c r="H144" s="54" t="s">
-        <v>151</v>
-      </c>
       <c r="M144" s="54" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N144" s="54" t="s">
         <v>68</v>
       </c>
       <c r="O144" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="P144" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="P144" s="54" t="s">
+      <c r="Q144" s="54" t="s">
         <v>150</v>
-      </c>
-      <c r="Q144" s="54" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="145" spans="4:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -19165,7 +19148,7 @@
         <v>1.6868877311999992E-3</v>
       </c>
       <c r="I145" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="M145" s="55">
         <v>1</v>
@@ -19187,7 +19170,7 @@
         <v>1.6868877311999992E-3</v>
       </c>
       <c r="R145" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="146" spans="4:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -19211,7 +19194,7 @@
         <v>3.3737754623999993E-4</v>
       </c>
       <c r="I146" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="M146" s="55">
         <v>2</v>
@@ -19233,7 +19216,7 @@
         <v>3.3737754623999993E-4</v>
       </c>
       <c r="R146" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="147" spans="4:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -19257,7 +19240,7 @@
         <v>6.7475509247999987E-4</v>
       </c>
       <c r="I147" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="M147" s="55">
         <v>2</v>
@@ -19279,7 +19262,7 @@
         <v>6.7475509247999987E-4</v>
       </c>
       <c r="R147" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="148" spans="4:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -19303,7 +19286,7 @@
         <v>2.530331596799999E-3</v>
       </c>
       <c r="I148" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="M148" s="55">
         <v>3</v>
@@ -19325,29 +19308,29 @@
         <v>2.530331596799999E-3</v>
       </c>
       <c r="R148" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="149" spans="4:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="150" spans="4:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D150" s="105" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="151" spans="4:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D151" s="104" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="152" spans="4:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D152" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="E152" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="E152" s="54" t="s">
+      <c r="F152" s="54" t="s">
         <v>150</v>
-      </c>
-      <c r="F152" s="54" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="153" spans="4:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -19364,56 +19347,56 @@
         <v>100</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="154" spans="4:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="155" spans="4:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D155" s="105" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="M155" s="105" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="156" spans="4:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D156" s="104" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M156" s="104" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="157" spans="4:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D157" s="54" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E157" s="54" t="s">
         <v>68</v>
       </c>
       <c r="F157" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="G157" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="G157" s="54" t="s">
+      <c r="H157" s="54" t="s">
         <v>150</v>
       </c>
-      <c r="H157" s="54" t="s">
-        <v>151</v>
-      </c>
       <c r="M157" s="54" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N157" s="54" t="s">
         <v>68</v>
       </c>
       <c r="O157" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="P157" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="P157" s="54" t="s">
+      <c r="Q157" s="54" t="s">
         <v>150</v>
-      </c>
-      <c r="Q157" s="54" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="158" spans="4:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -19612,7 +19595,7 @@
     <row r="163" spans="4:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="164" spans="4:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D164" s="110" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="E164" s="111">
         <f>SUM(F158:H161)</f>
@@ -19623,7 +19606,7 @@
         <v>t CH4</v>
       </c>
       <c r="M164" s="110" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="N164" s="111">
         <f>SUM(O158:Q161)</f>
@@ -19695,7 +19678,7 @@
     </row>
     <row r="169" spans="4:18" ht="18.75" x14ac:dyDescent="0.25">
       <c r="D169" s="48" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="E169" s="48" cm="1">
         <f t="array" ref="E169">Common_Equations.Common_ConvertCH4ToCO2e(G166,G167)</f>
@@ -19706,7 +19689,7 @@
         <v>t CO2e</v>
       </c>
       <c r="M169" s="48" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="N169" s="48" cm="1">
         <f t="array" ref="N169">Common_Equations.Common_ConvertCH4ToCO2e(P166,P167)</f>
@@ -19748,7 +19731,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
     </row>
     <row r="2" spans="1:17" s="9" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -19759,7 +19742,7 @@
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
@@ -19768,7 +19751,7 @@
       <c r="I3" s="4"/>
       <c r="K3" s="4"/>
       <c r="L3" s="4" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="M3" s="4"/>
       <c r="N3" s="4"/>
@@ -19804,7 +19787,7 @@
         <v>Site</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E7" s="13" t="str" cm="1">
         <f t="array" aca="1" ref="E7" ca="1">Common_InputFunctions.Utility_DisplayFunctionName(D30)</f>
@@ -19910,10 +19893,10 @@
         <v>Constants - Feedlot</v>
       </c>
       <c r="D17" s="105" t="s">
+        <v>160</v>
+      </c>
+      <c r="L17" s="105" t="s">
         <v>163</v>
-      </c>
-      <c r="L17" s="105" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="18" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -19922,10 +19905,10 @@
         <v>Constants - Livestock</v>
       </c>
       <c r="D18" s="104" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="L18" s="104" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="19" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -19934,22 +19917,22 @@
         <v>Constants - Common</v>
       </c>
       <c r="D19" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="E19" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="E19" s="54" t="s">
+      <c r="F19" s="54" t="s">
         <v>150</v>
       </c>
-      <c r="F19" s="54" t="s">
-        <v>151</v>
-      </c>
       <c r="L19" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="M19" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="M19" s="54" t="s">
+      <c r="N19" s="54" t="s">
         <v>150</v>
-      </c>
-      <c r="N19" s="54" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="20" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -19993,38 +19976,38 @@
     <row r="21" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="22" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D22" s="105" t="s">
+        <v>161</v>
+      </c>
+      <c r="L22" s="105" t="s">
         <v>164</v>
-      </c>
-      <c r="L22" s="105" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="23" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D23" s="104" t="s">
+        <v>207</v>
+      </c>
+      <c r="L23" s="104" t="s">
         <v>210</v>
-      </c>
-      <c r="L23" s="104" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="24" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D24" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="E24" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="E24" s="54" t="s">
+      <c r="F24" s="54" t="s">
         <v>150</v>
       </c>
-      <c r="F24" s="54" t="s">
-        <v>151</v>
-      </c>
       <c r="L24" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="M24" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="M24" s="54" t="s">
+      <c r="N24" s="54" t="s">
         <v>150</v>
-      </c>
-      <c r="N24" s="54" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="25" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20064,38 +20047,38 @@
     <row r="26" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="27" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D27" s="105" t="s">
+        <v>162</v>
+      </c>
+      <c r="L27" s="105" t="s">
         <v>165</v>
-      </c>
-      <c r="L27" s="105" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="28" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D28" s="104" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="L28" s="104" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="29" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D29" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="E29" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="E29" s="54" t="s">
+      <c r="F29" s="54" t="s">
         <v>150</v>
       </c>
-      <c r="F29" s="54" t="s">
-        <v>151</v>
-      </c>
       <c r="L29" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="M29" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="M29" s="54" t="s">
+      <c r="N29" s="54" t="s">
         <v>150</v>
-      </c>
-      <c r="N29" s="54" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="30" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20227,44 +20210,44 @@
     <row r="45" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="46" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D46" s="105" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E46" s="117" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="L46" s="105" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="M46" s="117" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
     </row>
     <row r="47" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D47" s="104" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="L47" s="104" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="48" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D48" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="E48" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="E48" s="54" t="s">
+      <c r="F48" s="54" t="s">
         <v>150</v>
       </c>
-      <c r="F48" s="54" t="s">
-        <v>151</v>
-      </c>
       <c r="L48" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="M48" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="M48" s="54" t="s">
+      <c r="N48" s="54" t="s">
         <v>150</v>
-      </c>
-      <c r="N48" s="54" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="49" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20281,7 +20264,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="H49" s="2"/>
       <c r="L49" s="55">
@@ -20304,38 +20287,38 @@
     <row r="50" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="51" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D51" s="105" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="L51" s="105" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="52" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D52" s="104" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="L52" s="104" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="53" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D53" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="E53" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="E53" s="54" t="s">
+      <c r="F53" s="54" t="s">
         <v>150</v>
       </c>
-      <c r="F53" s="54" t="s">
-        <v>151</v>
-      </c>
       <c r="L53" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="M53" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="M53" s="54" t="s">
+      <c r="N53" s="54" t="s">
         <v>150</v>
-      </c>
-      <c r="N53" s="54" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="54" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20479,23 +20462,23 @@
     <row r="69" spans="4:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="70" spans="4:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D70" s="105" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="71" spans="4:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D71" s="104" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="72" spans="4:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D72" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="E72" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="E72" s="54" t="s">
+      <c r="F72" s="54" t="s">
         <v>150</v>
-      </c>
-      <c r="F72" s="54" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="73" spans="4:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20512,30 +20495,30 @@
         <v>100</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H73" s="2"/>
     </row>
     <row r="74" spans="4:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="75" spans="4:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D75" s="105" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="76" spans="4:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D76" s="104" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="77" spans="4:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D77" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="E77" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="E77" s="54" t="s">
+      <c r="F77" s="54" t="s">
         <v>150</v>
-      </c>
-      <c r="F77" s="54" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="78" spans="4:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20559,38 +20542,38 @@
     <row r="79" spans="4:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="80" spans="4:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D80" s="105" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L80" s="105" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="81" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D81" s="104" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="L81" s="104" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="82" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D82" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="E82" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="E82" s="54" t="s">
+      <c r="F82" s="54" t="s">
         <v>150</v>
       </c>
-      <c r="F82" s="54" t="s">
-        <v>151</v>
-      </c>
       <c r="L82" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="M82" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="M82" s="54" t="s">
+      <c r="N82" s="54" t="s">
         <v>150</v>
-      </c>
-      <c r="N82" s="54" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="83" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20721,26 +20704,26 @@
     <row r="97" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="98" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D98" s="105" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
     <row r="99" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D99" s="104" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="100" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D100" s="54" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E100" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="F100" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="F100" s="54" t="s">
+      <c r="G100" s="54" t="s">
         <v>150</v>
-      </c>
-      <c r="G100" s="54" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="101" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20767,44 +20750,44 @@
     <row r="102" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="103" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D103" s="105" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="L103" s="105" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
     </row>
     <row r="104" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D104" s="104" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="L104" s="104" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="105" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D105" s="54" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E105" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="F105" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="F105" s="54" t="s">
+      <c r="G105" s="54" t="s">
         <v>150</v>
       </c>
-      <c r="G105" s="54" t="s">
-        <v>151</v>
-      </c>
       <c r="L105" s="54" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M105" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="N105" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="N105" s="54" t="s">
+      <c r="O105" s="54" t="s">
         <v>150</v>
-      </c>
-      <c r="O105" s="54" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="106" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20941,26 +20924,26 @@
     <row r="120" spans="4:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="121" spans="4:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D121" s="105" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
     </row>
     <row r="122" spans="4:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D122" s="104" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
     </row>
     <row r="123" spans="4:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D123" s="54" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E123" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="F123" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="F123" s="54" t="s">
+      <c r="G123" s="54" t="s">
         <v>150</v>
-      </c>
-      <c r="G123" s="54" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="124" spans="4:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20987,44 +20970,44 @@
     <row r="125" spans="4:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="126" spans="4:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D126" s="105" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="L126" s="105" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="127" spans="4:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D127" s="104" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="L127" s="104" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="128" spans="4:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D128" s="54" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E128" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="F128" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="F128" s="54" t="s">
+      <c r="G128" s="54" t="s">
         <v>150</v>
       </c>
-      <c r="G128" s="54" t="s">
-        <v>151</v>
-      </c>
       <c r="L128" s="54" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M128" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="N128" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="N128" s="54" t="s">
+      <c r="O128" s="54" t="s">
         <v>150</v>
-      </c>
-      <c r="O128" s="54" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="129" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21187,38 +21170,38 @@
     <row r="145" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="146" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D146" s="105" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="L146" s="105" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="147" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D147" s="104" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="L147" s="104" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="148" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D148" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="E148" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="E148" s="54" t="s">
+      <c r="F148" s="54" t="s">
         <v>150</v>
       </c>
-      <c r="F148" s="54" t="s">
-        <v>151</v>
-      </c>
       <c r="L148" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="M148" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="M148" s="54" t="s">
+      <c r="N148" s="54" t="s">
         <v>150</v>
-      </c>
-      <c r="N148" s="54" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="149" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21349,13 +21332,13 @@
     </row>
     <row r="164" spans="4:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D164" s="105" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="I164" s="2"/>
     </row>
     <row r="165" spans="4:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D165" s="104" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="166" spans="4:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21363,13 +21346,13 @@
         <v>105</v>
       </c>
       <c r="E166" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="F166" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="F166" s="54" t="s">
+      <c r="G166" s="54" t="s">
         <v>150</v>
-      </c>
-      <c r="G166" s="54" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="167" spans="4:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21417,18 +21400,18 @@
     <row r="169" spans="4:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="170" spans="4:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D170" s="105" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="L170" s="105" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="171" spans="4:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D171" s="104" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="L171" s="104" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="172" spans="4:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21436,25 +21419,25 @@
         <v>105</v>
       </c>
       <c r="E172" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="F172" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="F172" s="54" t="s">
+      <c r="G172" s="54" t="s">
         <v>150</v>
-      </c>
-      <c r="G172" s="54" t="s">
-        <v>151</v>
       </c>
       <c r="L172" s="54" t="s">
         <v>105</v>
       </c>
       <c r="M172" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="N172" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="N172" s="54" t="s">
+      <c r="O172" s="54" t="s">
         <v>150</v>
-      </c>
-      <c r="O172" s="54" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="173" spans="4:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21650,12 +21633,12 @@
     <row r="190" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="191" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D191" s="105" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
     </row>
     <row r="192" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D192" s="104" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
     </row>
     <row r="193" spans="4:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21663,7 +21646,7 @@
         <v>68</v>
       </c>
       <c r="E193" s="121" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="194" spans="4:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21709,18 +21692,18 @@
     <row r="198" spans="4:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="199" spans="4:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D199" s="105" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="L199" s="105" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
     </row>
     <row r="200" spans="4:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D200" s="104" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="L200" s="104" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="201" spans="4:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21728,25 +21711,25 @@
         <v>68</v>
       </c>
       <c r="E201" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="F201" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="F201" s="54" t="s">
+      <c r="G201" s="54" t="s">
         <v>150</v>
-      </c>
-      <c r="G201" s="54" t="s">
-        <v>151</v>
       </c>
       <c r="L201" s="121" t="s">
         <v>68</v>
       </c>
       <c r="M201" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="N201" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="N201" s="54" t="s">
+      <c r="O201" s="54" t="s">
         <v>150</v>
-      </c>
-      <c r="O201" s="54" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="202" spans="4:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21920,7 +21903,7 @@
     <row r="206" spans="4:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="207" spans="4:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D207" s="110" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E207" s="111">
         <f>SUM(E202:G205)</f>
@@ -21931,7 +21914,7 @@
         <v>t N2O</v>
       </c>
       <c r="L207" s="110" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="M207" s="111">
         <f>SUM(M202:O205)</f>
@@ -21996,7 +21979,7 @@
     <row r="211" spans="4:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="212" spans="4:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D212" s="48" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E212" s="48" cm="1">
         <f t="array" ref="E212">Common_Equations.Common_ConvertN2OToCO2e(G209,G210)</f>
@@ -22007,7 +21990,7 @@
         <v>t CO2e</v>
       </c>
       <c r="L212" s="48" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M212" s="48" cm="1">
         <f t="array" ref="M212">Common_Equations.Common_ConvertN2OToCO2e(O209,O210)</f>
@@ -22053,7 +22036,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
     </row>
     <row r="2" spans="1:17" s="9" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -22064,7 +22047,7 @@
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
@@ -22073,7 +22056,7 @@
       <c r="I3" s="4"/>
       <c r="K3" s="4"/>
       <c r="L3" s="4" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="M3" s="4"/>
       <c r="N3" s="4"/>
@@ -22204,10 +22187,10 @@
         <v>Constants - Feedlot</v>
       </c>
       <c r="D17" s="105" t="s">
+        <v>296</v>
+      </c>
+      <c r="L17" s="105" t="s">
         <v>299</v>
-      </c>
-      <c r="L17" s="105" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="18" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22216,10 +22199,10 @@
         <v>Constants - Livestock</v>
       </c>
       <c r="D18" s="104" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="L18" s="104" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
     </row>
     <row r="19" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22231,25 +22214,25 @@
         <v>68</v>
       </c>
       <c r="E19" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="F19" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="F19" s="54" t="s">
+      <c r="G19" s="54" t="s">
         <v>150</v>
-      </c>
-      <c r="G19" s="54" t="s">
-        <v>151</v>
       </c>
       <c r="L19" s="121" t="s">
         <v>68</v>
       </c>
       <c r="M19" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="N19" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="N19" s="54" t="s">
+      <c r="O19" s="54" t="s">
         <v>150</v>
-      </c>
-      <c r="O19" s="54" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="20" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22274,7 +22257,7 @@
         <v>3660.4799999999991</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="L20" s="55" t="str">
         <f>'Input - Feedlot'!$D$29</f>
@@ -22293,7 +22276,7 @@
         <v>3660.4799999999991</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
     <row r="21" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22314,7 +22297,7 @@
         <v>274.24316159999995</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="L21" s="55" t="str">
         <f>'Input - Feedlot'!$D$35</f>
@@ -22333,7 +22316,7 @@
         <v>274.24316159999995</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
     <row r="22" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22354,7 +22337,7 @@
         <v>1096.9726463999998</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="L22" s="55" t="str">
         <f>'Input - Feedlot'!$D$36</f>
@@ -22373,7 +22356,7 @@
         <v>1096.9726463999998</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
     <row r="23" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22394,7 +22377,7 @@
         <v>73.20959999999998</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="L23" s="55" t="str">
         <f>'Input - Feedlot'!$D$41</f>
@@ -22413,18 +22396,18 @@
         <v>73.20959999999998</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
     <row r="24" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="25" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D25" s="105" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
     </row>
     <row r="26" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D26" s="104" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="27" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22432,7 +22415,7 @@
         <v>68</v>
       </c>
       <c r="E27" s="121" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="28" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22445,7 +22428,7 @@
         <v>0.6</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="29" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22458,7 +22441,7 @@
         <v>0.25</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="30" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22471,7 +22454,7 @@
         <v>0.4</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="31" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22484,24 +22467,24 @@
         <v>0.35</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="32" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="33" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D33" s="105" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="L33" s="105" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
     </row>
     <row r="34" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D34" s="104" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="L34" s="104" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
     </row>
     <row r="35" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22509,25 +22492,25 @@
         <v>68</v>
       </c>
       <c r="E35" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="F35" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="F35" s="54" t="s">
+      <c r="G35" s="54" t="s">
         <v>150</v>
-      </c>
-      <c r="G35" s="54" t="s">
-        <v>151</v>
       </c>
       <c r="L35" s="121" t="s">
         <v>68</v>
       </c>
       <c r="M35" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="N35" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="N35" s="54" t="s">
+      <c r="O35" s="54" t="s">
         <v>150</v>
-      </c>
-      <c r="O35" s="54" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="36" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22568,7 +22551,7 @@
         <v>2196.2879999999996</v>
       </c>
       <c r="P36" s="2" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
     <row r="37" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22609,7 +22592,7 @@
         <v>68.560790399999988</v>
       </c>
       <c r="P37" s="2" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
     <row r="38" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22650,7 +22633,7 @@
         <v>438.78905855999994</v>
       </c>
       <c r="P38" s="2" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
     <row r="39" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22691,13 +22674,13 @@
         <v>25.623359999999991</v>
       </c>
       <c r="P39" s="2" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
     <row r="40" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="41" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D41" s="131" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="E41" s="48">
         <f>SUM(E36:G39)</f>
@@ -22708,7 +22691,7 @@
         <v>kg N</v>
       </c>
       <c r="L41" s="131" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="M41" s="48">
         <f>SUM(M36:O39)</f>
@@ -22820,7 +22803,7 @@
         <v>1.8E-3</v>
       </c>
       <c r="H54" s="117" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="L54" s="60" t="str">
         <v>EF_N2O</v>
@@ -22867,7 +22850,7 @@
       </c>
       <c r="F56" s="62"/>
       <c r="G56" s="60" t="str">
-        <f>'Input - Feedlot'!$E$63</f>
+        <f>'Input - Feedlot'!$E$62</f>
         <v>Pasture</v>
       </c>
       <c r="L56" s="60" t="str">
@@ -22878,7 +22861,7 @@
       </c>
       <c r="N56" s="62"/>
       <c r="O56" s="60" t="str">
-        <f>'Input - Feedlot'!$E$63</f>
+        <f>'Input - Feedlot'!$E$62</f>
         <v>Pasture</v>
       </c>
     </row>
@@ -22891,7 +22874,7 @@
       </c>
       <c r="F57" s="62"/>
       <c r="G57" s="60" t="str">
-        <f>'Input - Feedlot'!$E$64</f>
+        <f>'Input - Feedlot'!$E$63</f>
         <v>Not irrigated</v>
       </c>
       <c r="L57" s="60" t="str">
@@ -22902,7 +22885,7 @@
       </c>
       <c r="N57" s="62"/>
       <c r="O57" s="60" t="str">
-        <f>'Input - Feedlot'!$E$64</f>
+        <f>'Input - Feedlot'!$E$63</f>
         <v>Not irrigated</v>
       </c>
     </row>
@@ -22933,7 +22916,7 @@
     <row r="59" spans="4:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="60" spans="4:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D60" s="110" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="E60" s="111" cm="1">
         <f t="array" ref="E60">MMS_Feedlot_AtmosphericDeposition_Equations.VEERG_4_1_1_5__1_TotalAnnualAtmosphericDepositionEmissions(G53,G54,G55)</f>
@@ -22944,7 +22927,7 @@
         <v>t N2O</v>
       </c>
       <c r="L60" s="110" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="M60" s="111" cm="1">
         <f t="array" ref="M60">MMS_Feedlot_AtmosphericDeposition_Equations.VEERG_4_1_1_5__1_TotalAnnualAtmosphericDepositionEmissions(O53,O54,O55)</f>
@@ -23009,7 +22992,7 @@
     <row r="64" spans="4:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="65" spans="4:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D65" s="48" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E65" s="48" cm="1">
         <f t="array" ref="E65">Common_Equations.Common_ConvertN2OToCO2e(G62,G63)</f>
@@ -23020,7 +23003,7 @@
         <v>t CO2e</v>
       </c>
       <c r="L65" s="48" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M65" s="48" cm="1">
         <f t="array" ref="M65">Common_Equations.Common_ConvertN2OToCO2e(O62,O63)</f>
@@ -23158,7 +23141,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
     </row>
     <row r="2" spans="1:17" s="9" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -23169,7 +23152,7 @@
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
@@ -23178,7 +23161,7 @@
       <c r="I3" s="4"/>
       <c r="K3" s="4"/>
       <c r="L3" s="4" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="M3" s="4"/>
       <c r="N3" s="4"/>
@@ -23348,10 +23331,10 @@
         <v>Constants - Common</v>
       </c>
       <c r="D19" s="105" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="L19" s="105" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="20" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23360,10 +23343,10 @@
         <v>Acknowledgements</v>
       </c>
       <c r="D20" s="104" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="L20" s="104" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
     </row>
     <row r="21" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23371,25 +23354,25 @@
         <v>68</v>
       </c>
       <c r="E21" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="F21" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="F21" s="54" t="s">
+      <c r="G21" s="54" t="s">
         <v>150</v>
-      </c>
-      <c r="G21" s="54" t="s">
-        <v>151</v>
       </c>
       <c r="L21" s="54" t="s">
         <v>68</v>
       </c>
       <c r="M21" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="N21" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="N21" s="54" t="s">
+      <c r="O21" s="54" t="s">
         <v>150</v>
-      </c>
-      <c r="O21" s="54" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="22" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23410,7 +23393,7 @@
         <v>274.24316159999995</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="L22" s="55" t="str">
         <f>'Input - Feedlot'!$D$35</f>
@@ -23429,7 +23412,7 @@
         <v>274.24316159999995</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
     <row r="23" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23450,7 +23433,7 @@
         <v>1096.9726463999998</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="L23" s="55" t="str">
         <f>'Input - Feedlot'!$D$36</f>
@@ -23469,7 +23452,7 @@
         <v>1096.9726463999998</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
     <row r="24" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23490,7 +23473,7 @@
         <v>73.20959999999998</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="L24" s="55" t="str">
         <f>'Input - Feedlot'!$D$41</f>
@@ -23509,18 +23492,18 @@
         <v>73.20959999999998</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
     <row r="25" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="26" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D26" s="105" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
     </row>
     <row r="27" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D27" s="104" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
     </row>
     <row r="28" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23528,7 +23511,7 @@
         <v>68</v>
       </c>
       <c r="E28" s="121" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="29" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23541,7 +23524,7 @@
         <v>5.4000000000000003E-3</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="30" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23554,7 +23537,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="31" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23567,7 +23550,7 @@
         <v>0.01</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="32" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23580,18 +23563,18 @@
         <v>0</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="33" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="34" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D34" s="105" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
     </row>
     <row r="35" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D35" s="104" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="36" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23599,7 +23582,7 @@
         <v>68</v>
       </c>
       <c r="E36" s="121" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="37" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23612,7 +23595,7 @@
         <v>0.6</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="38" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23625,7 +23608,7 @@
         <v>0.25</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="39" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23638,7 +23621,7 @@
         <v>0.4</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="40" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23651,18 +23634,18 @@
         <v>0.35</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="41" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="42" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D42" s="105" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
     </row>
     <row r="43" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D43" s="104" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="44" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23670,13 +23653,13 @@
         <v>68</v>
       </c>
       <c r="E44" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="F44" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="F44" s="54" t="s">
+      <c r="G44" s="54" t="s">
         <v>150</v>
-      </c>
-      <c r="G44" s="54" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="45" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23745,18 +23728,18 @@
     <row r="48" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="49" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D49" s="105" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="L49" s="105" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="50" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D50" s="104" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="L50" s="104" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="51" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23764,25 +23747,25 @@
         <v>68</v>
       </c>
       <c r="E51" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="F51" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="F51" s="54" t="s">
+      <c r="G51" s="54" t="s">
         <v>150</v>
-      </c>
-      <c r="G51" s="54" t="s">
-        <v>151</v>
       </c>
       <c r="L51" s="54" t="s">
         <v>68</v>
       </c>
       <c r="M51" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="N51" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="N51" s="54" t="s">
+      <c r="O51" s="54" t="s">
         <v>150</v>
-      </c>
-      <c r="O51" s="54" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="52" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23914,7 +23897,7 @@
     <row r="55" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="56" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D56" s="110" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="E56" s="111">
         <f>SUM(E52:G54)</f>
@@ -23925,7 +23908,7 @@
         <v>kg N</v>
       </c>
       <c r="L56" s="110" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="M56" s="111">
         <f>SUM(M52:O54)</f>
@@ -24059,18 +24042,18 @@
     <row r="73" spans="4:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="74" spans="4:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D74" s="105" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="L74" s="105" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="75" spans="4:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D75" s="104" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="L75" s="104" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
     </row>
     <row r="76" spans="4:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -24078,25 +24061,25 @@
         <v>68</v>
       </c>
       <c r="E76" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="F76" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="F76" s="54" t="s">
+      <c r="G76" s="54" t="s">
         <v>150</v>
-      </c>
-      <c r="G76" s="54" t="s">
-        <v>151</v>
       </c>
       <c r="L76" s="54" t="s">
         <v>68</v>
       </c>
       <c r="M76" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="N76" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="N76" s="54" t="s">
+      <c r="O76" s="54" t="s">
         <v>150</v>
-      </c>
-      <c r="O76" s="54" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="77" spans="4:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -24228,7 +24211,7 @@
     <row r="80" spans="4:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="81" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D81" s="110" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="E81" s="111">
         <f>SUM(E77:G79)</f>
@@ -24239,7 +24222,7 @@
         <v>kg N</v>
       </c>
       <c r="L81" s="110" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="M81" s="111">
         <f>SUM(M77:O79)</f>
@@ -24281,7 +24264,7 @@
     </row>
     <row r="86" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D86" s="124" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="E86" s="122"/>
       <c r="F86" s="122"/>
@@ -24290,7 +24273,7 @@
     </row>
     <row r="87" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D87" s="97" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="E87" s="94"/>
       <c r="F87" s="94"/>
@@ -24300,17 +24283,17 @@
     <row r="88" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="89" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D89" s="6" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="90" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D90" s="105" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
     </row>
     <row r="91" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D91" s="104" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="92" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -24318,13 +24301,13 @@
         <v>68</v>
       </c>
       <c r="E92" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="F92" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="F92" s="54" t="s">
+      <c r="G92" s="54" t="s">
         <v>150</v>
-      </c>
-      <c r="G92" s="54" t="s">
-        <v>151</v>
       </c>
       <c r="H92" s="48"/>
     </row>
@@ -24394,18 +24377,18 @@
     <row r="96" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="97" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D97" s="105" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="L97" s="105" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
     </row>
     <row r="98" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D98" s="104" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="L98" s="104" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
     </row>
     <row r="99" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -24413,25 +24396,25 @@
         <v>68</v>
       </c>
       <c r="E99" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="F99" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="F99" s="54" t="s">
+      <c r="G99" s="54" t="s">
         <v>150</v>
-      </c>
-      <c r="G99" s="54" t="s">
-        <v>151</v>
       </c>
       <c r="L99" s="54" t="s">
         <v>68</v>
       </c>
       <c r="M99" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="N99" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="N99" s="54" t="s">
+      <c r="O99" s="54" t="s">
         <v>150</v>
-      </c>
-      <c r="O99" s="54" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="100" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -24563,7 +24546,7 @@
     <row r="103" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="104" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D104" s="110" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="E104" s="111">
         <f>SUM(E100:G102)</f>
@@ -24574,7 +24557,7 @@
         <v>kg N</v>
       </c>
       <c r="L104" s="110" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="M104" s="111">
         <f>SUM(M100:O102)</f>
@@ -24605,17 +24588,17 @@
     </row>
     <row r="108" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D108" s="6" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="109" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D109" s="105" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="110" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D110" s="104" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="111" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -24623,13 +24606,13 @@
         <v>68</v>
       </c>
       <c r="E111" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="F111" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="F111" s="54" t="s">
+      <c r="G111" s="54" t="s">
         <v>150</v>
-      </c>
-      <c r="G111" s="54" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="112" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -24698,18 +24681,18 @@
     <row r="115" spans="4:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="116" spans="4:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D116" s="105" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="L116" s="105" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="117" spans="4:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D117" s="104" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="L117" s="104" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
     </row>
     <row r="118" spans="4:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -24717,25 +24700,25 @@
         <v>68</v>
       </c>
       <c r="E118" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="F118" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="F118" s="54" t="s">
+      <c r="G118" s="54" t="s">
         <v>150</v>
-      </c>
-      <c r="G118" s="54" t="s">
-        <v>151</v>
       </c>
       <c r="L118" s="54" t="s">
         <v>68</v>
       </c>
       <c r="M118" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="N118" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="N118" s="54" t="s">
+      <c r="O118" s="54" t="s">
         <v>150</v>
-      </c>
-      <c r="O118" s="54" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="119" spans="4:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -24867,7 +24850,7 @@
     <row r="122" spans="4:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="123" spans="4:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D123" s="110" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="E123" s="111">
         <f>SUM(E119:G121)</f>
@@ -24878,7 +24861,7 @@
         <v>kg N</v>
       </c>
       <c r="L123" s="110" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="M123" s="111">
         <f>SUM(M119:O121)</f>
@@ -24956,7 +24939,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="2" spans="1:21" s="9" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25187,13 +25170,13 @@
     </row>
     <row r="25" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D25" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="M25" s="1"/>
     </row>
@@ -25208,10 +25191,10 @@
         <v>82</v>
       </c>
       <c r="G27" s="39" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="J27" s="39" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="M27" s="1"/>
     </row>
@@ -25229,7 +25212,7 @@
         <v>Production system only</v>
       </c>
       <c r="J28" s="39" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="M28" s="1"/>
     </row>
@@ -25247,7 +25230,7 @@
         <v>Pasture</v>
       </c>
       <c r="J29" s="39" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="M29" s="1"/>
     </row>
@@ -25261,7 +25244,7 @@
         <v>Composting (passive windrow) (m=6)</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="M30" s="1"/>
     </row>
@@ -25275,7 +25258,7 @@
         <v>Direct application (m=13)</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="M31" s="1"/>
     </row>
@@ -25289,17 +25272,11 @@
         <v>Anaerobic lagoon (m=1)</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="M32" s="1"/>
     </row>
     <row r="33" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D33" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="E33" s="39" t="s">
-        <v>108</v>
-      </c>
       <c r="M33" s="1"/>
     </row>
     <row r="34" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25324,10 +25301,10 @@
     </row>
     <row r="38" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D38" s="39" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E38" s="39" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="M38" s="1"/>
     </row>
@@ -25405,25 +25382,25 @@
     </row>
     <row r="49" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D49" s="39" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E49" s="39" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="F49" s="39" t="s">
         <v>20</v>
       </c>
       <c r="G49" s="39" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="H49" s="39" t="s">
+        <v>144</v>
+      </c>
+      <c r="I49" s="39" t="s">
         <v>145</v>
       </c>
-      <c r="I49" s="39" t="s">
+      <c r="J49" s="39" t="s">
         <v>146</v>
-      </c>
-      <c r="J49" s="39" t="s">
-        <v>147</v>
       </c>
       <c r="M49" s="24"/>
     </row>
@@ -25747,25 +25724,25 @@
     </row>
     <row r="66" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D66" s="39" t="s">
+        <v>142</v>
+      </c>
+      <c r="E66" s="39" t="s">
         <v>143</v>
-      </c>
-      <c r="E66" s="39" t="s">
-        <v>144</v>
       </c>
       <c r="F66" s="39" t="s">
         <v>20</v>
       </c>
       <c r="G66" s="39" t="s">
+        <v>144</v>
+      </c>
+      <c r="H66" s="39" t="s">
         <v>145</v>
       </c>
-      <c r="H66" s="39" t="s">
+      <c r="I66" s="39" t="s">
         <v>146</v>
       </c>
-      <c r="I66" s="39" t="s">
-        <v>147</v>
-      </c>
       <c r="J66" s="39" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="M66" s="24"/>
     </row>
@@ -26191,10 +26168,10 @@
     </row>
     <row r="88" spans="4:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D88" s="39" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E88" s="39" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F88" s="39" t="s">
         <v>84</v>
@@ -26489,13 +26466,13 @@
     </row>
     <row r="100" spans="4:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D100" s="39" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E100" s="39" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F100" s="39" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="G100" s="39" t="s">
         <v>100</v>
@@ -26635,13 +26612,13 @@
     </row>
     <row r="112" spans="4:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D112" s="116" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E112" s="116" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F112" s="116" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="G112" s="116" t="s">
         <v>100</v>
@@ -27276,15 +27253,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACB660BB23738846A00119B5826AC974" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3e3613359d4ae7f6bda6c57be713f101">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7291119c-fce9-4911-96ae-b800be5dccd8" xmlns:ns3="09eef6d6-daa8-4301-8f9f-b1ec38079286" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="87491bfad7f11426ad96486e70428b3e" ns2:_="" ns3:_="">
     <xsd:import namespace="7291119c-fce9-4911-96ae-b800be5dccd8"/>
@@ -27479,7 +27447,20 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgACcARgByAHkAJwAgAHQAbwAgACcARAByAHkAJwAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA1ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBXAGUAdAAgAG8AcgAgAEQAcgB5ACAAWgBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAG4AdABhAG4AZQBcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIAB3AGUAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGgAaQBnAGgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGgAaQBnAGgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAdwBhAHIAbQAgAC8AIABjAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAvACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAIABhAG4AZAAgAGgAaQBnAGgAIAB0AGUAbQBwACAAYwBsAGEAcwBzAGUAcwAgAHQAbwAgAGEAYwBjAG8AbQBtAG8AZABhAHQAZQAgAGMAbABpAG0AYQB0AGUAIABzAGMAZQBuAGEAcgBpAG8AcwAgAGUAeABjAGwAdQBkAGUAZAAgAGIAeQAgAFYARQBFAFIARwAgAGMAcgBpAHQAZQByAGkAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGkAeABlAGQAIAB0AHkAcABvACAAaQBuACAATQBBAFQAIAB2AGEAbAB1AGUAIABmAG8AcgAgAHcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGMAaABhAG4AZwBlAGQAIAAxADAAIAB0AG8AIAAxADEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAbQBpAG4AIABhAG4AZAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAGYAbwByACAATQBBAFQALAAgAE0AQQBQACwAIABmAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByACwAIABlAGwAZQB2AGEAdABpAG8AbgAsACAATQBBAFAAOgBQAEUAVAAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQBzACAAZgByAG8AbQAgAHIAZQBhAGwAIABjAGwAaQBtAGEAdABlACAAZABhAHQAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAEEARgAgAGEAYwBjAGUAcAB0AHMAIAByAGEAaQBuAGYAYQBsAGwAIABhAHMAIABhACAAcAByAG8AeAB5ACAAZgBvAHIAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADEANgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAXAAiACwAIABcACIATQBBAFAAXAAiACwAIABcACIARgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgBcACIALAAgAFwAIgBFAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAEEAUAA6AFAARQBUAFwAIgAsACAAXAAiAE0AaQBuACAAdABlAG0AcABcACIALAAgAFwAIgBNAGEAeAAgAHQAZQBtAHAAXAAiACwAIABcACIATQBpAG4AIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIATQBhAHgAIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIATQBpAG4AIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AYQB4ACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGkAbgAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AYQB4ACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAG4AdABhAG4AZQBcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgA+ACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAPgAgADEAOAAgAEMAXAAiACwAIABcACIAPgAgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAyADAAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgA+ACAAMQAwADAAMAAgAG0AbQAgAC0AIABkIiAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADEAMAAwADAALgAwADAAMQAsACAAMgAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAD4AIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgA+ACAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgA+ACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdABlADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQQBUACAAPQAgAG0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFAAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABFAFQAIAA9ACAAcABvAHQAZQBuAHQAaQBhAGwAIABlAHYAYQBwAG8AdAByAGEAbgBzAHAAaQByAGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABNAEEAVAAgAG0AaQBuACAAYQBuAGQAIABNAEEAVAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAGUAZABpAGEAbgAgAEEAbgBuAHUAYQBsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAKABNAEEAVAApAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFQAXAAiACwAIABcACIATQBhAHgAIABNAEEAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIiAAMgA2ACAAQwBcACIALAAgADIANgAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIABcACIAMQA1ACAALQAgADIANQAgAEMAXAAiACwAIAAxADUALAAgADIANQAuADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIgADEANAAgAEMAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADQALgA5ADkAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAZQB4AHQAcgBhACAAUgBhAGkAbgBmAGEAbABsACAAbQBpAG4AIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGEAbABsACAAWgBvAG4AZQBcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgBcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGEAeABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAD4AIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAPgCjAygANdg43DXYR9wwACkAKwA12GDcNdhc3DXYVtw12FncIAA12GTcNdhO3DXYYdw12FLcNdhf3CAADiE12FzcNdhZ3DXYUdw12FbcNdhb3DXYVNwgADXYUNw12E7cNdhd3DXYTtw12FDcNdhW3DXYYdw12GbcXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAGQAbwBlAHMAIABuAG8AdAAgAG8AYwBjAHUAcgBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAZCKjAygANdg43DXYR9wwACkAKwA12GDcNdhc3DXYVtw12FncIAA12GTcNdhO3DXYYdw12FLcNdhf3CAADiE12FzcNdhZ3DXYUdw12FbcNdhb3DXYVNwgADXYUNw12E7cNdhd3DXYTtw12FDcNdhW3DXYYdw12GbcXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHMAIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBZAGUAcwAgAC0AIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AIAAtACAAbgBvAHQAIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABkAGEAdABhACAAcwBjAG8AcgBlAHMAIABmAG8AcgAgAHMAYwBvAHAAZQAgADMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAWABYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAYQB0AGEAIABzAG8AdQByAGMAZQBcACIALAAgAFwAIgBEAGEAdABhACAAcwBjAG8AcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAG4AdABlAHIAbgBhAHQAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAgAG8AcgAgAHIAZQBnAGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAAaQBuAHQAZQBuAHMAaQB0AHkAIABjAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgAGEAcABwAHIAbwB2AGUAZAAgAG0AZQB0AGgAbwBkAFwAIgAsACAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAGUAcgBpAGYAaQBlAGQAIABjAHIAZQBkAGUAbgB0AGkAYQBsACAAbQBhAHQAYwBoAGkAbgBnACAASQBTAE8AMQA0ADAANgA3AFwAIgAsACAANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuACAAIAAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgACcAQQBxAHUAYQBjAHUAbAB0AHUAcgBlACcAIAByAG8AdwAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAYQBzAHQAZQByAGkAcwBrAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgACcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQAnACwAIAAnAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAJwAgAGEAbgBkACAAJwBpAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAJwAgAGMAbwBsAHUAbQBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAdQBwAGwAaQBjAGEAdABlAGQAIAAnAG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlACcAIAByAG8AdwAgAHcAaQB0AGgAIABzAGEAbQBlACAARQBGACAAZgBvAHIAIABsAG8AdwAgAGEAbgBkACAAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQAgAGQAYQB0AGEAIAB0AGgAYQB0ACAAaQBzACAAYwBvAG0AbQBvAG4AIABhAGMAcgBvAHMAcwAgAGEAbABsACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlAHMAXABuAEUAeABjAGUAbAAgAG0AbwBkAHUAbABlACAAbgBhAG0AZQA6ACAAUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlADoAIABOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBcAG4ARgByAGEAYwBXAEUAVABNAE0AUwBpACAAPQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4AKABUAGEAYgBsAGUAIABBADUALgA1AC4AMQAwAC4AMgAgAGkAcwAgAHIAZQBmAGUAcgBlAG4AYwBlAGQAIABpAG4AIABOAEkAUgAgAGIAdQB0ACAAMQAgAGkAcwAgAHUAcwBlAGQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgA1AGEAXwAzACwAIAAzAC4AQgAuADUAYwBfADMALAAgADMALgBCAC4ANQBkAF8AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAxACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXABuAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTACAAPQAgADAALgAwADIAIAAoAEcAZwAgAE4ALwBHAGcAIABhAHAAcABsAGkAZQBkACkAIAAoAEMAUwAgAEUARgAsACAAcwBvAHUAcgBjAGUAIABJAFAAQwBDACAAKAAyADAAMQA5ACkAKQAgAFwAbgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgA1AGEAXwAzACwAIAAzAC4AQgAuADUAYwBfADMALAAgADMALgBCAC4ANQBkAF8AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAIAAwAC4AMAAwADUAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsACAAMAAuADAAMAA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAgADAALgAwADAAMQA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcABcACIALAAgADAALgAwADAANAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAIABjAGEAbgBlAFwAIgAsACAAMAAuADAAMQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAMAAuADAAMAA1ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAMAAuADAAMAA2ADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXABuAFQAYQBiAGwAZQAgADUALgAxADIAIABBAGQAZABpAHQAaQBvAG4AYQBsACAAcwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAHIAZQBsAGEAdABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgADUALgAxADIAIABBAGQAZABpAHQAaQBvAG4AYQBsACAAcwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAHIAZQBsAGEAdABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVgBhAGkAcgBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE0AUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAAVABhAGIAbABlACAANQAuADEAMgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAOQAsACAAMwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB5AG0AYgBvAGwAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0ACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgACgAbQA9ADEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADIAXAAiACwAIABcACIATABpAHEAdQBpAGQAIABzAHkAcwB0AGUAbQBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwAgACgAbQA9ADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADMAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAG0APQAzACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGEAXAAiACwAIABcACIAUwB1AG0AcAAgAGEAbgBkACAAZABpAHMAcABlAHIAcwBhAGwAIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBTAHUAbQBwACAAYQBuAGQAIABkAGkAcwBwAGUAcgBzAGEAbAAgAHMAeQBzAHQAZQBtACAAKABtAD0AMwBhACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGIAXAAiACwAIABcACIARAByAGEAaQBuAHMAIAB0AG8AIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAEQAcgBhAGkAbgBzACAAdABvACAAcABhAGQAZABvAGMAawAgACgAbQA9ADMAYgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIANABcACIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAIAAoAG0APQA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA1AFwAIgAsACAAXAAiAEQAcgB5AGwAbwB0ACAAKABmAGUAZQBkACAAcABhAGQAKQBcACIALAAgAFwAIgBEAHIAeQBsAG8AdAAgACgAZgBlAGUAZAAgAHAAYQBkACkAIAAoAG0APQA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA2AFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQAgACgAbQA9ADYAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADcAXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwAgACgAbQA9ADcAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADgAXAAiACwAIABcACIARABlAGUAcAAgAGwAaQB0AHQAZQByAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgAgACgAbQA9ADgAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADkAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQAgACgAbQA9ADkAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMABcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwAgACgAbQA9ADEAMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnACAAKABtAD0AMQAxACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADEAYQBcACIALAAgAFwAIgBCAGUAbAB0ACAAbQBhAG4AdQByAGUAIAByAGUAbQBvAHYAYQBsAFwAIgAsACAAXAAiAEIAZQBsAHQAIABtAGEAbgB1AHIAZQAgAHIAZQBtAG8AdgBhAGwAIAAoAG0APQAxADEAYQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAGIAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABzAHQAbwByAGUAZAAgAGkAbgAgAGgAbwB1AHMAZQBcACIALAAgAFwAIgBNAGEAbgB1AHIAZQAgAHMAdABvAHIAZQBkACAAaQBuACAAaABvAHUAcwBlACAAKABtAD0AMQAxAGIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAKABtAD0AMQAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADMAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAG0APQAxADMAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEANABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAIAAoAG0APQAxADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgA8AHQAPgA8AHMAPgBcACIAIAAmAFwAbgAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAUwBVAEIAUwBUAEkAVABVAFQARQAoAEMAZQBsAGwALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQAsAFwAIgBcACIAKQAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAZQBsAGkAbQBpAHQAZQByACwAXAAiADwALwBzAD4APABzAD4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgACYAXABuACAAIAAgACAAIAAgACAAIABcACIAPAAvAHMAPgA8AC8AdAA+AFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC8ALwBzAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQB2AGcAVABlAG0AcAAsAGEAdgBnAFIAYQBpAG4ALABmAHIAbwBzAHQARABhAHkAcwAsAGUAbABlAHYALABtAGEAcABfAHAAZQB0ACwAXABuACAAIAAgACAAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkALABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQAsAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBQAEUAVABBAHIAcgBhAHkALABtAGEAeABQAEUAVABBAHIAcgBhAHkALABcAG4AIAAgACAAIABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkAKQA8AD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPAA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAPAA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAD4APQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApADwAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAPgA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQA8AD0AbQBhAHAAXwBwAGUAdAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFAARQBUAEEAcgByAGEAeQApAD4APQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQA8AD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAPgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAEkAdABlAG0AQQByAHIAYQB5ACwAIABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAEMAcgBpAHQAZQByAGkAYQAxACwAIABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACwAIABbAE0AdQBsAHQAaQBwAGwAaQBlAHIAXQAsACAAWwBDAHIAaQB0AGUAcgBpAGEAMgBdACwAWwBDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAXQAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABtAHUAbAB0AGkAcABsAGkAZQByACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsADEALABNAHUAbAB0AGkAcABsAGkAZQByACkALABcAG4AIAAgACAAIABxAHUAYQBuAHQAaQB0AHkALAAgAFEAdQBhAG4AdABpAHQAeQAqAE0AdQBsAHQAaQBwAGwAaQBlAHIALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMQAsAC0ALQAoAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADEAKQAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAyACwASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABDAHIAaQB0AGUAcgBpAGEAMgApACwAMQAsAC0ALQAoAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAyACkAKQAsAFwAbgAgACAAIAAgAFMAVQBNAFAAUgBPAEQAVQBDAFQAKABjAHIAaQB0AGUAcgBpAGEAMQAqAGMAcgBpAHQAZQByAGkAYQAyACoAcQB1AGEAbgB0AGkAdAB5ACkAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQA8ACAAUwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAD4AIABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAE0AQQBYACgAMAAsAGwAYQBzAHQAWQBlAGEAcgAtAGYAaQByAHMAdABZAGUAYQByACsAMQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAIAAvACoAaABlAGwAcABlAHIAOgAgAGUAbgBkACAAZABhAHQAZQAgAGYAbwByACAAYQAgAHIAZQBwAG8AcgB0AGkAbgBnACAAcABlAHIAaQBvAGQAIABzAHQAYQByAHQAaQBuAGcAIABhAHQAIABhACAAZwBpAHYAZQBuACAAZABhAHQAZQAqAC8AXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALAAgAC8AKgBvAG4AbAB5ACAAbgBlAGUAZAAgAHQAbwAgAGwAbwBvAGsAIABiAGEAYwBrACAAMwA2ADUAIABkAGEAeQBzACgAbQBhAHgAIABvAHYAZQByAGwAYQBwACAAdwBpAG4AZABvAHcAKQAqAC8AXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBhACAAZQBuAGQAcwAgAGIAZQBmAG8AcgBlACAAUwAsAGkAdAAgAGMAYQBuACcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABuAGUAeAB0ACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApADwAUwApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBiACAAcwB0AGEAcgB0AHMAIABhAGYAdABlAHIAIABFACwAaQB0ACAAYwBhAG4AJwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAHAAcgBlAHYAaQBvAHUAcwAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQA+AEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbgAsAE0AQQBYACgAMAAsAGwAYQBzAHQAWQBlAGEAcgAtAGYAaQByAHMAdABZAGUAYQByACsAMQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AHIAcwAsAFMARQBRAFUARQBOAEMARQAoAG4ALAAxACwAZgBpAHIAcwB0AFkAZQBhAHIALAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzACwARABBAFQARQAoAHkAcgBzACwAbQAsAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBuAGQAcwAsAE0AQQBQACgAcwB0AGEAcgB0AHMALABQAGUAcgBpAG8AZABFAG4AZAApACwAXABuACAAIAAgACAAIAAgACAAIAB0AGEAZwAsAEkARgAoAHMAdABhAHIAdABzAD0AUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAIgAgACgAVABoAGkAcwAgAHIAZQBwAG8AcgB0AGkAbgBnACAAYwB5AGMAbABlACkAXAAiACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwBUAGUAeAB0ACwAVABFAFgAVAAoAHMAdABhAHIAdABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBuAGQAcwBUAGUAeAB0ACwAVABFAFgAVAAoAGUAbgBkAHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABuAD0AMAAsAFwAIgBcACIALABIAFMAVABBAEMASwAoAHMAdABhAHIAdABzAFQAZQB4AHQAIAAmACAAXAAiACAAdABvACAAXAAiACAAJgAgAGUAbgBkAHMAVABlAHgAdAAgACYAIAB0AGEAZwApACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuAD0ATABBAE0AQgBEAEEAKABGAHUAbgBjAHQAaQBvAG4ALAAgAFQARQBYAFQAQgBFAEYATwBSAEUAKABGAE8AUgBNAFUATABBAFQARQBYAFQAKABGAHUAbgBjAHQAaQBvAG4AKQAsACAAXAAiACgAXAAiACkAKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5ACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5ACwAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAPQBcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAgAD0AIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQA9AFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5AD0ASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5AD0AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAgACsAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQAPgAwACwAIAAxACwAIAAwACkAXABuACAAIAAgACAAKQApADsAXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AQwBhAGwAYwB1AGwAYQB0AGUASABhAHIAdgBlAHMAdABJAG4AZABlAHgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABDAHIAbwBwAFQAeQBwAGUALAAgAEMAcgBvAHAAVAB5AHAAZQBBAHIAcgBhAHkALAAgAFIAZQBzAGkAZAB1AGUAQwByAG8AcABSAGEAdABpAG8AQQByAHIAYQB5ACwAXABuACAAIAAgACAAMQAvACgAMQArAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAQwByAG8AcABUAHkAcABlACwAIABDAHIAbwBwAFQAeQBwAGUAQQByAHIAYQB5ACwAIABSAGUAcwBpAGQAdQBlAEMAcgBvAHAAUgBhAHQAaQBvAEEAcgByAGEAeQApACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEMAYQBsAGMAdQBsAGEAdABlAFIAZQBzAGkAZAB1AGUAQwByAG8AcABSAGEAdABpAG8AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABIAGEAcgB2AGUAcwB0AEkAbgBkAGUAeAAsAFwAbgAgACAAIAAgACgAMQAtAEgAYQByAHYAZQBzAHQASQBuAGQAZQB4ACkALwBIAGEAcgB2AGUAcwB0AEkAbgBkAGUAeABcAG4AKQA7AFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEMAYQBsAGMAdQBsAGEAdABlAEYAcgBhAGMAdABpAG8AbgBSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAG8AdABhAGwAUgBlAHMAaQBkAHUAZQAsACAAQQBtAG8AdQBuAHQAUgBlAG0AbwB2AGUAZAAsAFwAbgAgACAAIAAgACgAQQBtAG8AdQBuAHQAUgBlAG0AbwB2AGUAZAAqADEAMABeADMAKQAvACgAVABvAHQAYQBsAFIAZQBzAGkAZAB1AGUAKgAxADAAXgAzACkAXABuACkAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AVgBTAEwAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAbABvAHMAdAAgAGkAbgAgAHQAaABlACAAcAByAGkAbQBhAHIAeQAgAE0ATQBTAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AVgBTAEwAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAZQBlAGQAbABvAHQAIAAtACAARgByAGEAYwB0AGkAbwBuACAAbwBmACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIABsAG8AcwB0ACAAZAB1AHIAaQBuAGcAIABzAHQAbwByAGEAZwBlACAAaQBuACAAdABoAGUAIABwAHIAaQBtAGEAcgB5ACAAcwB5AHMAdABlAG0AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AVgBTAEwAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAUwBMAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFYAUwBMAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFYAUwBMAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAxAC4AMgAuADMAIABDAE8ATgBTAFQAQQBOAFQAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBWAFMATABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBWAFMATABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADUAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAE0AUwBtADEAVAAzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAHQAbwAgAGUAYQBjAGgAIAB0AGUAcgB0AGkAYQByAHkAIABzAHkAcwB0AGUAbQAgAGEAcwBzAHUAbQBlAGQAIAB0AGgAYQB0ACAAMgAgAHAAZQByACAAYwBlAG4AdAAgAGkAcwAgAHIAdQBuACAALQAgAG8AZgBmACAAZgByAG8AbQAgAHQAaABlACAAZgBlAGUAZAAgAHAAYQBkAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAE0AUwBtADEAVAAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAHQAbwAgAGUAYQBjAGgAIAB0AGUAcgB0AGkAYQByAHkAIABzAHkAcwB0AGUAbQAgAGEAcwBzAHUAbQBlAGQAIAB0AGgAYQB0ACAAMgAgAHAAZQByACAAYwBlAG4AdAAgAGkAcwAgAHIAdQBuACAALQAgAG8AZgBmACAAZgByAG8AbQAgAHQAaABlACAAZgBlAGUAZAAgAHAAYQBkAC4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBNAFMAbQAxAFQAMwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBNAFMAbQAxAFQAMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAE0AUwBtADEAVAAzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0ATQBTAG0AMQBUADMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADEALgAyAC4AMwAgAEMATwBOAFMAVABBAE4AVABTAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0ATQBTAG0AMQBUADMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBNAFMAbQAxAFQAMwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADAAMgApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXABuAEEAcwBoACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAG0AYQBuAHUAcgBlAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHMAaAAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABtAGEAbgB1AHIAZQAuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAxAC4AMgAuADMAIABDAE8ATgBTAFQAQQBOAFQAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADAALgAxADYAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAFwAbgBNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbAAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAcABvAHQAZQBuAHQAaQBhAGwALgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBCADAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAG0AMwAgAEMASAA0ACAALwAgAGsAZwAgAFYAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAxAC4AMgAuADMAIABDAE8ATgBTAFQAQQBOAFQAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADAALgAxADkAKQA7AFwAbgBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AUwB0AGEAZwBlADEATQBNAFMATwBwAHQAaQBvAG4AcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADEALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAbABvAHQAIAAoAGYAZQBlAGQAIABwAGEAZAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBTAHQAYQBnAGUAMgBNAE0AUwBPAHAAdABpAG8AbgBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAAMQAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAATQBNAFMAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFMAdABhAGcAZQAzAE0ATQBTAE8AcAB0AGkAbwBuAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAAxACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwBlAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAbwBtAGUAcwB0AGkAYwBcACIAOwAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAHgAcABvAHIAdAAgAG0AaQBkACAAZgBlAGQAXAAiADsAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQB4AHAAbwByAHQAIABsAG8AbgBnACAAZgBlAGQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4AMQAuADEAOgAgAEIAZQBlAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIAAtACAARAB1AHIAYQB0AGkAbwBuACAAbwBmACAAcwB0AGEAeQAgACgAZABhAHkAcwApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAEQAdQByAGEAdABpAG8AbgAgAG8AZgAgAHMAdABhAHkAIAAoAGQAYQB5AHMAKQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgAxAC4AMQA6ACAAQgBlAGUAZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAC0AIABEAHUAcgBhAHQAaQBvAG4AIABvAGYAIABzAHQAYQB5ACAAKABkAGEAeQBzACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAZQBkAGwAbwB0ACAAdAB5AHAAZQBcACIALAAgAFwAIgBMAGUAbgBnAHQAaAAgAG8AZgAgAFMAdABhAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAbwBtAGUAcwB0AGkAYwBcACIALAAgAFwAIgAxAC0AOAAwACAAZABhAHkAcwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBpAGQALQBmAGUAZABcACIALAAgAFwAIgA4ADEALQAyADAAMAAgAGQAYQB5AHMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAbwBuAGcALQBmAGUAZABcACIALAAgAFwAIgAyADAAMQArACAAZABhAHkAcwBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAG4AaQBtAGEAbABDAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwBcAG4AVABhAGIAbABlACAAQQAuADEALgAxAC4AMgA6ACAAQgBlAGUAZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAC0AIABBAG4AaQBtAGEAbAAgAGMAaABhAHIAYQBjAHQAZQByAGkAcwB0AGkAYwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBuAGkAbQBhAGwAQwBoAGEAcgBhAGMAdABlAHIAaQBzAHQAaQBjAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEIAZQBlAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIAAtACAAQQBuAGkAbQBhAGwAIABjAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAG4AaQBtAGEAbABDAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAbgBpAG0AYQBsAEMAaABhAHIAYQBjAHQAZQByAGkAcwB0AGkAYwBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AMQAuADIAOgAgAEIAZQBlAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIAAtACAAQQBuAGkAbQBhAGwAIABjAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAG4AaQBtAGEAbABDAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AdgBlAGQAIABmAGUAZQBkAGwAbwB0ACAAdAB5AHAAZQBzACAAdABvACAAYQAgAHMAZQBwAGEAcgBhAHQAZQAgAGMAbwBsAHUAbQBuACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAGEAbQBlAGQAIAAnAGMAaABhAHIAYQBjAHQAZQByAGkAcwB0AGkAYwAnACAAYwBvAGwAdQBtAG4AIAAtACAAbwByAGkAZwBpAG4AYQBsACAAaABhAHMAIABoAGUAYQBkAGUAcgAgACcAVQBuAGkAdAAnACAAdwBoAGkAYwBoACAAYwBvAHYAZQByAHMAIAB0AHcAbwAgAGMAbwBsAHUAbQBuAHMAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBuAGkAbQBhAGwAQwBoAGEAcgBhAGMAdABlAHIAaQBzAHQAaQBjAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAwACwAIAA3ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAZQBkAGwAbwB0ACAAdAB5AHAAZQBcACIALAAgAFwAIgBDAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAXAAiACwAIABcACIAVQBuAGkAdABcACIALAAgAFwAIgAyADAAMAA1AC0AMgAwADAAOQBcACIALAAgAFwAIgAyADAAMQAwAC0AMgAwADEANABcACIALAAgAFwAIgAyADAAMQA1AC0AMgAwADEAOQBcACIALAAgAFwAIgAyADAAMgAwAC0AMgAwADIAMwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABvAG0AZQBzAHQAaQBjAFwAIgAsACAAXAAiAEQAYQB5AHMAIABvAG4AIABmAGUAZQBkAFwAIgAsACAAXAAiAGQAYQB5AHMAXAAiACwAIAA3ADAALAAgADcAMAAsACAANwAwACwAIAA3ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABvAG0AZQBzAHQAaQBjAFwAIgAsACAAXAAiAEYAZQBlAGQAIABpAG4AdABhAGsAZQBcACIALAAgAFwAIgBrAGcAIABEAE0ALwBkAGEAeQBcACIALAAgADEAMAAuADAALAAgADEAMAAuADAALAAgADEAMAAuADQALAAgADEAMAAuADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABvAG0AZQBzAHQAaQBjAFwAIgAsACAAXAAiAE4AIAByAGUAdABlAG4AdABpAG8AbgBcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAIABvAGYAIABpAG4AdABhAGsAZQBcACIALAAgADIAMQAuADEALAAgADIAMAAuADQALAAgADIAMAAuADQALAAgADIAMAAuADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBpAGQALQBmAGUAZABcACIALAAgAFwAIgBEAGEAeQBzACAAbwBuACAAZgBlAGUAZABcACIALAAgAFwAIgBkAGEAeQBzAFwAIgAsACAAMQAxADUALAAgADEAMQA1ACwAIAAxADIAMAAsACAAMQA1ADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBpAGQALQBmAGUAZABcACIALAAgAFwAIgBGAGUAZQBkACAAaQBuAHQAYQBrAGUAXAAiACwAIABcACIAawBnACAARABNAC8AZABhAHkAXAAiACwAIAAxADEALgAyACwAIAAxADAALgA4ACwAIAAxADAALgA4ACwAIAAxADAALgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AaQBkAC0AZgBlAGQAXAAiACwAIABcACIATgAgAHIAZQB0AGUAbgB0AGkAbwBuAFwAIgAsACAAXAAiAHAAZQByACAAYwBlAG4AdAAgAG8AZgAgAGkAbgB0AGEAawBlAFwAIgAsACAAMQAyAC4ANQAsACAAMQAyAC4ANwAsACAAMQAyAC4ANwAsACAAMQAyAC4ANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AbgBnAC0AZgBlAGQAXAAiACwAIABcACIARABhAHkAcwAgAG8AbgAgAGYAZQBlAGQAXAAiACwAIABcACIAZABhAHkAcwBcACIALAAgADIANQAwACwAIAAyADUAMAAsACAAMgA1ADAALAAgADIANQAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAbwBuAGcALQBmAGUAZABcACIALAAgAFwAIgBGAGUAZQBkACAAaQBuAHQAYQBrAGUAXAAiACwAIABcACIAawBnACAARABNAC8AZABhAHkAXAAiACwAIAA5AC4AMAAsACAAOAAuADUALAAgADgALgAyACwAIAA4AC4AMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AbgBnAC0AZgBlAGQAXAAiACwAIABcACIATgAgAHIAZQB0AGUAbgB0AGkAbwBuAFwAIgAsACAAXAAiAHAAZQByACAAYwBlAG4AdAAgAG8AZgAgAGkAbgB0AGEAawBlAFwAIgAsACAANgAuADYALAAgADcALgAwACwAIAA3AC4AMAAsACAANwAuADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARABpAGUAdABQAHIAbwBwAGUAcgB0AGkAZQBzAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADEALgAzADoAIABCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAEQAaQBlAHQAIABwAHIAbwBwAGUAcgB0AGkAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARABpAGUAdABQAHIAbwBwAGUAcgB0AGkAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAEQAaQBlAHQAIABwAHIAbwBwAGUAcgB0AGkAZQBzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAaQBlAHQAUAByAG8AcABlAHIAdABpAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAaQBlAHQAUAByAG8AcABlAHIAdABpAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADEALgAzADoAIABCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAEQAaQBlAHQAIABwAHIAbwBwAGUAcgB0AGkAZQBzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAaQBlAHQAUAByAG8AcABlAHIAdABpAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAAnAEMAbwBuAHYAZQByAHQAZQBkACAAdABvACAAZgByAGEAYwB0AGkAbwBuACAAYwBvAGwAdQBtAG4AIABhAG4AZAAgAGMAbwBuAHYAZQByAHQAZQBkACAATgBEAEYAIABhAG4AZAAgAEUAdABoAGUAcgAgAGUAeAB0AHIAYQBjAHQAIAB2AGEAbAB1AGUAcwAgAHQAbwAgAGYAcgBhAGMAdABpAG8AbgBzAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AbwB2AGUAZAAgAGYAZQBlAGQAbABvAHQAIAB0AHkAcABlAHMAIAB0AG8AIABhACAAcwBlAHAAYQByAGEAdABlACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAaQBlAHQAUAByAG8AcABlAHIAdABpAGUAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADMALAAgADgALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBlAGQAbABvAHQAIAB0AHkAcABlAFwAIgAsACAAXAAiAE4AdQB0AHIAaQBlAG4AdAAgAGEAbgBhAGwAeQBzAGkAcwBcACIALAAgAFwAIgBVAG4AaQB0AFwAIgAsACAAXAAiADIAMAAwADUALQAyADAAMAA5AFwAIgAsACAAXAAiADIAMAAxADAALQAyADAAMQA0AFwAIgAsACAAXAAiADIAMAAxADUALQAyADAAMQA5AFwAIgAsACAAXAAiADIAMAAyADAALQAyADAAMgAzAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHQAZQBkACAAdABvACAAZgByAGEAYwB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAG8AbQBlAHMAdABpAGMAXAAiACwAIABcACIARAByAHkAIABtAGEAdAB0AGUAcgAgAGQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAMAAuADgAMQAsACAAMAAuADgAMQAsACAAMAAuADgAMQAsACAAMAAuADgAMQAsACAAMAAuADgAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAG8AbQBlAHMAdABpAGMAXAAiACwAIABcACIAQwByAHUAZABlACAAcAByAG8AdABlAGkAbgBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIAAwAC4AMQA0ACwAIAAwAC4AMQA0ACwAIAAwAC4AMQA0ACwAIAAwAC4AMQA0ACwAIAAwAC4AMQA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAbwBtAGUAcwB0AGkAYwBcACIALAAgAFwAIgBOAEQARgBcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAXAAiACwAIAAyADMALgAwACwAIAAyADIALgAwACwAIAAyADIALgAwACwAIAAyADIALgAwACwAIAAwAC4AMgAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAbwBtAGUAcwB0AGkAYwBcACIALAAgAFwAIgBFAHQAaABlAHIAIABFAHgAdAByAGEAYwB0AFwAIgAsACAAXAAiAHAAZQByACAAYwBlAG4AdABcACIALAAgADQALgA1ACwAIAA0AC4ANQAsACAANAAuADgALAAgADQALgA4ACwAIAAwAC4AMAA0ADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBpAGQALQBmAGUAZABcACIALAAgAFwAIgBEAHIAeQAgAG0AYQB0AHQAZQByACAAZABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIAAwAC4AOAAxACwAIAAwAC4AOAAxACwAIAAwAC4AOAAxACwAIAAwAC4AOAAxACwAIAAwAC4AOAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AaQBkAC0AZgBlAGQAXAAiACwAIABcACIAQwByAHUAZABlACAAcAByAG8AdABlAGkAbgBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIAAwAC4AMQAzACwAIAAwAC4AMQAyADUALAAgADAALgAxADIALAAgADAALgAxADIALAAgADAALgAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBpAGQALQBmAGUAZABcACIALAAgAFwAIgBOAEQARgBcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAXAAiACwAIAAyADQALgAwACwAIAAyADIALgAwACwAIAAyADIALgAwACwAIAAyADIALgAwACwAIAAwAC4AMgAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AaQBkAC0AZgBlAGQAXAAiACwAIABcACIARQB0AGgAZQByACAARQB4AHQAcgBhAGMAdABcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAXAAiACwAIAA1AC4AMAAsACAANQAuADAALAAgADUALgAwACwAIAA1AC4AMAAsACAAMAAuADAANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AbgBnAC0ARgBlAGQAXAAiACwAIABcACIARAByAHkAIABtAGEAdAB0AGUAcgAgAGQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAMAAuADgAMQAsACAAMAAuADgAMQAsACAAMAAuADgAMQAsACAAMAAuADgAMQAsACAAMAAuADgAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AbgBnAC0ARgBlAGQAXAAiACwAIABcACIAQwByAHUAZABlACAAcAByAG8AdABlAGkAbgBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIAAwAC4AMQAzACwAIAAwAC4AMQAyADUALAAgADAALgAxADIALAAgADAALgAxADIALAAgADAALgAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABvAG4AZwAtAEYAZQBkAFwAIgAsACAAXAAiAE4ARABGAFwAIgAsACAAXAAiAHAAZQByACAAYwBlAG4AdABcACIALAAgADIANAAuADAALAAgADIANAAuADAALAAgADIANAAuADAALAAgADIANAAuADAALAAgADAALgAyADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABvAG4AZwAtAEYAZQBkAFwAIgAsACAAXAAiAEUAdABoAGUAcgAgAEUAeAB0AHIAYQBjAHQAXAAiACwAIABcACIAcABlAHIAIABjAGUAbgB0AFwAIgAsACAANQAuADAALAAgADUALgAwACwAIAA1AC4ANQAsACAANQAuADUALAAgADAALgAwADUANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBDAEYAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4AMQAuADQAOgAgAEIAZQBlAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIAAtACAATQBDAEYAcwAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQBUACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAEMARgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBlAGUAZABsAG8AdAAgAC0AIABNAEMARgBzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AQwBGAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBDAEYAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgAxAC4ANAA6ACAAQgBlAGUAZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAC0AIABNAEMARgBzACAAKABmAHIAYQBjAHQAaQBvAG4AKQAgACgATQBDAEYAaQBtAFQAKQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAEMARgBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHUAcABsAGkAYwBhAHQAZQBkACAATgBTAFcAIAB2AGEAbAB1AGUAcwAgAGYAbwByACAAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAE4AVAAgAGEAbgBkACAAVABBAFMAIABjAG8AbAB1AG0AbgBzACAAdwBpAHQAaAAgACcAbgBvACAAZABhAHQAYQAnACAAdgBhAGwAdQBlAHMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgACcATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuACcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABNAE0AUwAgAG4AYQBtAGUAcwAgAHQAaABhAHQAIABtAGEAdABjAGgAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAEMARgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAxADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAVABcACIALAAgAFwAIgBNAE0AUwAgAG0AXAAiACwAIABcACIATgBTAFcAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAUQBMAEQAXAAiACwAIABcACIATgBUAFwAIgAsACAAXAAiAFMAQQBcACIALAAgAFwAIgBWAEkAQwBcACIALAAgAFwAIgBXAEEAXAAiACwAIABcACIAVABBAFMAXAAiACwAIABcACIATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAaQBtAGEAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAbABvAHQAIAAoAEYAZQBlAGQAcABhAGQAKQBcACIALAAgADAALgAwADEALAAgADAALgAwADEALAAgADAALgAwADMALAAgAFwAIgBOAG8AIABkAGEAdABhAFwAIgAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAXAAiAE4AbwAgAGQAYQB0AGEAXAAiACwAIABcACIARAByAHkAbABvAHQAIAAoAGYAZQBlAGQAIABwAGEAZAApAFwAIgA7ACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBjAG8AbgBkAGEAcgB5AFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAIAAoAFMAdABvAGMAawBwAGkAbABlACkAXAAiACwAIAAwAC4AMAAyACwAIAAwAC4AMAAyACwAIAAwAC4AMAAyACwAIABcACIATgBvACAAZABhAHQAYQBcACIALAAgADAALgAwADIALAAgADAALgAwADIALAAgADAALgAwADIALAAgAFwAIgBOAG8AIABkAGEAdABhAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiADsAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAGMAbwBuAGQAYQByAHkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAUABhAHMAcwBpAHYAZQAgAFcAaQBuAGQAcgBvAHcAKQBcACIALAAgADAALgAwADEALAAgADAALgAwADEALAAgADAALgAwADEALAAgAFwAIgBOAG8AIABkAGEAdABhAFwAIgAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAXAAiAE4AbwAgAGQAYQB0AGEAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIAOwAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAGUAYwBvAG4AZABhAHIAeQBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgAgAHQAbwAgAHMAbwBpAGwAXAAiACwAIAAwACwAIAAwACwAIAAwACwAIABcACIATgBvACAAZABhAHQAYQBcACIALAAgADAALAAgADAALAAgADAALAAgAFwAIgBOAG8AIABkAGEAdABhAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgA7ACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQByAHQAaQBhAHIAeQBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AIAAoAEUAZgBmAGwAdQBlAG4AdAAgAHAAbwBuAGQAKQBcACIALAAgADAALgA3ADUALAAgADAALgA3ADUALAAgADAALgA3ADcALAAgAFwAIgBOAG8AIABkAGEAdABhAFwAIgAsACAAMAAuADcANQAsACAAMAAuADcANQAsACAAMAAuADcANwAsACAAXAAiAE4AbwAgAGQAYQB0AGEAXAAiACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBcAG4AVABhAGIAbABlACAAQQAuADEALgAxAC4ANQA6ACAAQgBlAGUAZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAC0AIABOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAARQBGAHMAIAAoAEUARgBtAFQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGUAZQBkAGwAbwB0ACAALQAgAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABFAEYAcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AMQAuADUAOgAgAEIAZQBlAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIAAtACAATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAEUARgBzACAAKABFAEYAbQBUACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAJwBOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AJwAgAGMAbwBsAHUAbQBuACAAdwBpAHQAaAAgAE0ATQBTACAAbgBhAG0AZQBzACAAdABoAGEAdAAgAG0AYQB0AGMAaAAgAE4ASQBSACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAVABcACIALAAgAFwAIgBNAE0AUwAgAG0AXAAiACwAIABcACIARQBGAG0AVAAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApAFwAIgAsACAAXAAiAE4ASQBSACAAZABlAGYAaQBuAGkAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUAByAGkAbQBhAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGwAbwB0ACAAKABGAGUAZQBkAHAAYQBkACkAXAAiACwAIAAwAC4AMAAwADUANAAsACAAXAAiAEQAcgB5AGwAbwB0ACAAKABmAGUAZQBkACAAcABhAGQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAGMAbwBuAGQAYQByAHkAXAAiACwAIABcACIAUwBvAGwAaQBkACAAUwB0AG8AcgBhAGcAZQAgACgAUwB0AG8AYwBrAHAAaQBsAGUAKQBcACIALAAgADAALgAwADAANQAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBjAG8AbgBkAGEAcgB5AFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAFAAYQBzAHMAaQB2AGUAIABXAGkAbgBkAHIAbwB3ACkAXAAiACwAIAAwAC4AMAAxACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAGMAbwBuAGQAYQByAHkAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AIAB0AG8AIABzAG8AaQBsAFwAIgAsACAAMAAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAcgB0AGkAYQByAHkAXAAiACwAIABcACIAVQBuAGMAbwB2AGUAcgBlAGQAIABhAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuACAAKABFAGYAZgBsAHUAZQBuAHQAIABQAG8AbgBkACkAXAAiACwAIAAwACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBGAHIAYQBjAE4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADEALgA2ADoAIABCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABiAHkAIABNAE0AUwAgACgARgByAGEAYwBHAEEAUwBNAG0AVAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARgByAGEAYwBOAFYAbwBsAGEAdABpAGwAaQBzAGUAZABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBlAGUAZABsAG8AdAAgAC0AIABGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAYgB5ACAATQBNAFMAIAAoAEYAcgBhAGMARwBBAFMATQBtAFQAKQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBGAHIAYQBjAE4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARgByAGEAYwBOAFYAbwBsAGEAdABpAGwAaQBzAGUAZABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADEALgA2ADoAIABCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABiAHkAIABNAE0AUwAgACgARgByAGEAYwBHAEEAUwBNAG0AVAApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEYAcgBhAGMATgBWAG8AbABhAHQAaQBsAGkAcwBlAGQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAJwBOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AJwAgAGMAbwBsAHUAbQBuACAAdwBpAHQAaAAgAE0ATQBTACAAbgBhAG0AZQBzACAAdABoAGEAdAAgAG0AYQB0AGMAaAAgAE4ASQBSACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEYAcgBhAGMATgBWAG8AbABhAHQAaQBsAGkAcwBlAGQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIABUAFwAIgAsACAAXAAiAE0ATQBTACAAbQBcACIALAAgAFwAIgBGAHIAYQBjAEcAQQBTAE0AbQBUACAAKABrAGcAIABOAEgAMwAtAE4AIAArACAATgBPAHgALQBOACkALwBrAGcAIABOAFwAIgAsACAAXAAiAE4ASQBSACAAZABlAGYAaQBuAGkAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUAByAGkAbQBhAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGwAbwB0ACAAKABGAGUAZQBkAHAAYQBkACkAXAAiACwAIAAwAC4ANgAsACAAXAAiAEQAcgB5AGwAbwB0ACAAKABmAGUAZQBkACAAcABhAGQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAGMAbwBuAGQAYQByAHkAXAAiACwAIABcACIAUwBvAGwAaQBkACAAUwB0AG8AcgBhAGcAZQAgACgAUwB0AG8AYwBrAHAAaQBsAGUAKQBcACIALAAgADAALgAyADUALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAGUAYwBvAG4AZABhAHIAeQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABQAGEAcwBzAGkAdgBlACAAVwBpAG4AZAByAG8AdwApAFwAIgAsACAAMAAuADQALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAGUAYwBvAG4AZABhAHIAeQBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgAgAHQAbwAgAHMAbwBpAGwAXAAiACwAIAAwACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQByAHQAaQBhAHIAeQBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AIAAoAEUAZgBmAGwAdQBlAG4AdAAgAHAAbwBuAGQAKQBcACIALAAgADAALgAzADUALAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADQALgAxADoAIABCAGUAZQBmACAARgBlAGUAZABsAG8AdABcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANAAuADEALgAxAC4AMQAgAE0AZQB0AGgAbwBkACAAMQAgAC0AIABNAGEAbgB1AHIAZQAgAE0AZQB0AGgAYQBuAGUAIABCAGUAZQBmACAARgBlAGUAZABsAG8AdABcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBcAG4AVABvAHQAYQBsACAAYQBuAG4AdQBhAGwAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAbQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0AFwAbgBFAF8AQwBIADQAXABuAHQAIABDAEgANABcAG4AewBFAH0AXwB7AEMASAA0AH0APQBcAFwAcwB1AG0AXwB7AGoAfQBcAFwAcwB1AG0AXwB7AG0AfQBcAFwAcwB1AG0AXwB7AFQAfQAoAEQAXwB7AGoAfQBcAFwAdABpAG0AZQBzACAATQBfAHsAagBtAFQAfQBcAFwAdABpAG0AZQBzACAATgBfAHsAagB9ACkAXABcAHQAaQBtAGUAcwAxADAAXgB7AC0AMwB9AFwAbgBEAF8AagAgAD0AIABsAGUAbgBnAHQAaAAgAG8AZgAgAHMAdABhAHkAIABvAGYAIABlAGEAYwBoACAAYwBhAHQAdABsAGUAIABnAHIAbwB1AHAAIAA6ACAAZABhAHkAcwBcAG4ATQBfAGoAbQBUACAAPQAgAG0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgByAG8AbQAgAG0AYQBuAHUAcgBlACAAcABlAHIAIABjAGEAdAB0AGwAZQAgAGcAcgBvAHUAcAAsACAATQBNAFMALAAgAGEAbgBkACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAA6ACAAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXABuAE4AXwBqACAAPQAgAG4AdQBtAGIAZQByAHMAIABvAGYAIABiAGUAZQBmACAAYwBhAHQAdABsAGUAIABpAG4AIABlAGEAYwBoACAAZwByAG8AdQBwACAAOgAgAGgAZQBhAGQAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEQAXwBqACwAIABNAF8AagBtAFQALAAgAE4AXwBqACwAXABuACAAIAAgACAAKABEAF8AagAgACoAIABNAF8AagBtAFQAIAAqACAATgBfAGoAKQAgACoAIAAxADAAIABeACAALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBUAG8AdABhAGwAIABhAG4AbgB1AGEAbAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAEMASAA0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBIADQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMQAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB7AEUAfQBfAHsAQwBIADQAfQA9AFwAXABzAHUAbQBfAHsAagB9AFwAXABzAHUAbQBfAHsAbQB9AFwAXABzAHUAbQBfAHsAVAB9ACgARABfAHsAagB9AFwAXAB0AGkAbQBlAHMAIABNAF8AewBqAG0AVAB9AFwAXAB0AGkAbQBlAHMAIABOAF8AewBqAH0AKQBcAFwAdABpAG0AZQBzADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAF8AagBcACIALABcACIAbABlAG4AZwB0AGgAIABvAGYAIABzAHQAYQB5ACAAbwBmACAAZQBhAGMAaAAgAGMAYQB0AHQAbABlACAAZwByAG8AdQBwACAAOgAgAGQAYQB5AHMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AXwBqAG0AVABcACIALABcACIAbQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAbQBhAG4AdQByAGUAIABwAGUAcgAgAGMAYQB0AHQAbABlACAAZwByAG8AdQBwACwAIABNAE0AUwAsACAAYQBuAGQAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADoAIABrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBfAGoAXAAiACwAXAAiAG4AdQBtAGIAZQByAHMAIABvAGYAIABiAGUAZQBmACAAYwBhAHQAdABsAGUAIABpAG4AIABlAGEAYwBoACAAZwByAG8AdQBwACAAOgAgAGgAZQBhAGQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMgBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBEAHIAeQBsAG8AdABcAG4AUAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADEAIABNAE0AUwBcAG4ATQBfAGoAbQA1AFQAMQBcAG4AawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXABuAE0AXwB7AGoAbQA9ADUALABUAD0AMQB9AD0AVgBTAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAEIATwBcAFwAdABpAG0AZQBzACAATQBNAFMAXwB7AG0APQA1ACwAVAA9ADEAfQBcAFwAdABpAG0AZQBzACAATQBDAEYAXwB7AGkAbQA9ADUAfQBcAFwAdABpAG0AZQBzACAAXABcAHIAaABvAFwAbgBWAFMAXwBqACAAPQAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAAaQBuACAAZQBhAGMAaAAgAGcAcgBvAHUAcAAgADoAIABrAGcALwBoAGUAYQBkAC8AZABhAHkAXABuAEIATwAgAD0AIABlAG0AaQBzAHMAaQBvAG4AcwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAOgAgAG0AMwAgAEMASAA0AC8AawBnACAAVgBTAFwAbgBNAE0AUwBfAG0ANQBUADEAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIABpAG4AIABwAHIAaQBtAGEAcgB5ACAAcwB5AHMAdABlAG0AIABkAHIAeQBsAG8AdAAgAE0ATQBTACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4ATQBDAEYAXwBpAG0ANQAgAD0AIABtAGUAdABoAGEAbgBlACAAYwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlACAAYQBuAGQAIABkAHIAeQBsAG8AdAAgAHMAeQBzAHQAZQBtACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4AcgBoAG8AIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIAA6ACAAawBnAC8AbQAzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADIAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARAByAHkAbABvAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVgBTAF8AagAsACAAQgBPACwAIABNAE0AUwBfAG0ANQBUADEALAAgAE0AQwBGAF8AaQBtADUALAAgAHIAaABvACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAATQBDAEYAXwBpAG0ANQAsACAASQBGACgASQBTAE4AVQBNAEIARQBSACgATQBDAEYAXwBpAG0ANQApACwAIABNAEMARgBfAGkAbQA1ACwAIAAwACkALABcAG4AIAAgACAAIAAgACAAVgBTAF8AagAgACoAIABCAE8AIAAqACAATQBNAFMAXwBtADUAVAAxACAAKgAgAE0AQwBGAF8AaQBtADUAIAAqACAAcgBoAG8AXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADIAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARAByAHkAbABvAHQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAxACAATQBNAFMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADIAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARAByAHkAbABvAHQAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwBqAG0ANQBUADEAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADIAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARAByAHkAbABvAHQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMgBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBEAHIAeQBsAG8AdABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMQAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADIAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMgBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBEAHIAeQBsAG8AdABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMgBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBEAHIAeQBsAG8AdABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwB7AGoAbQA9ADUALABUAD0AMQB9AD0AVgBTAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAEIATwBcAFwAdABpAG0AZQBzACAATQBNAFMAXwB7AG0APQA1ACwAVAA9ADEAfQBcAFwAdABpAG0AZQBzACAATQBDAEYAXwB7AGkAbQA9ADUAfQBcAFwAdABpAG0AZQBzACAAXABcAHIAaABvAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAyAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEQAcgB5AGwAbwB0AF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAUwBfAGoAXAAiACwAXAAiAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAAaQBuACAAZQBhAGMAaAAgAGcAcgBvAHUAcAAgADoAIABrAGcALwBoAGUAYQBkAC8AZABhAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIATwBcACIALABcACIAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbAAgADoAIABtADMAIABDAEgANAAvAGsAZwAgAFYAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBNAFMAXwBtADUAVAAxAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAGkAbgAgAHAAcgBpAG0AYQByAHkAIABzAHkAcwB0AGUAbQAgAGQAcgB5AGwAbwB0ACAATQBNAFMAIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEMARgBfAGkAbQA1AFwAIgAsAFwAIgBtAGUAdABoAGEAbgBlACAAYwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlACAAYQBuAGQAIABkAHIAeQBsAG8AdAAgAHMAeQBzAHQAZQBtACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcgBoAG8AXAAiACwAXAAiAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAOgAgAGsAZwAvAG0AMwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAaQBcACIALAAgAFwAIgBzAHQAYQB0AGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBcAG4AUAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADIAIABNAE0AUwBcAG4ATQBfAGoAbQBUADIAXABuAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAbgBNAF8AewBqAG0AVAA9ADIAfQA9ACgAMQAtAFYAUwBMACkAXABcAHQAaQBtAGUAcwAgAFYAUwBfAHsAagB9AFwAXAB0AGkAbQBlAHMAIABCAE8AXABcAHQAaQBtAGUAcwAgAE0ATQBTAF8AewBtAFQAPQAyAH0AXABcAHQAaQBtAGUAcwAgAE0AQwBGAF8AewBpAG0AfQBcAFwAdABpAG0AZQBzACAAXABcAHIAaABvAFwAbgBWAFMATAAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAGwAbwBzAHQAIABkAHUAcgBpAG4AZwAgAHMAdABvAHIAYQBnAGUAIABpAG4AIAB0AGgAZQAgAHAAcgBpAG0AYQByAHkAIABzAHkAcwB0AGUAbQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAFYAUwBfAGoAIAA9ACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIABpAG4AIABlAGEAYwBoACAAZwByAG8AdQBwACAAOgAgAGsAZwAvAGgAZQBhAGQALwBkAGEAeQBcAG4AQgBPACAAPQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAcABvAHQAZQBuAHQAaQBhAGwAIAA6ACAAbQAzACAAQwBIADQALwBrAGcAIABWAFMAXABuAE0ATQBTAF8AbQBUADIAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIABpAG4AIABlAGEAYwBoACAAcwBlAGMAbwBuAGQAYQByAHkAIABzAHkAcwB0AGUAbQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAE0AQwBGAF8AaQBtACAAPQAgAG0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIABhAG4AZAAgAE0ATQBTACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4AcgBoAG8AIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIAA6ACAAawBnAC8AbQAzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVgBTAEwALAAgAFYAUwBfAGoALAAgAEIATwAsACAATQBNAFMAXwBtAFQAMgAsACAATQBDAEYAXwBpAG0ALAAgAHIAaABvACwAXABuACAAIAAgACAAKAAxACAALQAgAFYAUwBMACkAIAAqACAAVgBTAF8AagAgACoAIABCAE8AIAAqACAATQBNAFMAXwBtAFQAMgAgACoAIABNAEMARgBfAGkAbQAgACoAIAByAGgAbwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAyACAATQBNAFMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwBqAG0AVAAyAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAzACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAF8AewBqAG0AVAA9ADIAfQA9ACgAMQAtAFYAUwBMACkAXABcAHQAaQBtAGUAcwAgAFYAUwBfAHsAagB9AFwAXAB0AGkAbQBlAHMAIABCAE8AXABcAHQAaQBtAGUAcwAgAE0ATQBTAF8AewBtAFQAPQAyAH0AXABcAHQAaQBtAGUAcwAgAE0AQwBGAF8AewBpAG0AfQBcAFwAdABpAG0AZQBzACAAXABcAHIAaABvAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA3ACwAIAAyACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAUwBMAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAGwAbwBzAHQAIABkAHUAcgBpAG4AZwAgAHMAdABvAHIAYQBnAGUAIABpAG4AIAB0AGgAZQAgAHAAcgBpAG0AYQByAHkAIABzAHkAcwB0AGUAbQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAUwBfAGoAXAAiACwAXAAiAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAAaQBuACAAZQBhAGMAaAAgAGcAcgBvAHUAcAAgADoAIABrAGcALwBoAGUAYQBkAC8AZABhAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIATwBcACIALABcACIAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbAAgADoAIABtADMAIABDAEgANAAvAGsAZwAgAFYAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBNAFMAXwBtAFQAMgBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIABpAG4AIABlAGEAYwBoACAAcwBlAGMAbwBuAGQAYQByAHkAIABzAHkAcwB0AGUAbQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQwBGAF8AaQBtAFwAIgAsAFwAIgBtAGUAdABoAGEAbgBlACAAYwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlACAAYQBuAGQAIABNAE0AUwAgADoAIABmAHIAYQBjAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHIAaABvAFwAIgAsAFwAIgBkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgADoAIABrAGcALwBtADMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGkAXAAiACwAIABcACIAcwB0AGEAdABlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADQAXwBTAHQAYQBnAGUAMwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXABuAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAzACAATQBNAFMAXABuAE0AXwBqAG0AMQBUADMAXABuAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAbgBNAF8AewBqAG0APQAxACwAVAA9ADMAfQA9AFYAUwBfAHsAagB9AFwAXAB0AGkAbQBlAHMAIABCAE8AXABcAHQAaQBtAGUAcwAgAE0ATQBTAF8AewBtAD0AMQAsAFQAPQAzAH0AXABcAHQAaQBtAGUAcwAgAE0AQwBGAF8AewBpAG0APQAxAH0AXABcAHQAaQBtAGUAcwAgAFwAXAByAGgAbwBcAG4AVgBTAF8AagAgAD0AIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgByAG8AbQAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAGkAbgAgAGUAYQBjAGgAIABnAHIAbwB1AHAAIAA6ACAAawBnAC8AaABlAGEAZAAvAGQAYQB5AFwAbgBCAE8AIAA9ACAAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbAAgADoAIABtADMAIABDAEgANAAvAGsAZwAgAFYAUwBcAG4ATQBNAFMAXwBtADEAVAAzACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAdABvACAAdABlAHIAdABpAGEAcgB5ACAAYQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgAHMAeQBzAHQAZQBtACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4ATQBDAEYAXwBpAG0AMQAgAD0AIABtAGUAdABoAGEAbgBlACAAYwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlACAAYQBuAGQAIABhAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuACAAcwB5AHMAdABlAG0AIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAbgByAGgAbwAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgADoAIABrAGcALwBtADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANABfAFMAdABhAGcAZQAzAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABWAFMAXwBqACwAIABCAE8ALAAgAE0ATQBTAF8AbQAxAFQAMwAsACAATQBDAEYAXwBpAG0AMQAsACAAcgBoAG8ALABcAG4AIAAgACAAIABWAFMAXwBqACAAKgAgAEIATwAgACoAIABNAE0AUwBfAG0AMQBUADMAIAAqACAATQBDAEYAXwBpAG0AMQAgACoAIAByAGgAbwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADQAXwBTAHQAYQBnAGUAMwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAzACAATQBNAFMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADQAXwBTAHQAYQBnAGUAMwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwBqAG0AMQBUADMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADQAXwBTAHQAYQBnAGUAMwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANABfAFMAdABhAGcAZQAzAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMQAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADQAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANABfAFMAdABhAGcAZQAzAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANABfAFMAdABhAGcAZQAzAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwB7AGoAbQA9ADEALABUAD0AMwB9AD0AVgBTAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAEIATwBcAFwAdABpAG0AZQBzACAATQBNAFMAXwB7AG0APQAxACwAVAA9ADMAfQBcAFwAdABpAG0AZQBzACAATQBDAEYAXwB7AGkAbQA9ADEAfQBcAFwAdABpAG0AZQBzACAAXABcAHIAaABvAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA0AF8AUwB0AGEAZwBlADMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAUwBfAGoAXAAiACwAXAAiAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAAaQBuACAAZQBhAGMAaAAgAGcAcgBvAHUAcAAgAGoAIAA6ACAAawBnAC8AaABlAGEAZAAvAGQAYQB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAE8AXAAiACwAXAAiAGUAbQBpAHMAcwBpAG8AbgBzACAAcABvAHQAZQBuAHQAaQBhAGwAIAA6ACAAbQAzACAAQwBIADQALwBrAGcAIABWAFMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATQBTAF8AbQAxAFQAMwBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIAB0AG8AIAB0AGUAcgB0AGkAYQByAHkAIABhAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuACAAcwB5AHMAdABlAG0AIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEMARgBfAGkAbQAxAFwAIgAsAFwAIgBtAGUAdABoAGEAbgBlACAAYwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlACAAYQBuAGQAIABhAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuACAAcwB5AHMAdABlAG0AIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgByAGgAbwBcACIALABcACIAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIAA6ACAAawBnAC8AbQAzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBpAFwAIgAsACAAXAAiAHMAdABhAHQAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA1AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABQAHIAbwBkAHUAYwB0AGkAbwBuAFwAbgBWAG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAIABwAHIAbwBkAHUAYwB0AGkAbwBuAFwAbgBWAFMAXwBqAFwAbgBrAGcALwBoAGUAYQBkAC8AZABhAHkAXABuAFYAUwBfAHsAagB9AD0ASQBfAHsAagB9AFwAXAB0AGkAbQBlAHMAKAAxAC0ARABNAEQAXwB7AGoAfQApAFwAXAB0AGkAbQBlAHMAKAAxAC0AQQApAFwAbgBJAF8AagAgAD0AIABkAHIAeQAgAG0AYQB0AHQAZQByACAAaQBuAHQAYQBrAGUAIABmAG8AcgAgAGUAYQBjAGgAIABnAHIAbwB1AHAAIAA6ACAAawBnACAARABNAC8AaABlAGEAZAAvAGQAYQB5AFwAbgBEAE0ARABfAGoAIAA9ACAAZAByAHkAIABtAGEAdAB0AGUAcgAgAGQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAIABmAG8AcgAgAGUAYQBjAGgAIABnAHIAbwB1AHAAIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAbgBBACAAPQAgAGEAcwBoACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAG0AYQBuAHUAcgBlACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA1AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABQAHIAbwBkAHUAYwB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEkAXwBqACwAIABEAE0ARABfAGoALAAgAEEALABcAG4AIAAgACAAIABJAF8AagAgACoAIAAoADEAIAAtACAARABNAEQAXwBqACkAIAAqACAAKAAxACAALQAgAEEAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAUwBfAGoAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcALwBoAGUAYQBkAC8AZABhAHkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAA1ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAFMAXwB7AGoAfQA9AEkAXwB7AGoAfQBcAFwAdABpAG0AZQBzACgAMQAtAEQATQBEAF8AewBqAH0AKQBcAFwAdABpAG0AZQBzACgAMQAtAEEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAUAByAG8AZAB1AGMAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAF8AagBcACIALABcACIAZAByAHkAIABtAGEAdAB0AGUAcgAgAGkAbgB0AGEAawBlACAAZgBvAHIAIABlAGEAYwBoACAAZwByAG8AdQBwACAAagAgADoAIABrAGcAIABEAE0ALwBoAGUAYQBkAC8AZABhAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQATQBEAF8AagBcACIALABcACIAZAByAHkAIABtAGEAdAB0AGUAcgAgAGQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAIABmAG8AcgAgAGUAYQBjAGgAIABnAHIAbwB1AHAAIABqACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBcACIALABcACIAYQBzAGgAIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAbQBhAG4AdQByAGUAIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAF8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANAAuADEAOgAgAEIAZQBlAGYAIABGAGUAZQBkAGwAbwB0AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA0AC4AMQAuADEALgAzACAATQBlAHQAaABvAGQAIAAxACAALQAgAE0AYQBuAHUAcgBlACAARABpAHIAZQBjAHQAIABOADIATwAgAEIAZQBlAGYAIABGAGUAZQBkAGwAbwB0AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBcAG4AVABvAHQAYQBsACAAYQBuAG4AdQBhAGwAIABkAGkAcgBlAGMAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAIABzAHkAcwB0AGUAbQBzAFwAbgBFAF8ATgAyAE8AZABpAHIAXABuAHQAIABOADIATwBcAG4ARQBfAHsATgAyAE8ALABkAGkAcgB9AD0AXABcAHMAdQBtAF8AewBqAH0AXABcAHMAdQBtAF8AewBtAH0AXABcAHMAdQBtAF8AewBUAH0AKABNAE4AXwB7AGoAbQBUAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAagBtAH0AXABcAHQAaQBtAGUAcwAgAEMAXwB7AE4AMgBPAH0AKQBcAFwAdABpAG0AZQBzADEAMABeAHsALQAzAH0AXABuAE0ATgBfAGoAbQBUACAAPQAgAG4AaQB0AHIAbwBnAGUAbgAgAHAAZQByACAAYwBhAHQAdABsAGUAIABnAHIAbwB1AHAALAAgAE0ATQBTACAAYQBuAGQAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADoAIABrAGcAIABOAFwAbgBFAEYAXwBqAG0AIAA9ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABNAE0AUwAgADoAIABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOAFwAbgBDAF8ATgAyAE8AIAA9ACAAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwAgADoAIAByAGEAdABpAG8AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAE4AXwBqAG0AVAAsACAARQBGAF8AagBtACwAIABDAF8ATgAyAE8ALABcAG4AIAAgACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgATQBOAF8AagBtAFQALAAgAEUARgBfAGoAbQAsACAAQwBfAE4AMgBPACkAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAbwB0AGEAbAAgAGEAbgBuAHUAYQBsACAAZABpAHIAZQBjAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAbQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0ACAAcwB5AHMAdABlAG0AcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAE4AMgBPAGQAaQByAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAxAC4AMQAuADMALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsATgAyAE8ALABkAGkAcgB9AD0AXABcAHMAdQBtAF8AewBqAH0AXABcAHMAdQBtAF8AewBtAH0AXABcAHMAdQBtAF8AewBUAH0AKABNAE4AXwB7AGoAbQBUAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAagBtAH0AXABcAHQAaQBtAGUAcwAgAEMAXwB7AE4AMgBPAH0AKQBcAFwAdABpAG0AZQBzADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBOAF8AagBtAFQAXAAiACwAXAAiAG4AaQB0AHIAbwBnAGUAbgAgAHAAZQByACAAYwBhAHQAdABsAGUAIABnAHIAbwB1AHAALAAgAE0ATQBTACAAYQBuAGQAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADoAIABrAGcAIABOAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBqAG0AXAAiACwAXAAiAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAATQBNAFMAIAA6ACAAawBnACAATgAyAE8ALQBOAC8AawBnACAATgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBfAE4AMgBPAFwAIgAsAFwAIgBmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzACAAOgAgAHIAYQB0AGkAbwBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAyAF8AUwB0AGEAZwBlADEATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBEAHIAeQBsAG8AdABcAG4ATgBpAHQAcgBvAGcAZQBuACAAaQBuACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAxACAATQBNAFMAXABuAE0ATgBfAGoAbQA1AFQAMQBcAG4AawBnACAATgBcAG4ATQBOAF8AewBqAG0APQA1ACwAVAA9ADEAfQA9AEEARQBfAHsAagB9AFwAXAB0AGkAbQBlAHMAIABNAE0AUwBfAHsAagBtAD0ANQAsAFQAPQAxAH0AXABuAEEARQBfAGoAIAA9ACAAdABvAHQAYQBsACAAbgBpAHQAcgBvAGcAZQBuACAAZQB4AGMAcgBlAHQAZQBkACAAYgB5ACAAZQBhAGMAaAAgAGMAYQB0AHQAbABlACAAZwByAG8AdQBwACAAOgAgAGsAZwAgAE4AXABuAE0ATQBTAF8AagBtADUAVAAxACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAaQBuACAAcAByAGkAbQBhAHIAeQAgAHMAeQBzAHQAZQBtACAAZAByAHkAbABvAHQAIABNAE0AUwAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMARAByAHkAbABvAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQBFAF8AagAsACAATQBNAFMAXwBqAG0ANQBUADEALABcAG4AIAAgACAAIABBAEUAXwBqACAAKgAgAE0ATQBTAF8AagBtADUAVAAxAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMARAByAHkAbABvAHQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMQAgAE0ATQBTAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAyAF8AUwB0AGEAZwBlADEATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBEAHIAeQBsAG8AdABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBOAF8AagBtADUAVAAxAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAyAF8AUwB0AGEAZwBlADEATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBEAHIAeQBsAG8AdABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADIAXwBTAHQAYQBnAGUAMQBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAEQAcgB5AGwAbwB0AF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAxAC4AMQAuADMALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAyAF8AUwB0AGEAZwBlADEATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBEAHIAeQBsAG8AdABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMARAByAHkAbABvAHQAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE4AXwB7AGoAbQA9ADUALABUAD0AMQB9AD0AQQBFAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAE0ATQBTAF8AewBqAG0APQA1ACwAVAA9ADEAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMARAByAHkAbABvAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBFAF8AagBcACIALABcACIAdABvAHQAYQBsACAAbgBpAHQAcgBvAGcAZQBuACAAZQB4AGMAcgBlAHQAZQBkACAAYgB5ACAAZQBhAGMAaAAgAGMAYQB0AHQAbABlACAAZwByAG8AdQBwACAAOgAgAGsAZwAgAE4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATQBTAF8AagBtADUAVAAxAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAGkAbgAgAHAAcgBpAG0AYQByAHkAIABzAHkAcwB0AGUAbQAgAGQAcgB5AGwAbwB0ACAATQBNAFMAIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADMAXwBBAG4AbgB1AGEAbABOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AXABuAEEAbgBuAHUAYQBsACAAbgBpAHQAcgBvAGcAZQBuACAAZQB4AGMAcgBlAHQAaQBvAG4AIABmAHIAbwBtACAAZQBhAGMAaAAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAGcAcgBvAHUAcABcAG4AQQBFAF8AagBcAG4AawBnACAATgBcAG4AQQBFAF8AewBqAH0APQBOAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAE4ARQBfAHsAagB9AFwAXAB0AGkAbQBlAHMAIABEAF8AewBqAH0AXABuAE4AXwBqACAAPQAgAG4AdQBtAGIAZQByACAAbwBmACAAYwBhAHQAdABsAGUAIABpAG4AIABlAGEAYwBoACAAZwByAG8AdQBwACAAOgAgAGgAZQBhAGQAXABuAE4ARQBfAGoAIAA9ACAAbgBpAHQAcgBvAGcAZQBuACAAZQB4AGMAcgBlAHQAaQBvAG4AIAA6ACAAawBnACAATgAvAGgAZQBhAGQALwBkAGEAeQBcAG4ARABfAGoAIAA9ACAAZAB1AHIAYQB0AGkAbwBuACAAbwBmACAAcwB0AGEAeQAgAG8AZgAgAGMAYQB0AHQAbABlACAAZwByAG8AdQBwACAAOgAgAGQAYQB5AHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMwBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABOAF8AagAsACAATgBFAF8AagAsACAARABfAGoALABcAG4AIAAgACAAIABOAF8AagAgACoAIABOAEUAXwBqACAAKgAgAEQAXwBqAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMwBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBuAG4AdQBhAGwAIABuAGkAdAByAG8AZwBlAG4AIABlAHgAYwByAGUAdABpAG8AbgAgAGYAcgBvAG0AIABlAGEAYwBoACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAAZwByAG8AdQBwAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAzAF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEUAXwBqAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAzAF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMwBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMQAuADEALgAzACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADMAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMwBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMwBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEARQBfAHsAagB9AD0ATgBfAHsAagB9AFwAXAB0AGkAbQBlAHMAIABOAEUAXwB7AGoAfQBcAFwAdABpAG0AZQBzACAARABfAHsAagB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAzAF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AXwBqAFwAIgAsAFwAIgBuAHUAbQBiAGUAcgAgAG8AZgAgAGMAYQB0AHQAbABlACAAaQBuACAAZQBhAGMAaAAgAGcAcgBvAHUAcAAgADoAIABoAGUAYQBkAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEUAXwBqAFwAIgAsAFwAIgBuAGkAdAByAG8AZwBlAG4AIABlAHgAYwByAGUAdABpAG8AbgAgADoAIABrAGcAIABOAC8AaABlAGEAZAAvAGQAYQB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAF8AagBcACIALABcACIAZAB1AHIAYQB0AGkAbwBuACAAbwBmACAAcwB0AGEAeQAgAG8AZgAgAGMAYQB0AHQAbABlACAAZwByAG8AdQBwACAAOgAgAGQAYQB5AHMAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANABfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBQAGUAcgBIAGUAYQBkAFwAbgBOAGkAdAByAG8AZwBlAG4AIABlAHgAYwByAGUAdABpAG8AbgAgAHAAZQByACAAaABlAGEAZAAgAHAAZQByACAAZABhAHkAXABuAE4ARQBfAGoAXABuAGsAZwAgAE4ALwBoAGUAYQBkAC8AZABhAHkAXABuAE4ARQBfAHsAagB9AD0ATgBJAF8AewBqAH0AXABcAHQAaQBtAGUAcwAoADEALQBOAFIAXwB7AGoAfQApAFwAbgBOAEkAXwBqACAAPQAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgB0AGEAawBlACAAOgAgAGsAZwAgAE4ALwBoAGUAYQBkAC8AZABhAHkAXABuAE4AUgBfAGoAIAA9ACAAbgBpAHQAcgBvAGcAZQBuACAAcgBlAHQAZQBuAHQAaQBvAG4AIABlAHgAcAByAGUAcwBzAGUAZAAgAGEAcwAgAGEAIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABpAG4AdABhAGsAZQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANABfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBQAGUAcgBIAGUAYQBkAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE4ASQBfAGoALAAgAE4AUgBfAGoALABcAG4AIAAgACAAIABOAEkAXwBqACAAKgAgACgAMQAgAC0AIABOAFIAXwBqACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA0AF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAFAAZQByAEgAZQBhAGQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwBnAGUAbgAgAGUAeABjAHIAZQB0AGkAbwBuACAAcABlAHIAIABoAGUAYQBkACAAcABlAHIAIABkAGEAeQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANABfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBQAGUAcgBIAGUAYQBkAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAEUAXwBqAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA0AF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAFAAZQByAEgAZQBhAGQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOAC8AaABlAGEAZAAvAGQAYQB5AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA0AF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAFAAZQByAEgAZQBhAGQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADEALgAxAC4AMwAsACAARQBxAHUAYQB0AGkAbwBuACAAKAA0ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADQAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AUABlAHIASABlAGEAZABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANABfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBQAGUAcgBIAGUAYQBkAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBFAF8AewBqAH0APQBOAEkAXwB7AGoAfQBcAFwAdABpAG0AZQBzACgAMQAtAE4AUgBfAHsAagB9ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADQAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AUABlAHIASABlAGEAZABfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEkAXwBqAFwAIgAsAFwAIgBuAGkAdAByAG8AZwBlAG4AIABpAG4AdABhAGsAZQAgADoAIABrAGcAIABOAC8AaABlAGEAZAAvAGQAYQB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAFIAXwBqAFwAIgAsAFwAIgBuAGkAdAByAG8AZwBlAG4AIAByAGUAdABlAG4AdABpAG8AbgAgAGUAeABwAHIAZQBzAHMAZQBkACAAYQBzACAAYQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAGkAbgB0AGEAawBlACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA1AF8ATgBpAHQAcgBvAGcAZQBuAEkAbgB0AGEAawBlAFwAbgBOAGkAdAByAG8AZwBlAG4AIABpAG4AdABhAGsAZQAgAG8AZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQBcAG4ATgBJAF8AagBcAG4AawBnACAATgAvAGgAZQBhAGQALwBkAGEAeQBcAG4ATgBJAF8AewBqAH0APQBJAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAEMAUABfAHsAagB9AFwAXABkAGkAdgAgADYALgAyADUAXABuAEkAXwBqACAAPQAgAGQAcgB5ACAAbQBhAHQAdABlAHIAIABpAG4AdABhAGsAZQAgADoAIABrAGcAIABEAE0ALwBoAGUAYQBkAC8AZABhAHkAXABuAEMAUABfAGoAIAA9ACAAYwByAHUAZABlACAAcAByAG8AdABlAGkAbgAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABmAGUAZQBkACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4ANgAuADIANQAgAD0AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAYwBvAG4AdgBlAHIAdABpAG4AZwAgAGMAcgB1AGQAZQAgAHAAcgBvAHQAZQBpAG4AIABpAG4AdABvACAAbgBpAHQAcgBvAGcAZQBuACAAOgAgAHIAYQB0AGkAbwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA1AF8ATgBpAHQAcgBvAGcAZQBuAEkAbgB0AGEAawBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEkAXwBqACwAIABDAFAAXwBqACwAXABuACAAIAAgACAASQBfAGoAIAAqACAAQwBQAF8AagAgAC8AIAA2AC4AMgA1AFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANQBfAE4AaQB0AHIAbwBnAGUAbgBJAG4AdABhAGsAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBpAHQAcgBvAGcAZQBuACAAaQBuAHQAYQBrAGUAIABvAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADUAXwBOAGkAdAByAG8AZwBlAG4ASQBuAHQAYQBrAGUAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4ASQBfAGoAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADUAXwBOAGkAdAByAG8AZwBlAG4ASQBuAHQAYQBrAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOAC8AaABlAGEAZAAvAGQAYQB5AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA1AF8ATgBpAHQAcgBvAGcAZQBuAEkAbgB0AGEAawBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAxAC4AMQAuADMALAAgAEUAcQB1AGEAdABpAG8AbgAgACgANQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA1AF8ATgBpAHQAcgBvAGcAZQBuAEkAbgB0AGEAawBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA1AF8ATgBpAHQAcgBvAGcAZQBuAEkAbgB0AGEAawBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBJAF8AewBqAH0APQBJAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAEMAUABfAHsAagB9AFwAXABkAGkAdgAgADYALgAyADUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADUAXwBOAGkAdAByAG8AZwBlAG4ASQBuAHQAYQBrAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBfAGoAXAAiACwAXAAiAGQAcgB5ACAAbQBhAHQAdABlAHIAIABpAG4AdABhAGsAZQAgADoAIABrAGcAIABEAE0ALwBoAGUAYQBkAC8AZABhAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAUABfAGoAXAAiACwAXAAiAGMAcgB1AGQAZQAgAHAAcgBvAHQAZQBpAG4AIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAZgBlAGUAZAAgADoAIABmAHIAYQBjAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiADYALgAyADUAXAAiACwAXAAiAGYAYQBjAHQAbwByACAAZgBvAHIAIABjAG8AbgB2AGUAcgB0AGkAbgBnACAAYwByAHUAZABlACAAcAByAG8AdABlAGkAbgAgAGkAbgB0AG8AIABuAGkAdAByAG8AZwBlAG4AIAA6ACAAcgBhAHQAaQBvAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADYAXwBTAHQAYQBnAGUAMgBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAFwAbgBOAGkAdAByAG8AZwBlAG4AIABpAG4AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADIAIABNAE0AUwBcAG4ATQBOAF8AagBtAFQAMgBcAG4AawBnACAATgBcAG4ATQBOAF8AewBqAG0ALABUAD0AMgB9AD0ATgBUAF8AewBqAG0ALABUAD0AMgB9AFwAXAB0AGkAbQBlAHMAIABNAE0AUwBfAHsAagBtACwAVAA9ADIAfQBcAG4ATgBUAF8AagBtAFQAMgAgAD0AIABuAGkAdAByAG8AZwBlAG4AIAB0AHIAYQBuAHMAZgBlAHIAcgBlAGQAIAB0AG8AIABzAGUAYwBvAG4AZABhAHIAeQAgAHQAcgBlAGEAdABtAGUAbgB0ACAATQBNAFMAIAA6ACAAawBnACAATgBcAG4ATQBNAFMAXwBqAG0AVAAyACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAaQBuACAAZQBhAGMAaAAgAHMAZQBjAG8AbgBkAGEAcgB5ACAAcwB5AHMAdABlAG0AIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADYAXwBTAHQAYQBnAGUAMgBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE4AVABfAGoAbQBUADIALAAgAE0ATQBTAF8AagBtAFQAMgAsAFwAbgAgACAAIAAgAE4AVABfAGoAbQBUADIAIAAqACAATQBNAFMAXwBqAG0AVAAyAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANgBfAFMAdABhAGcAZQAyAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMgAgAE0ATQBTAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA2AF8AUwB0AGEAZwBlADIATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBOAF8AagBtAFQAMgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANgBfAFMAdABhAGcAZQAyAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA2AF8AUwB0AGEAZwBlADIATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMQAuADEALgAzACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADYAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANgBfAFMAdABhAGcAZQAyAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADYAXwBTAHQAYQBnAGUAMgBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBOAF8AewBqAG0ALABUAD0AMgB9AD0ATgBUAF8AewBqAG0ALABUAD0AMgB9AFwAXAB0AGkAbQBlAHMAIABNAE0AUwBfAHsAagBtACwAVAA9ADIAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANgBfAFMAdABhAGcAZQAyAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBUAF8AagBtAFQAMgBcACIALABcACIAbgBpAHQAcgBvAGcAZQBuACAAdAByAGEAbgBzAGYAZQByAHIAZQBkACAAdABvACAAcwBlAGMAbwBuAGQAYQByAHkAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAE0ATQBTACAAOgAgAGsAZwAgAE4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATQBTAF8AagBtAFQAMgBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIABpAG4AIABlAGEAYwBoACAAcwBlAGMAbwBuAGQAYQByAHkAIABzAHkAcwB0AGUAbQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANwBfAE4AaQB0AHIAbwBnAGUAbgBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAVABvAFMAdABhAGcAZQAyAFwAbgBOAGkAdAByAG8AZwBlAG4AIAB0AHIAYQBuAHMAZgBlAHIAcgBlAGQAIAB0AG8AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADIAIABNAE0AUwBcAG4ATgBUAF8AagBtAFQAMgBcAG4AawBnACAATgBcAG4ATgBUAF8AewBqAG0ALABUAD0AMgB9AD0AKABNAE4AXwB7AGoAbQA9ADUALABUAD0AMQB9AFwAXAB0AGkAbQBlAHMAKAAxAC0ARgByAGEAYwBHAEEAUwBNAF8AewBtAD0ANQB9AC0ARQBGAF8AewBtAD0ANQB9ACkAKQAtAE0ATgBfAHsAagBtACwAVAA9ADMAfQBcAG4ATQBOAF8AagBtADUAVAAxACAAPQAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAE0ATQBTACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAxACAAOgAgAGsAZwAgAE4AXABuAEYAcgBhAGMARwBBAFMATQBfAG0ANQAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAZgByAG8AbQAgAGQAcgB5AGwAbwB0ACAATQBNAFMAIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAbgBFAEYAXwBtADUAIAA9ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABkAHIAeQBsAG8AdAAgAE0ATQBTACAAOgAgAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AIABkAGUAcABvAHMAaQB0AGUAZABcAG4ATQBOAF8AagBtAFQAMwAgAD0AIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABNAE0AUwAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMwAgADoAIABrAGcAIABOAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADcAXwBOAGkAdAByAG8AZwBlAG4AVAByAGEAbgBzAGYAZQByAHIAZQBkAFQAbwBTAHQAYQBnAGUAMgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAE4AXwBqAG0ANQBUADEALAAgAEYAcgBhAGMARwBBAFMATQBfAG0ANQAsACAARQBGAF8AbQA1ACwAIABNAE4AXwBqAG0AVAAzACwAXABuACAAIAAgACAAKABNAE4AXwBqAG0ANQBUADEAIAAqACAAKAAxACAALQAgAEYAcgBhAGMARwBBAFMATQBfAG0ANQAgAC0AIABFAEYAXwBtADUAKQApACAALQAgAE0ATgBfAGoAbQBUADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA3AF8ATgBpAHQAcgBvAGcAZQBuAFQAcgBhAG4AcwBmAGUAcgByAGUAZABUAG8AUwB0AGEAZwBlADIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwBnAGUAbgAgAHQAcgBhAG4AcwBmAGUAcgByAGUAZAAgAHQAbwAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMgAgAE0ATQBTAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA3AF8ATgBpAHQAcgBvAGcAZQBuAFQAcgBhAG4AcwBmAGUAcgByAGUAZABUAG8AUwB0AGEAZwBlADIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AVABfAGoAbQBUADIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADcAXwBOAGkAdAByAG8AZwBlAG4AVAByAGEAbgBzAGYAZQByAHIAZQBkAFQAbwBTAHQAYQBnAGUAMgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADcAXwBOAGkAdAByAG8AZwBlAG4AVAByAGEAbgBzAGYAZQByAHIAZQBkAFQAbwBTAHQAYQBnAGUAMgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMQAuADEALgAzACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADcAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANwBfAE4AaQB0AHIAbwBnAGUAbgBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAVABvAFMAdABhAGcAZQAyAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA3AF8ATgBpAHQAcgBvAGcAZQBuAFQAcgBhAG4AcwBmAGUAcgByAGUAZABUAG8AUwB0AGEAZwBlADIAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAFQAXwB7AGoAbQAsAFQAPQAyAH0APQAoAE0ATgBfAHsAagBtAD0ANQAsAFQAPQAxAH0AXABcAHQAaQBtAGUAcwAoADEALQBGAHIAYQBjAEcAQQBTAE0AXwB7AG0APQA1AH0ALQBFAEYAXwB7AG0APQA1AH0AKQApAC0ATQBOAF8AewBqAG0ALABUAD0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA3AF8ATgBpAHQAcgBvAGcAZQBuAFQAcgBhAG4AcwBmAGUAcgByAGUAZABUAG8AUwB0AGEAZwBlADIAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBOAF8AagBtADUAVAAxAFwAIgAsAFwAIgBuAGkAdAByAG8AZwBlAG4AIABpAG4AIABNAE0AUwAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMQAgADoAIABrAGcAIABOAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAEcAQQBTAE0AXwBtADUAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABmAHIAbwBtACAAZAByAHkAbABvAHQAIABNAE0AUwAgADoAIABmAHIAYQBjAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAG0ANQBcACIALABcACIAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABkAHIAeQBsAG8AdAAgAE0ATQBTACAAOgAgAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AIABkAGUAcABvAHMAaQB0AGUAZABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBOAF8AagBtAFQAMwBcACIALABcACIAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAATQBNAFMAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADMAIAA6ACAAawBnACAATgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA4AF8AUwB0AGEAZwBlADMATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBcAG4ATgBpAHQAcgBvAGcAZQBuACAAaQBuACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAzACAATQBNAFMAXABuAE0ATgBfAGoAbQAxAFQAMwBcAG4AawBnACAATgBcAG4ATQBOAF8AewBqAG0APQAxACwAVAA9ADMAfQA9AEEARQBfAHsAagB9AFwAXAB0AGkAbQBlAHMAIABNAE0AUwBfAHsAagBtAD0AMQAsAFQAPQAzAH0AXABuAEEARQBfAGoAIAA9ACAAdABvAHQAYQBsACAAbgBpAHQAcgBvAGcAZQBuACAAZQB4AGMAcgBlAHQAZQBkACAAYgB5ACAAZQBhAGMAaAAgAGMAYQB0AHQAbABlACAAZwByAG8AdQBwACAAOgAgAGsAZwAgAE4AXABuAE0ATQBTAF8AagBtADEAVAAzACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAdABvACAAdABlAHIAdABpAGEAcgB5ACAAYQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgAHMAeQBzAHQAZQBtACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA4AF8AUwB0AGEAZwBlADMATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAEUAXwBqACwAIABNAE0AUwBfAGoAbQAxAFQAMwAsAFwAbgAgACAAIAAgAEEARQBfAGoAIAAqACAATQBNAFMAXwBqAG0AMQBUADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA4AF8AUwB0AGEAZwBlADMATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBpAHQAcgBvAGcAZQBuACAAaQBuACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAzACAATQBNAFMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADgAXwBTAHQAYQBnAGUAMwBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE4AXwBqAG0AMQBUADMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADgAXwBTAHQAYQBnAGUAMwBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AOABfAFMAdABhAGcAZQAzAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADEALgAxAC4AMwAsACAARQBxAHUAYQB0AGkAbwBuACAAKAA4ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADgAXwBTAHQAYQBnAGUAMwBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA4AF8AUwB0AGEAZwBlADMATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATgBfAHsAagBtAD0AMQAsAFQAPQAzAH0APQBBAEUAXwB7AGoAfQBcAFwAdABpAG0AZQBzACAATQBNAFMAXwB7AGoAbQA9ADEALABUAD0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA4AF8AUwB0AGEAZwBlADMATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAEUAXwBqAFwAIgAsAFwAIgB0AG8AdABhAGwAIABuAGkAdAByAG8AZwBlAG4AIABlAHgAYwByAGUAdABlAGQAIABiAHkAIABlAGEAYwBoACAAYwBhAHQAdABsAGUAIABnAHIAbwB1AHAAIAA6ACAAawBnACAATgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBNAFMAXwBqAG0AMQBUADMAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAdABvACAAdABlAHIAdABpAGEAcgB5ACAAYQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgAHMAeQBzAHQAZQBtACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBhAG4AdQByAGUAQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADQALgAxADoAIABCAGUAZQBmACAARgBlAGUAZABsAG8AdABcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANAAuADEALgAxAC4AOQAgAE0AYQBuAHUAcgBlACAAQQBwAHAAbABpAGUAZAAgAHQAbwAgAFMAbwBpAGwAcwBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxAFwAbgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHMAbwBpAGwAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMQAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBNAE4AUwBvAGkAbABfAHMAYwBvAHAAZQAxAFwAbgBrAGcAIABOAFwAbgBNAE4AUwBvAGkAbABfAHsAcwBjAG8AcABlADEAfQA9AFwAXABzAHUAbQBfAHsAagB9AFwAXABzAHUAbQBfAHsAbQB9AFwAXABzAHUAbQBfAHsAVAB9ACgATQBOAF8AewBqAG0AVAA9ADIALAAzAH0AXABcAHQAaQBtAGUAcwAoADEALQBFAEYAXwB7AG0AVAA9ADIALAAzAH0ALQBGAHIAYQBjAEcAQQBTAE0AXwB7AG0AVAA9ADIALAAzAH0AKQApAFwAXAB0AGkAbQBlAHMAIABQAEYAXABuAE0ATgBfAGoAbQBUADIAMwAgAD0AIABtAGEAcwBzACAAbwBmACAATgAgAGkAbgAgAHMAZQBjAG8AbgBkAGEAcgB5ACAAYQBuAGQAIAB0AGUAcgB0AGkAYQByAHkAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAE0ATQBTACAAcwB0AGEAZwBlAHMAIABhAHMAIABjAGEAbABjAHUAbABhAHQAZQBkACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAIAA6ACAAawBnACAATgBcAG4ARQBGAF8AbQBUADIAMwAgAD0AIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGUAYQBjAGgAIABNAE0AUwAgADoAIABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOAFwAbgBGAHIAYQBjAEcAQQBTAE0AXwBtAFQAMgAzACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAGEAbgBpAG0AYQBsACAAdwBhAHMAdABlACAATgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGkAbgAgAGUAYQBjAGgAIABNAE0AUwAgAGYAbwByACAAZQBhAGMAaAAgAGMAYQB0AHQAbABlACAAZwByAG8AdQBwACAAOgAgACgAawBnACAATgBIADMALQBOACAAKwAgAE4ATwB4AC0ATgApAC8AawBnACAATgBcAG4AUABGACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHMAbwBpAGwAIAB3AGkAdABoAGkAbgAgAHQAaABlACAAZgBlAGUAZABsAG8AdAAgAGIAbwB1AG4AZABhAHIAeQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMQBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBOAF8AagBtAFQAMgAzACwAIABFAEYAXwBtAFQAMgAzACwAIABGAHIAYQBjAEcAQQBTAE0AXwBtAFQAMgAzACwAIABQAEYALABcAG4AIAAgACAAIAAoAE0ATgBfAGoAbQBUADIAMwAgACoAIAAoADEAIAAtACAARQBGAF8AbQBUADIAMwAgAC0AIABGAHIAYQBjAEcAQQBTAE0AXwBtAFQAMgAzACkAKQAgACoAIABQAEYAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA5AF8AXwAxAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABzAG8AaQBsAHMAIABmAG8AcgAgAHMAYwBvAHAAZQAgADEAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMQBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADEAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATgBTAG8AaQBsAF8AcwBjAG8AcABlADEAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMQBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADEAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADEALgAxAC4AOQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA5AF8AXwAxAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATgBTAG8AaQBsAF8AewBzAGMAbwBwAGUAMQB9AD0AXABcAHMAdQBtAF8AewBqAH0AXABcAHMAdQBtAF8AewBtAH0AXABcAHMAdQBtAF8AewBUAH0AKABNAE4AXwB7AGoAbQBUAD0AMgAsADMAfQBcAFwAdABpAG0AZQBzACgAMQAtAEUARgBfAHsAbQBUAD0AMgAsADMAfQAtAEYAcgBhAGMARwBBAFMATQBfAHsAbQBUAD0AMgAsADMAfQApACkAXABcAHQAaQBtAGUAcwAgAFAARgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMQBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADEAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBOAF8AagBtAFQAMgAzAFwAIgAsAFwAIgBtAGEAcwBzACAAbwBmACAATgAgAGkAbgAgAHMAZQBjAG8AbgBkAGEAcgB5ACAAYQBuAGQAIAB0AGUAcgB0AGkAYQByAHkAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAE0ATQBTACAAcwB0AGEAZwBlAHMAIABhAHMAIABjAGEAbABjAHUAbABhAHQAZQBkACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAIAA6ACAAawBnACAATgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AbQBUADIAMwBcACIALABcACIAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABlAGEAYwBoACAATQBNAFMAIAA6ACAAawBnACAATgAyAE8ALQBOAC8AawBnACAATgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBHAEEAUwBNAF8AbQBUADIAMwBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAYQBuAGkAbQBhAGwAIAB3AGEAcwB0AGUAIABOACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAaQBuACAAZQBhAGMAaAAgAE0ATQBTACAAZgBvAHIAIABlAGEAYwBoACAAYwBhAHQAdABsAGUAIABnAHIAbwB1AHAAIAA6ACAAKABrAGcAIABOAEgAMwAtAE4AIAArACAATgBPAHgALQBOACkALwBrAGcAIABOAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEYAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHMAbwBpAGwAIAB3AGkAdABoAGkAbgAgAHQAaABlACAAZgBlAGUAZABsAG8AdAAgAGIAbwB1AG4AZABhAHIAeQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADMAXABuAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzACAAZQBtAGkAcwBzAGkAbwBuAHMAXABuAE0ATgBTAG8AaQBsAF8AcwBjAG8AcABlADMAXABuAGsAZwAgAE4AXABuAE0ATgBTAG8AaQBsAF8AewBzAGMAbwBwAGUAMwB9AD0AXABcAHMAdQBtAF8AewBqAH0AXABcAHMAdQBtAF8AewBtAH0AXABcAHMAdQBtAF8AewBUAH0AKABNAE4AXwB7AGoAbQBUAD0AMgAsADMAfQBcAFwAdABpAG0AZQBzACgAMQAtAEUARgBfAHsAbQBUAD0AMgAsADMAfQAtAEYAcgBhAGMARwBBAFMATQBfAHsAbQBUAD0AMgAsADMAfQApACkAXABcAHQAaQBtAGUAcwAoADEALQBQAEYAKQBcAG4ATQBOAF8AagBtAFQAMgAzACAAPQAgAG0AYQBzAHMAIABvAGYAIABOACAAaQBuACAAcwBlAGMAbwBuAGQAYQByAHkAIABhAG4AZAAgAHQAZQByAHQAaQBhAHIAeQAgAHQAcgBlAGEAdABtAGUAbgB0ACAATQBNAFMAIABzAHQAYQBnAGUAcwAgAGEAcwAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABmAG8AcgAgAG0AYQBuAHUAcgBlACAAbQBhAG4AYQBnAGUAbQBlAG4AdAAgADoAIABrAGcAIABOAFwAbgBFAEYAXwBtAFQAMgAzACAAPQAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZQBhAGMAaAAgAE0ATQBTACAAOgAgAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AXABuAEYAcgBhAGMARwBBAFMATQBfAG0AVAAyADMAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAYQBuAGkAbQBhAGwAIAB3AGEAcwB0AGUAIABOACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAaQBuACAAZQBhAGMAaAAgAE0ATQBTACAAZgBvAHIAIABlAGEAYwBoACAAYwBhAHQAdABsAGUAIABnAHIAbwB1AHAAIAA6ACAAKABrAGcAIABOAEgAMwAtAE4AIAArACAATgBPAHgALQBOACkALwBrAGcAIABOAFwAbgBQAEYAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbAAgAHcAaQB0AGgAaQBuACAAdABoAGUAIABmAGUAZQBkAGwAbwB0ACAAYgBvAHUAbgBkAGEAcgB5ACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA5AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAE4AXwBqAG0AVAAyADMALAAgAEUARgBfAG0AVAAyADMALAAgAEYAcgBhAGMARwBBAFMATQBfAG0AVAAyADMALAAgAFAARgAsAFwAbgAgACAAIAAgACgATQBOAF8AagBtAFQAMgAzACAAKgAgACgAMQAgAC0AIABFAEYAXwBtAFQAMgAzACAALQAgAEYAcgBhAGMARwBBAFMATQBfAG0AVAAyADMAKQApACAAKgAgACgAMQAgAC0AIABQAEYAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHMAbwBpAGwAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA5AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBOAFMAbwBpAGwAXwBzAGMAbwBwAGUAMwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA5AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMQAuADEALgA5ACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADIAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBOAFMAbwBpAGwAXwB7AHMAYwBvAHAAZQAzAH0APQBcAFwAcwB1AG0AXwB7AGoAfQBcAFwAcwB1AG0AXwB7AG0AfQBcAFwAcwB1AG0AXwB7AFQAfQAoAE0ATgBfAHsAagBtAFQAPQAyACwAMwB9AFwAXAB0AGkAbQBlAHMAKAAxAC0ARQBGAF8AewBtAFQAPQAyACwAMwB9AC0ARgByAGEAYwBHAEEAUwBNAF8AewBtAFQAPQAyACwAMwB9ACkAKQBcAFwAdABpAG0AZQBzACgAMQAtAFAARgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA5AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAAMgAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE4AXwBqAG0AVAAyADMAXAAiACwAXAAiAG0AYQBzAHMAIABvAGYAIABOACAAaQBuACAAcwBlAGMAbwBuAGQAYQByAHkAIABhAG4AZAAgAHQAZQByAHQAaQBhAHIAeQAgAHQAcgBlAGEAdABtAGUAbgB0ACAATQBNAFMAIABzAHQAYQBnAGUAcwAgAGEAcwAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABmAG8AcgAgAG0AYQBuAHUAcgBlACAAbQBhAG4AYQBnAGUAbQBlAG4AdAAgADoAIABrAGcAIABOAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBtAFQAMgAzAFwAIgAsAFwAIgBuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGUAYQBjAGgAIABNAE0AUwAgADoAIABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAEcAQQBTAE0AXwBtAFQAMgAzAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABhAG4AaQBtAGEAbAAgAHcAYQBzAHQAZQAgAE4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABpAG4AIABlAGEAYwBoACAATQBNAFMAIABmAG8AcgAgAGUAYQBjAGgAIABjAGEAdAB0AGwAZQAgAGcAcgBvAHUAcAAgADoAIAAoAGsAZwAgAE4ASAAzAC0ATgAgACsAIABOAE8AeAAtAE4AKQAvAGsAZwAgAE4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAARgBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbAAgAHcAaQB0AGgAaQBuACAAdABoAGUAIABmAGUAZQBkAGwAbwB0ACAAYgBvAHUAbgBkAGEAcgB5ACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADQALgAxADoAIABCAGUAZQBmACAARgBlAGUAZABsAG8AdABcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANAAuADEALgAxAC4ANQAgAE0AZQB0AGgAbwBkACAAMQAgAC0AIABNAGEAbgB1AHIAZQAgAEEAdABtAG8AcwBwAGgAZQByAGkAYwAgAEQAZQBwAG8AcwBpAHQAaQBvAG4AIABCAGUAZQBmACAARgBlAGUAZABsAG8AdABcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADUAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMAXABuAFQAbwB0AGEAbAAgAGEAbgBuAHUAYQBsACAAYQB0AG0AbwBzAHAAaABlAHIAaQBjACAAZABlAHAAbwBzAGkAdABpAG8AbgAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAG0AYQBuAHUAcgBlACAAbQBhAG4AYQBnAGUAbQBlAG4AdABcAG4ARQBfAE4AMgBPAGEAZABcAG4AdAAgAE4AMgBPAFwAbgBFAF8AewBOADIATwAsAGEAZAB9AD0AKABNAE0AUwBfAHsAQQBUAE0ATwBTAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsATgAyAE8AfQBcAFwAdABpAG0AZQBzACAAQwBfAHsATgAyAE8AfQApAFwAXAB0AGkAbQBlAHMAMQAwAF4AewAtADMAfQBcAG4ATQBNAFMAXwBBAFQATQBPAFMAIAA9ACAAbQBhAHMAcwAgAG8AZgAgAE4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABmAHIAbwBtACAATQBNAFMAIAA6ACAAawBnACAATgBcAG4ARQBGAF8ATgAyAE8AIAA9ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABhAHQAbQBvAHMAcABoAGUAcgBpAGMAIABkAGUAcABvAHMAaQB0AGkAbwBuACAAOgAgAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AXABuAEMAXwBOADIATwAgAD0AIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzACAAOgAgAHIAYQB0AGkAbwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0ATQBTAF8AQQBUAE0ATwBTACwAIABFAEYAXwBOADIATwAsACAAQwBfAE4AMgBPACwAXABuACAAIAAgACAAKABNAE0AUwBfAEEAVABNAE8AUwAgACoAIABFAEYAXwBOADIATwAgACoAIABDAF8ATgAyAE8AKQAgACoAIAAxADAAIABeACAALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABvAHQAYQBsACAAYQBuAG4AdQBhAGwAIABhAHQAbQBvAHMAcABoAGUAcgBpAGMAIABkAGUAcABvAHMAaQB0AGkAbwBuACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAbQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8ATgAyAE8AYQBkAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAxAC4AMQAuADUALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsATgAyAE8ALABhAGQAfQA9ACgATQBNAFMAXwB7AEEAVABNAE8AUwB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AE4AMgBPAH0AXABcAHQAaQBtAGUAcwAgAEMAXwB7AE4AMgBPAH0AKQBcAFwAdABpAG0AZQBzADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADUAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBNAFMAXwBBAFQATQBPAFMAXAAiACwAXAAiAG0AYQBzAHMAIABvAGYAIABOACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAZgByAG8AbQAgAE0ATQBTACAAOgAgAGsAZwAgAE4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAE4AMgBPAFwAIgAsAFwAIgBuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGEAdABtAG8AcwBwAGgAZQByAGkAYwAgAGQAZQBwAG8AcwBpAHQAaQBvAG4AIAA6ACAAawBnACAATgAyAE8ALQBOAC8AawBnACAATgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBfAE4AMgBPAFwAIgAsAFwAIgBmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzACAAOgAgAHIAYQB0AGkAbwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAagBcACIALAAgAFwAIgBwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGkAXAAiACwAIABcACIAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgByAFwAIgAsACAAXAAiAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMgBfAFYAbwBsAGEAdABpAGwAaQBzAGUAZABOAGkAdAByAG8AZwBlAG4ARgByAG8AbQBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AFwAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQAIABuAGkAdAByAG8AZwBlAG4AIABmAHIAbwBtACAAbQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0AFwAbgBNAE0AUwBfAEEAVABNAE8AUwBcAG4AawBnACAATgBcAG4ATQBNAFMAXwB7AEEAVABNAE8AUwB9AD0AXABcAHMAdQBtAF8AewBqAH0AXABcAHMAdQBtAF8AewBtAH0AXABcAHMAdQBtAF8AewBUAH0AKABNAE4AXwB7AGoAbQBUAH0AXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMARwBBAFMATQBfAHsAbQBUAH0AKQBcAG4ATQBOAF8AagBtAFQAIAA9ACAAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAAZQBhAGMAaAAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAATQBNAFMAIAAoAGUAeABjAGwAdQBkAGkAbgBnACAATQBOAF8AaQBqAG0AMQAzAFQAMgApACAAOgAgAGsAZwAgAE4AXABuAEYAcgBhAGMARwBBAFMATQBfAG0AVAAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAaQBuACAAZQBhAGMAaAAgAE0ATQBTACAAOgAgACgAawBnACAATgBIADMALQBOACAAKwAgAE4ATwB4AC0ATgApAC8AawBnACAATgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAyAF8AVgBvAGwAYQB0AGkAbABpAHMAZQBkAE4AaQB0AHIAbwBnAGUAbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBOAF8AagBtAFQALAAgAEYAcgBhAGMARwBBAFMATQBfAG0AVAAsAFwAbgAgACAAIAAgAE0ATgBfAGoAbQBUACAAKgAgAEYAcgBhAGMARwBBAFMATQBfAG0AVABcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADUAXwBfADIAXwBWAG8AbABhAHQAaQBsAGkAcwBlAGQATgBpAHQAcgBvAGcAZQBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBvAGwAYQB0AGkAbABpAHMAZQBkACAAbgBpAHQAcgBvAGcAZQBuACAAZgByAG8AbQAgAG0AYQBuAHUAcgBlACAAbQBhAG4AYQBnAGUAbQBlAG4AdABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMgBfAFYAbwBsAGEAdABpAGwAaQBzAGUAZABOAGkAdAByAG8AZwBlAG4ARgByAG8AbQBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE0AUwBfAEEAVABNAE8AUwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMgBfAFYAbwBsAGEAdABpAGwAaQBzAGUAZABOAGkAdAByAG8AZwBlAG4ARgByAG8AbQBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMgBfAFYAbwBsAGEAdABpAGwAaQBzAGUAZABOAGkAdAByAG8AZwBlAG4ARgByAG8AbQBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAxAC4AMQAuADUALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAyAF8AVgBvAGwAYQB0AGkAbABpAHMAZQBkAE4AaQB0AHIAbwBnAGUAbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADUAXwBfADIAXwBWAG8AbABhAHQAaQBsAGkAcwBlAGQATgBpAHQAcgBvAGcAZQBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATQBTAF8AewBBAFQATQBPAFMAfQA9AFwAXABzAHUAbQBfAHsAagB9AFwAXABzAHUAbQBfAHsAbQB9AFwAXABzAHUAbQBfAHsAVAB9ACgATQBOAF8AewBqAG0AVAB9AFwAXAB0AGkAbQBlAHMAIABGAHIAYQBjAEcAQQBTAE0AXwB7AG0AVAB9ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADUAXwBfADIAXwBWAG8AbABhAHQAaQBsAGkAcwBlAGQATgBpAHQAcgBvAGcAZQBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE4AXwBqAG0AVABcACIALABcACIAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAAZQBhAGMAaAAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAATQBNAFMAIAAoAGUAeABjAGwAdQBkAGkAbgBnACAATQBOAF8AaQBqAG0AMQAzAFQAMgApACAAOgAgAGsAZwAgAE4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMARwBBAFMATQBfAG0AVABcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGkAbgAgAGUAYQBjAGgAIABNAE0AUwAgADoAIAAoAGsAZwAgAE4ASAAzAC0ATgAgACsAIABOAE8AeAAtAE4AKQAvAGsAZwAgAE4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuACIAfQBdACwAIgBwAHIAbwBqAGUAYwB0AE4AYQBtAGUAcwAiADoAWwAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFYAYQBpAHIAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAIgAsACIAQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBIAGEAcgB2AGUAcwB0AEkAbgBkAGUAeAAiACwAIgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBSAGUAcwBpAGQAdQBlAEMAcgBvAHAAUgBhAHQAaQBvACIALAAiAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEMAYQBsAGMAdQBsAGEAdABlAEYAcgBhAGMAdABpAG8AbgBSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFYAUwBMAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBWAFMATABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AVgBTAEwAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBWAFMATABfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBWAFMATABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBWAFMATABfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0ATQBTAG0AMQBUADMAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0ATQBTAG0AMQBUADMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0ATQBTAG0AMQBUADMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAE0AUwBtADEAVAAzAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0ATQBTAG0AMQBUADMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBNAFMAbQAxAFQAMwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFMAdABhAGcAZQAxAE0ATQBTAE8AcAB0AGkAbwBuAHMAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFMAdABhAGcAZQAyAE0ATQBTAE8AcAB0AGkAbwBuAHMAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFMAdABhAGcAZQAzAE0ATQBTAE8AcAB0AGkAbwBuAHMAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwBlAHMAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAG4AaQBtAGEAbABDAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBuAGkAbQBhAGwAQwBoAGEAcgBhAGMAdABlAHIAaQBzAHQAaQBjAHMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAG4AaQBtAGEAbABDAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAG4AaQBtAGEAbABDAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAG4AaQBtAGEAbABDAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAaQBlAHQAUAByAG8AcABlAHIAdABpAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARABpAGUAdABQAHIAbwBwAGUAcgB0AGkAZQBzAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARABpAGUAdABQAHIAbwBwAGUAcgB0AGkAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAaQBlAHQAUAByAG8AcABlAHIAdABpAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAGkAZQB0AFAAcgBvAHAAZQByAHQAaQBlAHMAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAEMARgBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBDAEYAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAEMARgBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAEMARgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAEMARgBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARgByAGEAYwBOAFYAbwBsAGEAdABpAGwAaQBzAGUAZABfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARgByAGEAYwBOAFYAbwBsAGEAdABpAGwAaQBzAGUAZABfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEYAcgBhAGMATgBWAG8AbABhAHQAaQBsAGkAcwBlAGQAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARgByAGEAYwBOAFYAbwBsAGEAdABpAGwAaQBzAGUAZABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBGAHIAYQBjAE4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAF8ARABhAHQAYQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBVAG4AaQB0ACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMgBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBEAHIAeQBsAG8AdAAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAyAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEQAcgB5AGwAbwB0AF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADIAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARAByAHkAbABvAHQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMgBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBEAHIAeQBsAG8AdABfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMgBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBEAHIAeQBsAG8AdABfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADIAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARAByAHkAbABvAHQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAyAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEQAcgB5AGwAbwB0AF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAyAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEQAcgB5AGwAbwB0AF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANABfAFMAdABhAGcAZQAzAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA0AF8AUwB0AGEAZwBlADMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuAF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADQAXwBTAHQAYQBnAGUAMwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANABfAFMAdABhAGcAZQAzAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANABfAFMAdABhAGcAZQAzAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADQAXwBTAHQAYQBnAGUAMwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA0AF8AUwB0AGEAZwBlADMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA0AF8AUwB0AGEAZwBlADMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAUAByAG8AZAB1AGMAdABpAG8AbgAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA1AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAUAByAG8AZAB1AGMAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAUAByAG8AZAB1AGMAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA1AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA1AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABQAHIAbwBkAHUAYwB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8AXwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBfAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAF8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8AXwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8AXwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAF8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBfAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBfAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8AXwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMARAByAHkAbABvAHQAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8AXwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMARAByAHkAbABvAHQAXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8AXwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMARAByAHkAbABvAHQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8AXwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMARAByAHkAbABvAHQAXwBVAG4AaQB0ACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAF8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADIAXwBTAHQAYQBnAGUAMQBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAEQAcgB5AGwAbwB0AF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8AXwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMARAByAHkAbABvAHQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBfAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAyAF8AUwB0AGEAZwBlADEATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBEAHIAeQBsAG8AdABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8AXwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMARAByAHkAbABvAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBfAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAzAF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAF8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADMAXwBBAG4AbgB1AGEAbABOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8AXwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMwBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBfAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAzAF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBfAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAzAF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8AXwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMwBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAF8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADMAXwBBAG4AbgB1AGEAbABOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAF8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADMAXwBBAG4AbgB1AGEAbABOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBfAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA0AF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAFAAZQByAEgAZQBhAGQAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8AXwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANABfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBQAGUAcgBIAGUAYQBkAF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAF8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADQAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AUABlAHIASABlAGEAZABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBfAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA0AF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAFAAZQByAEgAZQBhAGQAXwBVAG4AaQB0ACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAF8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADQAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AUABlAHIASABlAGEAZABfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAF8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADQAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AUABlAHIASABlAGEAZABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAF8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADQAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AUABlAHIASABlAGEAZABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8AXwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANABfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBQAGUAcgBIAGUAYQBkAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8AXwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANQBfAE4AaQB0AHIAbwBnAGUAbgBJAG4AdABhAGsAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBfAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA1AF8ATgBpAHQAcgBvAGcAZQBuAEkAbgB0AGEAawBlAF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAF8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADUAXwBOAGkAdAByAG8AZwBlAG4ASQBuAHQAYQBrAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8AXwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANQBfAE4AaQB0AHIAbwBnAGUAbgBJAG4AdABhAGsAZQBfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8AXwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANQBfAE4AaQB0AHIAbwBnAGUAbgBJAG4AdABhAGsAZQBfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAF8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADUAXwBOAGkAdAByAG8AZwBlAG4ASQBuAHQAYQBrAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBfAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA1AF8ATgBpAHQAcgBvAGcAZQBuAEkAbgB0AGEAawBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBfAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA1AF8ATgBpAHQAcgBvAGcAZQBuAEkAbgB0AGEAawBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8AXwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANgBfAFMAdABhAGcAZQAyAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8AXwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANgBfAFMAdABhAGcAZQAyAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8AXwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANgBfAFMAdABhAGcAZQAyAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8AXwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANgBfAFMAdABhAGcAZQAyAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBVAG4AaQB0ACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAF8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADYAXwBTAHQAYQBnAGUAMgBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8AXwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANgBfAFMAdABhAGcAZQAyAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBfAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA2AF8AUwB0AGEAZwBlADIATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8AXwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANgBfAFMAdABhAGcAZQAyAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBfAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA3AF8ATgBpAHQAcgBvAGcAZQBuAFQAcgBhAG4AcwBmAGUAcgByAGUAZABUAG8AUwB0AGEAZwBlADIAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8AXwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANwBfAE4AaQB0AHIAbwBnAGUAbgBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAVABvAFMAdABhAGcAZQAyAF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAF8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADcAXwBOAGkAdAByAG8AZwBlAG4AVAByAGEAbgBzAGYAZQByAHIAZQBkAFQAbwBTAHQAYQBnAGUAMgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBfAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA3AF8ATgBpAHQAcgBvAGcAZQBuAFQAcgBhAG4AcwBmAGUAcgByAGUAZABUAG8AUwB0AGEAZwBlADIAXwBVAG4AaQB0ACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAF8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADcAXwBOAGkAdAByAG8AZwBlAG4AVAByAGEAbgBzAGYAZQByAHIAZQBkAFQAbwBTAHQAYQBnAGUAMgBfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAF8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADcAXwBOAGkAdAByAG8AZwBlAG4AVAByAGEAbgBzAGYAZQByAHIAZQBkAFQAbwBTAHQAYQBnAGUAMgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAF8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADcAXwBOAGkAdAByAG8AZwBlAG4AVAByAGEAbgBzAGYAZQByAHIAZQBkAFQAbwBTAHQAYQBnAGUAMgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8AXwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANwBfAE4AaQB0AHIAbwBnAGUAbgBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAVABvAFMAdABhAGcAZQAyAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8AXwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AOABfAFMAdABhAGcAZQAzAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8AXwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AOABfAFMAdABhAGcAZQAzAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8AXwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AOABfAFMAdABhAGcAZQAzAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8AXwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AOABfAFMAdABhAGcAZQAzAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBVAG4AaQB0ACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAF8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADgAXwBTAHQAYQBnAGUAMwBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8AXwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AOABfAFMAdABhAGcAZQAzAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBfAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA4AF8AUwB0AGEAZwBlADMATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8AXwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AOABfAFMAdABhAGcAZQAzAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGEAbgB1AHIAZQBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AYQBuAHUAcgBlAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMQBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADEAXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBhAG4AdQByAGUAQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA5AF8AXwAxAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGEAbgB1AHIAZQBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxAF8AVQBuAGkAdAAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGEAbgB1AHIAZQBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBhAG4AdQByAGUAQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA5AF8AXwAxAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AYQBuAHUAcgBlAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMQBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADEAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AYQBuAHUAcgBlAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMQBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADEAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGEAbgB1AHIAZQBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAzACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AYQBuAHUAcgBlAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADMAXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBhAG4AdQByAGUAQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA5AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGEAbgB1AHIAZQBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAzAF8AVQBuAGkAdAAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGEAbgB1AHIAZQBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBhAG4AdQByAGUAQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA5AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AYQBuAHUAcgBlAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AYQBuAHUAcgBlAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADMAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4AcwAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4AcwBfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADUAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAyAF8AVgBvAGwAYQB0AGkAbABpAHMAZQBkAE4AaQB0AHIAbwBnAGUAbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADUAXwBfADIAXwBWAG8AbABhAHQAaQBsAGkAcwBlAGQATgBpAHQAcgBvAGcAZQBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAFQAaQB0AGwAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMgBfAFYAbwBsAGEAdABpAGwAaQBzAGUAZABOAGkAdAByAG8AZwBlAG4ARgByAG8AbQBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8AVgBhAHIAaQBhAGIAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAyAF8AVgBvAGwAYQB0AGkAbABpAHMAZQBkAE4AaQB0AHIAbwBnAGUAbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBVAG4AaQB0ACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAyAF8AVgBvAGwAYQB0AGkAbABpAHMAZQBkAE4AaQB0AHIAbwBnAGUAbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBTAG8AdQByAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMgBfAFYAbwBsAGEAdABpAGwAaQBzAGUAZABOAGkAdAByAG8AZwBlAG4ARgByAG8AbQBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADUAXwBfADIAXwBWAG8AbABhAHQAaQBsAGkAcwBlAGQATgBpAHQAcgBvAGcAZQBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADUAXwBfADIAXwBWAG8AbABhAHQAaQBsAGkAcwBlAGQATgBpAHQAcgBvAGcAZQBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAEEAcgBnAHUAbQBlAG4AdABzACIAXQAsACIAbABvAGMAYQBsAGUAIgA6AHsAIgBsAGkAcwB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAcgBvAHcAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBjAG8AbAB1AG0AbgBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUABvAHMAaQB0AGkAbwBuAHMAIgA6AFsAMwBdACwAIgBkAGUAYwBpAG0AYQBsAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiAC4AIgAsACIAZABhAHQAZQBPAHIAZABlAHIAIgA6ACIARABNAFkAIgAsACIAYwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsACIAOgAiACQAIgAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbABMAGUAYQBkACIAOgB0AHIAdQBlACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAZQBwAEIAeQBTAHAAYQBjAGUAIgA6AGYAYQBsAHMAZQAsACIAcgBvAHcATABlAHQAdABlAHIAIgA6ACIAUgAiACwAIgBjAG8AbAB1AG0AbgBMAGUAdAB0AGUAcgAiADoAIgBDACIALAAiAHIAYwBMAGUAZgB0AEIAcgBhAGMAawBlAHQAIgA6ACIAWwAiACwAIgByAGMAUgBpAGcAaAB0AEIAcgBhAGMAawBlAHQAIgA6ACIAXQAiACwAIgBzAHQAYQB0AGUAbQBlAG4AdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGwAbwBjAGEAbABlAE4AYQBtAGUAIgA6ACIAZQBuAC0AdQBzACIAfQB9AA==</AFEJSONBlob>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
@@ -27490,19 +27471,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgACcARgByAHkAJwAgAHQAbwAgACcARAByAHkAJwAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA1ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBXAGUAdAAgAG8AcgAgAEQAcgB5ACAAWgBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAG4AdABhAG4AZQBcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIAB3AGUAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGgAaQBnAGgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGgAaQBnAGgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAdwBhAHIAbQAgAC8AIABjAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAvACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAIABhAG4AZAAgAGgAaQBnAGgAIAB0AGUAbQBwACAAYwBsAGEAcwBzAGUAcwAgAHQAbwAgAGEAYwBjAG8AbQBtAG8AZABhAHQAZQAgAGMAbABpAG0AYQB0AGUAIABzAGMAZQBuAGEAcgBpAG8AcwAgAGUAeABjAGwAdQBkAGUAZAAgAGIAeQAgAFYARQBFAFIARwAgAGMAcgBpAHQAZQByAGkAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGkAeABlAGQAIAB0AHkAcABvACAAaQBuACAATQBBAFQAIAB2AGEAbAB1AGUAIABmAG8AcgAgAHcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGMAaABhAG4AZwBlAGQAIAAxADAAIAB0AG8AIAAxADEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAbQBpAG4AIABhAG4AZAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAGYAbwByACAATQBBAFQALAAgAE0AQQBQACwAIABmAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByACwAIABlAGwAZQB2AGEAdABpAG8AbgAsACAATQBBAFAAOgBQAEUAVAAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQBzACAAZgByAG8AbQAgAHIAZQBhAGwAIABjAGwAaQBtAGEAdABlACAAZABhAHQAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAEEARgAgAGEAYwBjAGUAcAB0AHMAIAByAGEAaQBuAGYAYQBsAGwAIABhAHMAIABhACAAcAByAG8AeAB5ACAAZgBvAHIAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADEANgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAXAAiACwAIABcACIATQBBAFAAXAAiACwAIABcACIARgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgBcACIALAAgAFwAIgBFAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAEEAUAA6AFAARQBUAFwAIgAsACAAXAAiAE0AaQBuACAAdABlAG0AcABcACIALAAgAFwAIgBNAGEAeAAgAHQAZQBtAHAAXAAiACwAIABcACIATQBpAG4AIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIATQBhAHgAIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIATQBpAG4AIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AYQB4ACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGkAbgAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AYQB4ACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAG4AdABhAG4AZQBcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgA+ACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAPgAgADEAOAAgAEMAXAAiACwAIABcACIAPgAgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAyADAAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgA+ACAAMQAwADAAMAAgAG0AbQAgAC0AIABkIiAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADEAMAAwADAALgAwADAAMQAsACAAMgAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAD4AIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgA+ACAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgA+ACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdABlADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQQBUACAAPQAgAG0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFAAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABFAFQAIAA9ACAAcABvAHQAZQBuAHQAaQBhAGwAIABlAHYAYQBwAG8AdAByAGEAbgBzAHAAaQByAGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABNAEEAVAAgAG0AaQBuACAAYQBuAGQAIABNAEEAVAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAGUAZABpAGEAbgAgAEEAbgBuAHUAYQBsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAKABNAEEAVAApAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFQAXAAiACwAIABcACIATQBhAHgAIABNAEEAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIiAAMgA2ACAAQwBcACIALAAgADIANgAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIABcACIAMQA1ACAALQAgADIANQAgAEMAXAAiACwAIAAxADUALAAgADIANQAuADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIgADEANAAgAEMAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADQALgA5ADkAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAZQB4AHQAcgBhACAAUgBhAGkAbgBmAGEAbABsACAAbQBpAG4AIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGEAbABsACAAWgBvAG4AZQBcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgBcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGEAeABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAD4AIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAPgCjAygANdg43DXYR9wwACkAKwA12GDcNdhc3DXYVtw12FncIAA12GTcNdhO3DXYYdw12FLcNdhf3CAADiE12FzcNdhZ3DXYUdw12FbcNdhb3DXYVNwgADXYUNw12E7cNdhd3DXYTtw12FDcNdhW3DXYYdw12GbcXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAGQAbwBlAHMAIABuAG8AdAAgAG8AYwBjAHUAcgBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAZCKjAygANdg43DXYR9wwACkAKwA12GDcNdhc3DXYVtw12FncIAA12GTcNdhO3DXYYdw12FLcNdhf3CAADiE12FzcNdhZ3DXYUdw12FbcNdhb3DXYVNwgADXYUNw12E7cNdhd3DXYTtw12FDcNdhW3DXYYdw12GbcXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHMAIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBZAGUAcwAgAC0AIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AIAAtACAAbgBvAHQAIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABkAGEAdABhACAAcwBjAG8AcgBlAHMAIABmAG8AcgAgAHMAYwBvAHAAZQAgADMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAWABYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAYQB0AGEAIABzAG8AdQByAGMAZQBcACIALAAgAFwAIgBEAGEAdABhACAAcwBjAG8AcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAG4AdABlAHIAbgBhAHQAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAgAG8AcgAgAHIAZQBnAGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAAaQBuAHQAZQBuAHMAaQB0AHkAIABjAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgAGEAcABwAHIAbwB2AGUAZAAgAG0AZQB0AGgAbwBkAFwAIgAsACAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAGUAcgBpAGYAaQBlAGQAIABjAHIAZQBkAGUAbgB0AGkAYQBsACAAbQBhAHQAYwBoAGkAbgBnACAASQBTAE8AMQA0ADAANgA3AFwAIgAsACAANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuACAAIAAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgACcAQQBxAHUAYQBjAHUAbAB0AHUAcgBlACcAIAByAG8AdwAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAYQBzAHQAZQByAGkAcwBrAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgACcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQAnACwAIAAnAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAJwAgAGEAbgBkACAAJwBpAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAJwAgAGMAbwBsAHUAbQBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAdQBwAGwAaQBjAGEAdABlAGQAIAAnAG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlACcAIAByAG8AdwAgAHcAaQB0AGgAIABzAGEAbQBlACAARQBGACAAZgBvAHIAIABsAG8AdwAgAGEAbgBkACAAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQAgAGQAYQB0AGEAIAB0AGgAYQB0ACAAaQBzACAAYwBvAG0AbQBvAG4AIABhAGMAcgBvAHMAcwAgAGEAbABsACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlAHMAXABuAEUAeABjAGUAbAAgAG0AbwBkAHUAbABlACAAbgBhAG0AZQA6ACAAUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlADoAIABOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBcAG4ARgByAGEAYwBXAEUAVABNAE0AUwBpACAAPQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4AKABUAGEAYgBsAGUAIABBADUALgA1AC4AMQAwAC4AMgAgAGkAcwAgAHIAZQBmAGUAcgBlAG4AYwBlAGQAIABpAG4AIABOAEkAUgAgAGIAdQB0ACAAMQAgAGkAcwAgAHUAcwBlAGQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgA1AGEAXwAzACwAIAAzAC4AQgAuADUAYwBfADMALAAgADMALgBCAC4ANQBkAF8AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAxACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXABuAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTACAAPQAgADAALgAwADIAIAAoAEcAZwAgAE4ALwBHAGcAIABhAHAAcABsAGkAZQBkACkAIAAoAEMAUwAgAEUARgAsACAAcwBvAHUAcgBjAGUAIABJAFAAQwBDACAAKAAyADAAMQA5ACkAKQAgAFwAbgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgA1AGEAXwAzACwAIAAzAC4AQgAuADUAYwBfADMALAAgADMALgBCAC4ANQBkAF8AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAIAAwAC4AMAAwADUAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsACAAMAAuADAAMAA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAgADAALgAwADAAMQA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcABcACIALAAgADAALgAwADAANAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAIABjAGEAbgBlAFwAIgAsACAAMAAuADAAMQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAMAAuADAAMAA1ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAMAAuADAAMAA2ADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXABuAFQAYQBiAGwAZQAgADUALgAxADIAIABBAGQAZABpAHQAaQBvAG4AYQBsACAAcwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAHIAZQBsAGEAdABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgADUALgAxADIAIABBAGQAZABpAHQAaQBvAG4AYQBsACAAcwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAHIAZQBsAGEAdABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVgBhAGkAcgBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE0AUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAAVABhAGIAbABlACAANQAuADEAMgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAOQAsACAAMwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB5AG0AYgBvAGwAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0ACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgACgAbQA9ADEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADIAXAAiACwAIABcACIATABpAHEAdQBpAGQAIABzAHkAcwB0AGUAbQBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwAgACgAbQA9ADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADMAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAG0APQAzACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGEAXAAiACwAIABcACIAUwB1AG0AcAAgAGEAbgBkACAAZABpAHMAcABlAHIAcwBhAGwAIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBTAHUAbQBwACAAYQBuAGQAIABkAGkAcwBwAGUAcgBzAGEAbAAgAHMAeQBzAHQAZQBtACAAKABtAD0AMwBhACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGIAXAAiACwAIABcACIARAByAGEAaQBuAHMAIAB0AG8AIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAEQAcgBhAGkAbgBzACAAdABvACAAcABhAGQAZABvAGMAawAgACgAbQA9ADMAYgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIANABcACIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAIAAoAG0APQA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA1AFwAIgAsACAAXAAiAEQAcgB5AGwAbwB0ACAAKABmAGUAZQBkACAAcABhAGQAKQBcACIALAAgAFwAIgBEAHIAeQBsAG8AdAAgACgAZgBlAGUAZAAgAHAAYQBkACkAIAAoAG0APQA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA2AFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQAgACgAbQA9ADYAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADcAXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwAgACgAbQA9ADcAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADgAXAAiACwAIABcACIARABlAGUAcAAgAGwAaQB0AHQAZQByAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgAgACgAbQA9ADgAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADkAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQAgACgAbQA9ADkAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMABcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwAgACgAbQA9ADEAMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnACAAKABtAD0AMQAxACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADEAYQBcACIALAAgAFwAIgBCAGUAbAB0ACAAbQBhAG4AdQByAGUAIAByAGUAbQBvAHYAYQBsAFwAIgAsACAAXAAiAEIAZQBsAHQAIABtAGEAbgB1AHIAZQAgAHIAZQBtAG8AdgBhAGwAIAAoAG0APQAxADEAYQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAGIAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABzAHQAbwByAGUAZAAgAGkAbgAgAGgAbwB1AHMAZQBcACIALAAgAFwAIgBNAGEAbgB1AHIAZQAgAHMAdABvAHIAZQBkACAAaQBuACAAaABvAHUAcwBlACAAKABtAD0AMQAxAGIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAKABtAD0AMQAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADMAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAG0APQAxADMAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEANABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAIAAoAG0APQAxADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgA8AHQAPgA8AHMAPgBcACIAIAAmAFwAbgAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAUwBVAEIAUwBUAEkAVABVAFQARQAoAEMAZQBsAGwALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQAsAFwAIgBcACIAKQAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAZQBsAGkAbQBpAHQAZQByACwAXAAiADwALwBzAD4APABzAD4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgACYAXABuACAAIAAgACAAIAAgACAAIABcACIAPAAvAHMAPgA8AC8AdAA+AFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC8ALwBzAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQB2AGcAVABlAG0AcAAsAGEAdgBnAFIAYQBpAG4ALABmAHIAbwBzAHQARABhAHkAcwAsAGUAbABlAHYALABtAGEAcABfAHAAZQB0ACwAXABuACAAIAAgACAAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkALABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQAsAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBQAEUAVABBAHIAcgBhAHkALABtAGEAeABQAEUAVABBAHIAcgBhAHkALABcAG4AIAAgACAAIABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkAKQA8AD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPAA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAPAA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAD4APQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApADwAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAPgA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQA8AD0AbQBhAHAAXwBwAGUAdAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFAARQBUAEEAcgByAGEAeQApAD4APQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQA8AD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAPgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAEkAdABlAG0AQQByAHIAYQB5ACwAIABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAEMAcgBpAHQAZQByAGkAYQAxACwAIABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACwAIABbAE0AdQBsAHQAaQBwAGwAaQBlAHIAXQAsACAAWwBDAHIAaQB0AGUAcgBpAGEAMgBdACwAWwBDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAXQAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABtAHUAbAB0AGkAcABsAGkAZQByACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsADEALABNAHUAbAB0AGkAcABsAGkAZQByACkALABcAG4AIAAgACAAIABxAHUAYQBuAHQAaQB0AHkALAAgAFEAdQBhAG4AdABpAHQAeQAqAE0AdQBsAHQAaQBwAGwAaQBlAHIALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMQAsAC0ALQAoAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADEAKQAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAyACwASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABDAHIAaQB0AGUAcgBpAGEAMgApACwAMQAsAC0ALQAoAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAyACkAKQAsAFwAbgAgACAAIAAgAFMAVQBNAFAAUgBPAEQAVQBDAFQAKABjAHIAaQB0AGUAcgBpAGEAMQAqAGMAcgBpAHQAZQByAGkAYQAyACoAcQB1AGEAbgB0AGkAdAB5ACkAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQA8ACAAUwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAD4AIABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAE0AQQBYACgAMAAsAGwAYQBzAHQAWQBlAGEAcgAtAGYAaQByAHMAdABZAGUAYQByACsAMQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAIAAvACoAaABlAGwAcABlAHIAOgAgAGUAbgBkACAAZABhAHQAZQAgAGYAbwByACAAYQAgAHIAZQBwAG8AcgB0AGkAbgBnACAAcABlAHIAaQBvAGQAIABzAHQAYQByAHQAaQBuAGcAIABhAHQAIABhACAAZwBpAHYAZQBuACAAZABhAHQAZQAqAC8AXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALAAgAC8AKgBvAG4AbAB5ACAAbgBlAGUAZAAgAHQAbwAgAGwAbwBvAGsAIABiAGEAYwBrACAAMwA2ADUAIABkAGEAeQBzACgAbQBhAHgAIABvAHYAZQByAGwAYQBwACAAdwBpAG4AZABvAHcAKQAqAC8AXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBhACAAZQBuAGQAcwAgAGIAZQBmAG8AcgBlACAAUwAsAGkAdAAgAGMAYQBuACcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABuAGUAeAB0ACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApADwAUwApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBiACAAcwB0AGEAcgB0AHMAIABhAGYAdABlAHIAIABFACwAaQB0ACAAYwBhAG4AJwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAHAAcgBlAHYAaQBvAHUAcwAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQA+AEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbgAsAE0AQQBYACgAMAAsAGwAYQBzAHQAWQBlAGEAcgAtAGYAaQByAHMAdABZAGUAYQByACsAMQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AHIAcwAsAFMARQBRAFUARQBOAEMARQAoAG4ALAAxACwAZgBpAHIAcwB0AFkAZQBhAHIALAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzACwARABBAFQARQAoAHkAcgBzACwAbQAsAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBuAGQAcwAsAE0AQQBQACgAcwB0AGEAcgB0AHMALABQAGUAcgBpAG8AZABFAG4AZAApACwAXABuACAAIAAgACAAIAAgACAAIAB0AGEAZwAsAEkARgAoAHMAdABhAHIAdABzAD0AUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAIgAgACgAVABoAGkAcwAgAHIAZQBwAG8AcgB0AGkAbgBnACAAYwB5AGMAbABlACkAXAAiACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwBUAGUAeAB0ACwAVABFAFgAVAAoAHMAdABhAHIAdABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBuAGQAcwBUAGUAeAB0ACwAVABFAFgAVAAoAGUAbgBkAHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABuAD0AMAAsAFwAIgBcACIALABIAFMAVABBAEMASwAoAHMAdABhAHIAdABzAFQAZQB4AHQAIAAmACAAXAAiACAAdABvACAAXAAiACAAJgAgAGUAbgBkAHMAVABlAHgAdAAgACYAIAB0AGEAZwApACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuAD0ATABBAE0AQgBEAEEAKABGAHUAbgBjAHQAaQBvAG4ALAAgAFQARQBYAFQAQgBFAEYATwBSAEUAKABGAE8AUgBNAFUATABBAFQARQBYAFQAKABGAHUAbgBjAHQAaQBvAG4AKQAsACAAXAAiACgAXAAiACkAKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5ACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5ACwAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAPQBcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAgAD0AIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQA9AFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5AD0ASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5AD0AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAgACsAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQAPgAwACwAIAAxACwAIAAwACkAXABuACAAIAAgACAAKQApADsAXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AQwBhAGwAYwB1AGwAYQB0AGUASABhAHIAdgBlAHMAdABJAG4AZABlAHgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABDAHIAbwBwAFQAeQBwAGUALAAgAEMAcgBvAHAAVAB5AHAAZQBBAHIAcgBhAHkALAAgAFIAZQBzAGkAZAB1AGUAQwByAG8AcABSAGEAdABpAG8AQQByAHIAYQB5ACwAXABuACAAIAAgACAAMQAvACgAMQArAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAQwByAG8AcABUAHkAcABlACwAIABDAHIAbwBwAFQAeQBwAGUAQQByAHIAYQB5ACwAIABSAGUAcwBpAGQAdQBlAEMAcgBvAHAAUgBhAHQAaQBvAEEAcgByAGEAeQApACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEMAYQBsAGMAdQBsAGEAdABlAFIAZQBzAGkAZAB1AGUAQwByAG8AcABSAGEAdABpAG8AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABIAGEAcgB2AGUAcwB0AEkAbgBkAGUAeAAsAFwAbgAgACAAIAAgACgAMQAtAEgAYQByAHYAZQBzAHQASQBuAGQAZQB4ACkALwBIAGEAcgB2AGUAcwB0AEkAbgBkAGUAeABcAG4AKQA7AFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEMAYQBsAGMAdQBsAGEAdABlAEYAcgBhAGMAdABpAG8AbgBSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAG8AdABhAGwAUgBlAHMAaQBkAHUAZQAsACAAQQBtAG8AdQBuAHQAUgBlAG0AbwB2AGUAZAAsAFwAbgAgACAAIAAgACgAQQBtAG8AdQBuAHQAUgBlAG0AbwB2AGUAZAAqADEAMABeADMAKQAvACgAVABvAHQAYQBsAFIAZQBzAGkAZAB1AGUAKgAxADAAXgAzACkAXABuACkAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AVgBTAEwAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAbABvAHMAdAAgAGkAbgAgAHQAaABlACAAcAByAGkAbQBhAHIAeQAgAE0ATQBTAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AVgBTAEwAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAZQBlAGQAbABvAHQAIAAtACAARgByAGEAYwB0AGkAbwBuACAAbwBmACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIABsAG8AcwB0ACAAZAB1AHIAaQBuAGcAIABzAHQAbwByAGEAZwBlACAAaQBuACAAdABoAGUAIABwAHIAaQBtAGEAcgB5ACAAcwB5AHMAdABlAG0AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AVgBTAEwAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAUwBMAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFYAUwBMAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFYAUwBMAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAxAC4AMgAuADMAIABDAE8ATgBTAFQAQQBOAFQAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBWAFMATABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBWAFMATABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADUAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAE0AUwBtADEAVAAzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAHQAbwAgAGUAYQBjAGgAIAB0AGUAcgB0AGkAYQByAHkAIABzAHkAcwB0AGUAbQAgAGEAcwBzAHUAbQBlAGQAIAB0AGgAYQB0ACAAMgAgAHAAZQByACAAYwBlAG4AdAAgAGkAcwAgAHIAdQBuACAALQAgAG8AZgBmACAAZgByAG8AbQAgAHQAaABlACAAZgBlAGUAZAAgAHAAYQBkAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAE0AUwBtADEAVAAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAHQAbwAgAGUAYQBjAGgAIAB0AGUAcgB0AGkAYQByAHkAIABzAHkAcwB0AGUAbQAgAGEAcwBzAHUAbQBlAGQAIAB0AGgAYQB0ACAAMgAgAHAAZQByACAAYwBlAG4AdAAgAGkAcwAgAHIAdQBuACAALQAgAG8AZgBmACAAZgByAG8AbQAgAHQAaABlACAAZgBlAGUAZAAgAHAAYQBkAC4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBNAFMAbQAxAFQAMwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBNAFMAbQAxAFQAMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAE0AUwBtADEAVAAzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0ATQBTAG0AMQBUADMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADEALgAyAC4AMwAgAEMATwBOAFMAVABBAE4AVABTAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0ATQBTAG0AMQBUADMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBNAFMAbQAxAFQAMwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADAAMgApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXABuAEEAcwBoACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAG0AYQBuAHUAcgBlAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHMAaAAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABtAGEAbgB1AHIAZQAuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAxAC4AMgAuADMAIABDAE8ATgBTAFQAQQBOAFQAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADAALgAxADYAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAFwAbgBNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbAAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAcABvAHQAZQBuAHQAaQBhAGwALgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBCADAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAG0AMwAgAEMASAA0ACAALwAgAGsAZwAgAFYAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAxAC4AMgAuADMAIABDAE8ATgBTAFQAQQBOAFQAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADAALgAxADkAKQA7AFwAbgBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AUwB0AGEAZwBlADEATQBNAFMATwBwAHQAaQBvAG4AcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADEALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAbABvAHQAIAAoAGYAZQBlAGQAIABwAGEAZAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBTAHQAYQBnAGUAMgBNAE0AUwBPAHAAdABpAG8AbgBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAAMQAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAATQBNAFMAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFMAdABhAGcAZQAzAE0ATQBTAE8AcAB0AGkAbwBuAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAAxACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwBlAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAbwBtAGUAcwB0AGkAYwBcACIAOwAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAHgAcABvAHIAdAAgAG0AaQBkACAAZgBlAGQAXAAiADsAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQB4AHAAbwByAHQAIABsAG8AbgBnACAAZgBlAGQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4AMQAuADEAOgAgAEIAZQBlAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIAAtACAARAB1AHIAYQB0AGkAbwBuACAAbwBmACAAcwB0AGEAeQAgACgAZABhAHkAcwApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAEQAdQByAGEAdABpAG8AbgAgAG8AZgAgAHMAdABhAHkAIAAoAGQAYQB5AHMAKQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgAxAC4AMQA6ACAAQgBlAGUAZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAC0AIABEAHUAcgBhAHQAaQBvAG4AIABvAGYAIABzAHQAYQB5ACAAKABkAGEAeQBzACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAZQBkAGwAbwB0ACAAdAB5AHAAZQBcACIALAAgAFwAIgBMAGUAbgBnAHQAaAAgAG8AZgAgAFMAdABhAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAbwBtAGUAcwB0AGkAYwBcACIALAAgAFwAIgAxAC0AOAAwACAAZABhAHkAcwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBpAGQALQBmAGUAZABcACIALAAgAFwAIgA4ADEALQAyADAAMAAgAGQAYQB5AHMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAbwBuAGcALQBmAGUAZABcACIALAAgAFwAIgAyADAAMQArACAAZABhAHkAcwBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAG4AaQBtAGEAbABDAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwBcAG4AVABhAGIAbABlACAAQQAuADEALgAxAC4AMgA6ACAAQgBlAGUAZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAC0AIABBAG4AaQBtAGEAbAAgAGMAaABhAHIAYQBjAHQAZQByAGkAcwB0AGkAYwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBuAGkAbQBhAGwAQwBoAGEAcgBhAGMAdABlAHIAaQBzAHQAaQBjAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEIAZQBlAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIAAtACAAQQBuAGkAbQBhAGwAIABjAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAG4AaQBtAGEAbABDAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAbgBpAG0AYQBsAEMAaABhAHIAYQBjAHQAZQByAGkAcwB0AGkAYwBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AMQAuADIAOgAgAEIAZQBlAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIAAtACAAQQBuAGkAbQBhAGwAIABjAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAG4AaQBtAGEAbABDAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AdgBlAGQAIABmAGUAZQBkAGwAbwB0ACAAdAB5AHAAZQBzACAAdABvACAAYQAgAHMAZQBwAGEAcgBhAHQAZQAgAGMAbwBsAHUAbQBuACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAGEAbQBlAGQAIAAnAGMAaABhAHIAYQBjAHQAZQByAGkAcwB0AGkAYwAnACAAYwBvAGwAdQBtAG4AIAAtACAAbwByAGkAZwBpAG4AYQBsACAAaABhAHMAIABoAGUAYQBkAGUAcgAgACcAVQBuAGkAdAAnACAAdwBoAGkAYwBoACAAYwBvAHYAZQByAHMAIAB0AHcAbwAgAGMAbwBsAHUAbQBuAHMAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBuAGkAbQBhAGwAQwBoAGEAcgBhAGMAdABlAHIAaQBzAHQAaQBjAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAwACwAIAA3ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAZQBkAGwAbwB0ACAAdAB5AHAAZQBcACIALAAgAFwAIgBDAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAXAAiACwAIABcACIAVQBuAGkAdABcACIALAAgAFwAIgAyADAAMAA1AC0AMgAwADAAOQBcACIALAAgAFwAIgAyADAAMQAwAC0AMgAwADEANABcACIALAAgAFwAIgAyADAAMQA1AC0AMgAwADEAOQBcACIALAAgAFwAIgAyADAAMgAwAC0AMgAwADIAMwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABvAG0AZQBzAHQAaQBjAFwAIgAsACAAXAAiAEQAYQB5AHMAIABvAG4AIABmAGUAZQBkAFwAIgAsACAAXAAiAGQAYQB5AHMAXAAiACwAIAA3ADAALAAgADcAMAAsACAANwAwACwAIAA3ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABvAG0AZQBzAHQAaQBjAFwAIgAsACAAXAAiAEYAZQBlAGQAIABpAG4AdABhAGsAZQBcACIALAAgAFwAIgBrAGcAIABEAE0ALwBkAGEAeQBcACIALAAgADEAMAAuADAALAAgADEAMAAuADAALAAgADEAMAAuADQALAAgADEAMAAuADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABvAG0AZQBzAHQAaQBjAFwAIgAsACAAXAAiAE4AIAByAGUAdABlAG4AdABpAG8AbgBcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAIABvAGYAIABpAG4AdABhAGsAZQBcACIALAAgADIAMQAuADEALAAgADIAMAAuADQALAAgADIAMAAuADQALAAgADIAMAAuADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBpAGQALQBmAGUAZABcACIALAAgAFwAIgBEAGEAeQBzACAAbwBuACAAZgBlAGUAZABcACIALAAgAFwAIgBkAGEAeQBzAFwAIgAsACAAMQAxADUALAAgADEAMQA1ACwAIAAxADIAMAAsACAAMQA1ADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBpAGQALQBmAGUAZABcACIALAAgAFwAIgBGAGUAZQBkACAAaQBuAHQAYQBrAGUAXAAiACwAIABcACIAawBnACAARABNAC8AZABhAHkAXAAiACwAIAAxADEALgAyACwAIAAxADAALgA4ACwAIAAxADAALgA4ACwAIAAxADAALgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AaQBkAC0AZgBlAGQAXAAiACwAIABcACIATgAgAHIAZQB0AGUAbgB0AGkAbwBuAFwAIgAsACAAXAAiAHAAZQByACAAYwBlAG4AdAAgAG8AZgAgAGkAbgB0AGEAawBlAFwAIgAsACAAMQAyAC4ANQAsACAAMQAyAC4ANwAsACAAMQAyAC4ANwAsACAAMQAyAC4ANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AbgBnAC0AZgBlAGQAXAAiACwAIABcACIARABhAHkAcwAgAG8AbgAgAGYAZQBlAGQAXAAiACwAIABcACIAZABhAHkAcwBcACIALAAgADIANQAwACwAIAAyADUAMAAsACAAMgA1ADAALAAgADIANQAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAbwBuAGcALQBmAGUAZABcACIALAAgAFwAIgBGAGUAZQBkACAAaQBuAHQAYQBrAGUAXAAiACwAIABcACIAawBnACAARABNAC8AZABhAHkAXAAiACwAIAA5AC4AMAAsACAAOAAuADUALAAgADgALgAyACwAIAA4AC4AMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AbgBnAC0AZgBlAGQAXAAiACwAIABcACIATgAgAHIAZQB0AGUAbgB0AGkAbwBuAFwAIgAsACAAXAAiAHAAZQByACAAYwBlAG4AdAAgAG8AZgAgAGkAbgB0AGEAawBlAFwAIgAsACAANgAuADYALAAgADcALgAwACwAIAA3AC4AMAAsACAANwAuADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARABpAGUAdABQAHIAbwBwAGUAcgB0AGkAZQBzAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADEALgAzADoAIABCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAEQAaQBlAHQAIABwAHIAbwBwAGUAcgB0AGkAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARABpAGUAdABQAHIAbwBwAGUAcgB0AGkAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAEQAaQBlAHQAIABwAHIAbwBwAGUAcgB0AGkAZQBzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAaQBlAHQAUAByAG8AcABlAHIAdABpAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAaQBlAHQAUAByAG8AcABlAHIAdABpAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADEALgAzADoAIABCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAEQAaQBlAHQAIABwAHIAbwBwAGUAcgB0AGkAZQBzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAaQBlAHQAUAByAG8AcABlAHIAdABpAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAAnAEMAbwBuAHYAZQByAHQAZQBkACAAdABvACAAZgByAGEAYwB0AGkAbwBuACAAYwBvAGwAdQBtAG4AIABhAG4AZAAgAGMAbwBuAHYAZQByAHQAZQBkACAATgBEAEYAIABhAG4AZAAgAEUAdABoAGUAcgAgAGUAeAB0AHIAYQBjAHQAIAB2AGEAbAB1AGUAcwAgAHQAbwAgAGYAcgBhAGMAdABpAG8AbgBzAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AbwB2AGUAZAAgAGYAZQBlAGQAbABvAHQAIAB0AHkAcABlAHMAIAB0AG8AIABhACAAcwBlAHAAYQByAGEAdABlACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAaQBlAHQAUAByAG8AcABlAHIAdABpAGUAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADMALAAgADgALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBlAGQAbABvAHQAIAB0AHkAcABlAFwAIgAsACAAXAAiAE4AdQB0AHIAaQBlAG4AdAAgAGEAbgBhAGwAeQBzAGkAcwBcACIALAAgAFwAIgBVAG4AaQB0AFwAIgAsACAAXAAiADIAMAAwADUALQAyADAAMAA5AFwAIgAsACAAXAAiADIAMAAxADAALQAyADAAMQA0AFwAIgAsACAAXAAiADIAMAAxADUALQAyADAAMQA5AFwAIgAsACAAXAAiADIAMAAyADAALQAyADAAMgAzAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHQAZQBkACAAdABvACAAZgByAGEAYwB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAG8AbQBlAHMAdABpAGMAXAAiACwAIABcACIARAByAHkAIABtAGEAdAB0AGUAcgAgAGQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAMAAuADgAMQAsACAAMAAuADgAMQAsACAAMAAuADgAMQAsACAAMAAuADgAMQAsACAAMAAuADgAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAG8AbQBlAHMAdABpAGMAXAAiACwAIABcACIAQwByAHUAZABlACAAcAByAG8AdABlAGkAbgBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIAAwAC4AMQA0ACwAIAAwAC4AMQA0ACwAIAAwAC4AMQA0ACwAIAAwAC4AMQA0ACwAIAAwAC4AMQA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAbwBtAGUAcwB0AGkAYwBcACIALAAgAFwAIgBOAEQARgBcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAXAAiACwAIAAyADMALgAwACwAIAAyADIALgAwACwAIAAyADIALgAwACwAIAAyADIALgAwACwAIAAwAC4AMgAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAbwBtAGUAcwB0AGkAYwBcACIALAAgAFwAIgBFAHQAaABlAHIAIABFAHgAdAByAGEAYwB0AFwAIgAsACAAXAAiAHAAZQByACAAYwBlAG4AdABcACIALAAgADQALgA1ACwAIAA0AC4ANQAsACAANAAuADgALAAgADQALgA4ACwAIAAwAC4AMAA0ADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBpAGQALQBmAGUAZABcACIALAAgAFwAIgBEAHIAeQAgAG0AYQB0AHQAZQByACAAZABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIAAwAC4AOAAxACwAIAAwAC4AOAAxACwAIAAwAC4AOAAxACwAIAAwAC4AOAAxACwAIAAwAC4AOAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AaQBkAC0AZgBlAGQAXAAiACwAIABcACIAQwByAHUAZABlACAAcAByAG8AdABlAGkAbgBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIAAwAC4AMQAzACwAIAAwAC4AMQAyADUALAAgADAALgAxADIALAAgADAALgAxADIALAAgADAALgAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBpAGQALQBmAGUAZABcACIALAAgAFwAIgBOAEQARgBcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAXAAiACwAIAAyADQALgAwACwAIAAyADIALgAwACwAIAAyADIALgAwACwAIAAyADIALgAwACwAIAAwAC4AMgAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AaQBkAC0AZgBlAGQAXAAiACwAIABcACIARQB0AGgAZQByACAARQB4AHQAcgBhAGMAdABcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAXAAiACwAIAA1AC4AMAAsACAANQAuADAALAAgADUALgAwACwAIAA1AC4AMAAsACAAMAAuADAANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AbgBnAC0ARgBlAGQAXAAiACwAIABcACIARAByAHkAIABtAGEAdAB0AGUAcgAgAGQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAMAAuADgAMQAsACAAMAAuADgAMQAsACAAMAAuADgAMQAsACAAMAAuADgAMQAsACAAMAAuADgAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AbgBnAC0ARgBlAGQAXAAiACwAIABcACIAQwByAHUAZABlACAAcAByAG8AdABlAGkAbgBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIAAwAC4AMQAzACwAIAAwAC4AMQAyADUALAAgADAALgAxADIALAAgADAALgAxADIALAAgADAALgAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABvAG4AZwAtAEYAZQBkAFwAIgAsACAAXAAiAE4ARABGAFwAIgAsACAAXAAiAHAAZQByACAAYwBlAG4AdABcACIALAAgADIANAAuADAALAAgADIANAAuADAALAAgADIANAAuADAALAAgADIANAAuADAALAAgADAALgAyADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABvAG4AZwAtAEYAZQBkAFwAIgAsACAAXAAiAEUAdABoAGUAcgAgAEUAeAB0AHIAYQBjAHQAXAAiACwAIABcACIAcABlAHIAIABjAGUAbgB0AFwAIgAsACAANQAuADAALAAgADUALgAwACwAIAA1AC4ANQAsACAANQAuADUALAAgADAALgAwADUANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBDAEYAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4AMQAuADQAOgAgAEIAZQBlAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIAAtACAATQBDAEYAcwAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQBUACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAEMARgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBlAGUAZABsAG8AdAAgAC0AIABNAEMARgBzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AQwBGAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBDAEYAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgAxAC4ANAA6ACAAQgBlAGUAZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAC0AIABNAEMARgBzACAAKABmAHIAYQBjAHQAaQBvAG4AKQAgACgATQBDAEYAaQBtAFQAKQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAEMARgBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHUAcABsAGkAYwBhAHQAZQBkACAATgBTAFcAIAB2AGEAbAB1AGUAcwAgAGYAbwByACAAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAE4AVAAgAGEAbgBkACAAVABBAFMAIABjAG8AbAB1AG0AbgBzACAAdwBpAHQAaAAgACcAbgBvACAAZABhAHQAYQAnACAAdgBhAGwAdQBlAHMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgACcATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuACcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABNAE0AUwAgAG4AYQBtAGUAcwAgAHQAaABhAHQAIABtAGEAdABjAGgAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAEMARgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAxADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAVABcACIALAAgAFwAIgBNAE0AUwAgAG0AXAAiACwAIABcACIATgBTAFcAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAUQBMAEQAXAAiACwAIABcACIATgBUAFwAIgAsACAAXAAiAFMAQQBcACIALAAgAFwAIgBWAEkAQwBcACIALAAgAFwAIgBXAEEAXAAiACwAIABcACIAVABBAFMAXAAiACwAIABcACIATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAaQBtAGEAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAbABvAHQAIAAoAEYAZQBlAGQAcABhAGQAKQBcACIALAAgADAALgAwADEALAAgADAALgAwADEALAAgADAALgAwADMALAAgAFwAIgBOAG8AIABkAGEAdABhAFwAIgAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAXAAiAE4AbwAgAGQAYQB0AGEAXAAiACwAIABcACIARAByAHkAbABvAHQAIAAoAGYAZQBlAGQAIABwAGEAZAApAFwAIgA7ACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBjAG8AbgBkAGEAcgB5AFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAIAAoAFMAdABvAGMAawBwAGkAbABlACkAXAAiACwAIAAwAC4AMAAyACwAIAAwAC4AMAAyACwAIAAwAC4AMAAyACwAIABcACIATgBvACAAZABhAHQAYQBcACIALAAgADAALgAwADIALAAgADAALgAwADIALAAgADAALgAwADIALAAgAFwAIgBOAG8AIABkAGEAdABhAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiADsAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAGMAbwBuAGQAYQByAHkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAUABhAHMAcwBpAHYAZQAgAFcAaQBuAGQAcgBvAHcAKQBcACIALAAgADAALgAwADEALAAgADAALgAwADEALAAgADAALgAwADEALAAgAFwAIgBOAG8AIABkAGEAdABhAFwAIgAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAXAAiAE4AbwAgAGQAYQB0AGEAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIAOwAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAGUAYwBvAG4AZABhAHIAeQBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgAgAHQAbwAgAHMAbwBpAGwAXAAiACwAIAAwACwAIAAwACwAIAAwACwAIABcACIATgBvACAAZABhAHQAYQBcACIALAAgADAALAAgADAALAAgADAALAAgAFwAIgBOAG8AIABkAGEAdABhAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgA7ACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQByAHQAaQBhAHIAeQBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AIAAoAEUAZgBmAGwAdQBlAG4AdAAgAHAAbwBuAGQAKQBcACIALAAgADAALgA3ADUALAAgADAALgA3ADUALAAgADAALgA3ADcALAAgAFwAIgBOAG8AIABkAGEAdABhAFwAIgAsACAAMAAuADcANQAsACAAMAAuADcANQAsACAAMAAuADcANwAsACAAXAAiAE4AbwAgAGQAYQB0AGEAXAAiACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBcAG4AVABhAGIAbABlACAAQQAuADEALgAxAC4ANQA6ACAAQgBlAGUAZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAC0AIABOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAARQBGAHMAIAAoAEUARgBtAFQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGUAZQBkAGwAbwB0ACAALQAgAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABFAEYAcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AMQAuADUAOgAgAEIAZQBlAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIAAtACAATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAEUARgBzACAAKABFAEYAbQBUACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAJwBOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AJwAgAGMAbwBsAHUAbQBuACAAdwBpAHQAaAAgAE0ATQBTACAAbgBhAG0AZQBzACAAdABoAGEAdAAgAG0AYQB0AGMAaAAgAE4ASQBSACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAVABcACIALAAgAFwAIgBNAE0AUwAgAG0AXAAiACwAIABcACIARQBGAG0AVAAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApAFwAIgAsACAAXAAiAE4ASQBSACAAZABlAGYAaQBuAGkAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUAByAGkAbQBhAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGwAbwB0ACAAKABGAGUAZQBkAHAAYQBkACkAXAAiACwAIAAwAC4AMAAwADUANAAsACAAXAAiAEQAcgB5AGwAbwB0ACAAKABmAGUAZQBkACAAcABhAGQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAGMAbwBuAGQAYQByAHkAXAAiACwAIABcACIAUwBvAGwAaQBkACAAUwB0AG8AcgBhAGcAZQAgACgAUwB0AG8AYwBrAHAAaQBsAGUAKQBcACIALAAgADAALgAwADAANQAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBjAG8AbgBkAGEAcgB5AFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAFAAYQBzAHMAaQB2AGUAIABXAGkAbgBkAHIAbwB3ACkAXAAiACwAIAAwAC4AMAAxACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAGMAbwBuAGQAYQByAHkAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AIAB0AG8AIABzAG8AaQBsAFwAIgAsACAAMAAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAcgB0AGkAYQByAHkAXAAiACwAIABcACIAVQBuAGMAbwB2AGUAcgBlAGQAIABhAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuACAAKABFAGYAZgBsAHUAZQBuAHQAIABQAG8AbgBkACkAXAAiACwAIAAwACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBGAHIAYQBjAE4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADEALgA2ADoAIABCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABiAHkAIABNAE0AUwAgACgARgByAGEAYwBHAEEAUwBNAG0AVAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARgByAGEAYwBOAFYAbwBsAGEAdABpAGwAaQBzAGUAZABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBlAGUAZABsAG8AdAAgAC0AIABGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAYgB5ACAATQBNAFMAIAAoAEYAcgBhAGMARwBBAFMATQBtAFQAKQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBGAHIAYQBjAE4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARgByAGEAYwBOAFYAbwBsAGEAdABpAGwAaQBzAGUAZABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADEALgA2ADoAIABCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABiAHkAIABNAE0AUwAgACgARgByAGEAYwBHAEEAUwBNAG0AVAApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEYAcgBhAGMATgBWAG8AbABhAHQAaQBsAGkAcwBlAGQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAJwBOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AJwAgAGMAbwBsAHUAbQBuACAAdwBpAHQAaAAgAE0ATQBTACAAbgBhAG0AZQBzACAAdABoAGEAdAAgAG0AYQB0AGMAaAAgAE4ASQBSACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEYAcgBhAGMATgBWAG8AbABhAHQAaQBsAGkAcwBlAGQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIABUAFwAIgAsACAAXAAiAE0ATQBTACAAbQBcACIALAAgAFwAIgBGAHIAYQBjAEcAQQBTAE0AbQBUACAAKABrAGcAIABOAEgAMwAtAE4AIAArACAATgBPAHgALQBOACkALwBrAGcAIABOAFwAIgAsACAAXAAiAE4ASQBSACAAZABlAGYAaQBuAGkAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUAByAGkAbQBhAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGwAbwB0ACAAKABGAGUAZQBkAHAAYQBkACkAXAAiACwAIAAwAC4ANgAsACAAXAAiAEQAcgB5AGwAbwB0ACAAKABmAGUAZQBkACAAcABhAGQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAGMAbwBuAGQAYQByAHkAXAAiACwAIABcACIAUwBvAGwAaQBkACAAUwB0AG8AcgBhAGcAZQAgACgAUwB0AG8AYwBrAHAAaQBsAGUAKQBcACIALAAgADAALgAyADUALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAGUAYwBvAG4AZABhAHIAeQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABQAGEAcwBzAGkAdgBlACAAVwBpAG4AZAByAG8AdwApAFwAIgAsACAAMAAuADQALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAGUAYwBvAG4AZABhAHIAeQBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgAgAHQAbwAgAHMAbwBpAGwAXAAiACwAIAAwACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQByAHQAaQBhAHIAeQBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AIAAoAEUAZgBmAGwAdQBlAG4AdAAgAHAAbwBuAGQAKQBcACIALAAgADAALgAzADUALAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADQALgAxADoAIABCAGUAZQBmACAARgBlAGUAZABsAG8AdABcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANAAuADEALgAxAC4AMQAgAE0AZQB0AGgAbwBkACAAMQAgAC0AIABNAGEAbgB1AHIAZQAgAE0AZQB0AGgAYQBuAGUAIABCAGUAZQBmACAARgBlAGUAZABsAG8AdABcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBcAG4AVABvAHQAYQBsACAAYQBuAG4AdQBhAGwAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAbQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0AFwAbgBFAF8AQwBIADQAXABuAHQAIABDAEgANABcAG4AewBFAH0AXwB7AEMASAA0AH0APQBcAFwAcwB1AG0AXwB7AGoAfQBcAFwAcwB1AG0AXwB7AG0AfQBcAFwAcwB1AG0AXwB7AFQAfQAoAEQAXwB7AGoAfQBcAFwAdABpAG0AZQBzACAATQBfAHsAagBtAFQAfQBcAFwAdABpAG0AZQBzACAATgBfAHsAagB9ACkAXABcAHQAaQBtAGUAcwAxADAAXgB7AC0AMwB9AFwAbgBEAF8AagAgAD0AIABsAGUAbgBnAHQAaAAgAG8AZgAgAHMAdABhAHkAIABvAGYAIABlAGEAYwBoACAAYwBhAHQAdABsAGUAIABnAHIAbwB1AHAAIAA6ACAAZABhAHkAcwBcAG4ATQBfAGoAbQBUACAAPQAgAG0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgByAG8AbQAgAG0AYQBuAHUAcgBlACAAcABlAHIAIABjAGEAdAB0AGwAZQAgAGcAcgBvAHUAcAAsACAATQBNAFMALAAgAGEAbgBkACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAA6ACAAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXABuAE4AXwBqACAAPQAgAG4AdQBtAGIAZQByAHMAIABvAGYAIABiAGUAZQBmACAAYwBhAHQAdABsAGUAIABpAG4AIABlAGEAYwBoACAAZwByAG8AdQBwACAAOgAgAGgAZQBhAGQAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEQAXwBqACwAIABNAF8AagBtAFQALAAgAE4AXwBqACwAXABuACAAIAAgACAAKABEAF8AagAgACoAIABNAF8AagBtAFQAIAAqACAATgBfAGoAKQAgACoAIAAxADAAIABeACAALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBUAG8AdABhAGwAIABhAG4AbgB1AGEAbAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAEMASAA0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBIADQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMQAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB7AEUAfQBfAHsAQwBIADQAfQA9AFwAXABzAHUAbQBfAHsAagB9AFwAXABzAHUAbQBfAHsAbQB9AFwAXABzAHUAbQBfAHsAVAB9ACgARABfAHsAagB9AFwAXAB0AGkAbQBlAHMAIABNAF8AewBqAG0AVAB9AFwAXAB0AGkAbQBlAHMAIABOAF8AewBqAH0AKQBcAFwAdABpAG0AZQBzADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAF8AagBcACIALABcACIAbABlAG4AZwB0AGgAIABvAGYAIABzAHQAYQB5ACAAbwBmACAAZQBhAGMAaAAgAGMAYQB0AHQAbABlACAAZwByAG8AdQBwACAAOgAgAGQAYQB5AHMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AXwBqAG0AVABcACIALABcACIAbQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAbQBhAG4AdQByAGUAIABwAGUAcgAgAGMAYQB0AHQAbABlACAAZwByAG8AdQBwACwAIABNAE0AUwAsACAAYQBuAGQAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADoAIABrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBfAGoAXAAiACwAXAAiAG4AdQBtAGIAZQByAHMAIABvAGYAIABiAGUAZQBmACAAYwBhAHQAdABsAGUAIABpAG4AIABlAGEAYwBoACAAZwByAG8AdQBwACAAOgAgAGgAZQBhAGQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMgBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBEAHIAeQBsAG8AdABcAG4AUAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADEAIABNAE0AUwBcAG4ATQBfAGoAbQA1AFQAMQBcAG4AawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXABuAE0AXwB7AGoAbQA9ADUALABUAD0AMQB9AD0AVgBTAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAEIATwBcAFwAdABpAG0AZQBzACAATQBNAFMAXwB7AG0APQA1ACwAVAA9ADEAfQBcAFwAdABpAG0AZQBzACAATQBDAEYAXwB7AGkAbQA9ADUAfQBcAFwAdABpAG0AZQBzACAAXABcAHIAaABvAFwAbgBWAFMAXwBqACAAPQAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAAaQBuACAAZQBhAGMAaAAgAGcAcgBvAHUAcAAgADoAIABrAGcALwBoAGUAYQBkAC8AZABhAHkAXABuAEIATwAgAD0AIABlAG0AaQBzAHMAaQBvAG4AcwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAOgAgAG0AMwAgAEMASAA0AC8AawBnACAAVgBTAFwAbgBNAE0AUwBfAG0ANQBUADEAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIABpAG4AIABwAHIAaQBtAGEAcgB5ACAAcwB5AHMAdABlAG0AIABkAHIAeQBsAG8AdAAgAE0ATQBTACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4ATQBDAEYAXwBpAG0ANQAgAD0AIABtAGUAdABoAGEAbgBlACAAYwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlACAAYQBuAGQAIABkAHIAeQBsAG8AdAAgAHMAeQBzAHQAZQBtACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4AcgBoAG8AIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIAA6ACAAawBnAC8AbQAzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADIAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARAByAHkAbABvAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVgBTAF8AagAsACAAQgBPACwAIABNAE0AUwBfAG0ANQBUADEALAAgAE0AQwBGAF8AaQBtADUALAAgAHIAaABvACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAATQBDAEYAXwBpAG0ANQAsACAASQBGACgASQBTAE4AVQBNAEIARQBSACgATQBDAEYAXwBpAG0ANQApACwAIABNAEMARgBfAGkAbQA1ACwAIAAwACkALABcAG4AIAAgACAAIAAgACAAVgBTAF8AagAgACoAIABCAE8AIAAqACAATQBNAFMAXwBtADUAVAAxACAAKgAgAE0AQwBGAF8AaQBtADUAIAAqACAAcgBoAG8AXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADIAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARAByAHkAbABvAHQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAxACAATQBNAFMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADIAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARAByAHkAbABvAHQAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwBqAG0ANQBUADEAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADIAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARAByAHkAbABvAHQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMgBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBEAHIAeQBsAG8AdABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMQAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADIAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMgBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBEAHIAeQBsAG8AdABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMgBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBEAHIAeQBsAG8AdABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwB7AGoAbQA9ADUALABUAD0AMQB9AD0AVgBTAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAEIATwBcAFwAdABpAG0AZQBzACAATQBNAFMAXwB7AG0APQA1ACwAVAA9ADEAfQBcAFwAdABpAG0AZQBzACAATQBDAEYAXwB7AGkAbQA9ADUAfQBcAFwAdABpAG0AZQBzACAAXABcAHIAaABvAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAyAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEQAcgB5AGwAbwB0AF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAUwBfAGoAXAAiACwAXAAiAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAAaQBuACAAZQBhAGMAaAAgAGcAcgBvAHUAcAAgADoAIABrAGcALwBoAGUAYQBkAC8AZABhAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIATwBcACIALABcACIAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbAAgADoAIABtADMAIABDAEgANAAvAGsAZwAgAFYAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBNAFMAXwBtADUAVAAxAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAGkAbgAgAHAAcgBpAG0AYQByAHkAIABzAHkAcwB0AGUAbQAgAGQAcgB5AGwAbwB0ACAATQBNAFMAIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEMARgBfAGkAbQA1AFwAIgAsAFwAIgBtAGUAdABoAGEAbgBlACAAYwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlACAAYQBuAGQAIABkAHIAeQBsAG8AdAAgAHMAeQBzAHQAZQBtACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcgBoAG8AXAAiACwAXAAiAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAOgAgAGsAZwAvAG0AMwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAaQBcACIALAAgAFwAIgBzAHQAYQB0AGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBcAG4AUAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADIAIABNAE0AUwBcAG4ATQBfAGoAbQBUADIAXABuAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAbgBNAF8AewBqAG0AVAA9ADIAfQA9ACgAMQAtAFYAUwBMACkAXABcAHQAaQBtAGUAcwAgAFYAUwBfAHsAagB9AFwAXAB0AGkAbQBlAHMAIABCAE8AXABcAHQAaQBtAGUAcwAgAE0ATQBTAF8AewBtAFQAPQAyAH0AXABcAHQAaQBtAGUAcwAgAE0AQwBGAF8AewBpAG0AfQBcAFwAdABpAG0AZQBzACAAXABcAHIAaABvAFwAbgBWAFMATAAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAGwAbwBzAHQAIABkAHUAcgBpAG4AZwAgAHMAdABvAHIAYQBnAGUAIABpAG4AIAB0AGgAZQAgAHAAcgBpAG0AYQByAHkAIABzAHkAcwB0AGUAbQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAFYAUwBfAGoAIAA9ACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIABpAG4AIABlAGEAYwBoACAAZwByAG8AdQBwACAAOgAgAGsAZwAvAGgAZQBhAGQALwBkAGEAeQBcAG4AQgBPACAAPQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAcABvAHQAZQBuAHQAaQBhAGwAIAA6ACAAbQAzACAAQwBIADQALwBrAGcAIABWAFMAXABuAE0ATQBTAF8AbQBUADIAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIABpAG4AIABlAGEAYwBoACAAcwBlAGMAbwBuAGQAYQByAHkAIABzAHkAcwB0AGUAbQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAE0AQwBGAF8AaQBtACAAPQAgAG0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIABhAG4AZAAgAE0ATQBTACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4AcgBoAG8AIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIAA6ACAAawBnAC8AbQAzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVgBTAEwALAAgAFYAUwBfAGoALAAgAEIATwAsACAATQBNAFMAXwBtAFQAMgAsACAATQBDAEYAXwBpAG0ALAAgAHIAaABvACwAXABuACAAIAAgACAAKAAxACAALQAgAFYAUwBMACkAIAAqACAAVgBTAF8AagAgACoAIABCAE8AIAAqACAATQBNAFMAXwBtAFQAMgAgACoAIABNAEMARgBfAGkAbQAgACoAIAByAGgAbwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAyACAATQBNAFMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwBqAG0AVAAyAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAzACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAF8AewBqAG0AVAA9ADIAfQA9ACgAMQAtAFYAUwBMACkAXABcAHQAaQBtAGUAcwAgAFYAUwBfAHsAagB9AFwAXAB0AGkAbQBlAHMAIABCAE8AXABcAHQAaQBtAGUAcwAgAE0ATQBTAF8AewBtAFQAPQAyAH0AXABcAHQAaQBtAGUAcwAgAE0AQwBGAF8AewBpAG0AfQBcAFwAdABpAG0AZQBzACAAXABcAHIAaABvAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA3ACwAIAAyACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAUwBMAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAGwAbwBzAHQAIABkAHUAcgBpAG4AZwAgAHMAdABvAHIAYQBnAGUAIABpAG4AIAB0AGgAZQAgAHAAcgBpAG0AYQByAHkAIABzAHkAcwB0AGUAbQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAUwBfAGoAXAAiACwAXAAiAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAAaQBuACAAZQBhAGMAaAAgAGcAcgBvAHUAcAAgADoAIABrAGcALwBoAGUAYQBkAC8AZABhAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIATwBcACIALABcACIAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbAAgADoAIABtADMAIABDAEgANAAvAGsAZwAgAFYAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBNAFMAXwBtAFQAMgBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIABpAG4AIABlAGEAYwBoACAAcwBlAGMAbwBuAGQAYQByAHkAIABzAHkAcwB0AGUAbQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQwBGAF8AaQBtAFwAIgAsAFwAIgBtAGUAdABoAGEAbgBlACAAYwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlACAAYQBuAGQAIABNAE0AUwAgADoAIABmAHIAYQBjAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHIAaABvAFwAIgAsAFwAIgBkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgADoAIABrAGcALwBtADMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGkAXAAiACwAIABcACIAcwB0AGEAdABlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADQAXwBTAHQAYQBnAGUAMwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXABuAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAzACAATQBNAFMAXABuAE0AXwBqAG0AMQBUADMAXABuAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAbgBNAF8AewBqAG0APQAxACwAVAA9ADMAfQA9AFYAUwBfAHsAagB9AFwAXAB0AGkAbQBlAHMAIABCAE8AXABcAHQAaQBtAGUAcwAgAE0ATQBTAF8AewBtAD0AMQAsAFQAPQAzAH0AXABcAHQAaQBtAGUAcwAgAE0AQwBGAF8AewBpAG0APQAxAH0AXABcAHQAaQBtAGUAcwAgAFwAXAByAGgAbwBcAG4AVgBTAF8AagAgAD0AIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgByAG8AbQAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAGkAbgAgAGUAYQBjAGgAIABnAHIAbwB1AHAAIAA6ACAAawBnAC8AaABlAGEAZAAvAGQAYQB5AFwAbgBCAE8AIAA9ACAAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbAAgADoAIABtADMAIABDAEgANAAvAGsAZwAgAFYAUwBcAG4ATQBNAFMAXwBtADEAVAAzACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAdABvACAAdABlAHIAdABpAGEAcgB5ACAAYQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgAHMAeQBzAHQAZQBtACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4ATQBDAEYAXwBpAG0AMQAgAD0AIABtAGUAdABoAGEAbgBlACAAYwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlACAAYQBuAGQAIABhAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuACAAcwB5AHMAdABlAG0AIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAbgByAGgAbwAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgADoAIABrAGcALwBtADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANABfAFMAdABhAGcAZQAzAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABWAFMAXwBqACwAIABCAE8ALAAgAE0ATQBTAF8AbQAxAFQAMwAsACAATQBDAEYAXwBpAG0AMQAsACAAcgBoAG8ALABcAG4AIAAgACAAIABWAFMAXwBqACAAKgAgAEIATwAgACoAIABNAE0AUwBfAG0AMQBUADMAIAAqACAATQBDAEYAXwBpAG0AMQAgACoAIAByAGgAbwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADQAXwBTAHQAYQBnAGUAMwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAzACAATQBNAFMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADQAXwBTAHQAYQBnAGUAMwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwBqAG0AMQBUADMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADQAXwBTAHQAYQBnAGUAMwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANABfAFMAdABhAGcAZQAzAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMQAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADQAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANABfAFMAdABhAGcAZQAzAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANABfAFMAdABhAGcAZQAzAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwB7AGoAbQA9ADEALABUAD0AMwB9AD0AVgBTAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAEIATwBcAFwAdABpAG0AZQBzACAATQBNAFMAXwB7AG0APQAxACwAVAA9ADMAfQBcAFwAdABpAG0AZQBzACAATQBDAEYAXwB7AGkAbQA9ADEAfQBcAFwAdABpAG0AZQBzACAAXABcAHIAaABvAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA0AF8AUwB0AGEAZwBlADMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAUwBfAGoAXAAiACwAXAAiAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAAaQBuACAAZQBhAGMAaAAgAGcAcgBvAHUAcAAgAGoAIAA6ACAAawBnAC8AaABlAGEAZAAvAGQAYQB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAE8AXAAiACwAXAAiAGUAbQBpAHMAcwBpAG8AbgBzACAAcABvAHQAZQBuAHQAaQBhAGwAIAA6ACAAbQAzACAAQwBIADQALwBrAGcAIABWAFMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATQBTAF8AbQAxAFQAMwBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIAB0AG8AIAB0AGUAcgB0AGkAYQByAHkAIABhAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuACAAcwB5AHMAdABlAG0AIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEMARgBfAGkAbQAxAFwAIgAsAFwAIgBtAGUAdABoAGEAbgBlACAAYwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlACAAYQBuAGQAIABhAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuACAAcwB5AHMAdABlAG0AIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgByAGgAbwBcACIALABcACIAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIAA6ACAAawBnAC8AbQAzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBpAFwAIgAsACAAXAAiAHMAdABhAHQAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA1AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABQAHIAbwBkAHUAYwB0AGkAbwBuAFwAbgBWAG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAIABwAHIAbwBkAHUAYwB0AGkAbwBuAFwAbgBWAFMAXwBqAFwAbgBrAGcALwBoAGUAYQBkAC8AZABhAHkAXABuAFYAUwBfAHsAagB9AD0ASQBfAHsAagB9AFwAXAB0AGkAbQBlAHMAKAAxAC0ARABNAEQAXwB7AGoAfQApAFwAXAB0AGkAbQBlAHMAKAAxAC0AQQApAFwAbgBJAF8AagAgAD0AIABkAHIAeQAgAG0AYQB0AHQAZQByACAAaQBuAHQAYQBrAGUAIABmAG8AcgAgAGUAYQBjAGgAIABnAHIAbwB1AHAAIAA6ACAAawBnACAARABNAC8AaABlAGEAZAAvAGQAYQB5AFwAbgBEAE0ARABfAGoAIAA9ACAAZAByAHkAIABtAGEAdAB0AGUAcgAgAGQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAIABmAG8AcgAgAGUAYQBjAGgAIABnAHIAbwB1AHAAIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAbgBBACAAPQAgAGEAcwBoACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAG0AYQBuAHUAcgBlACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA1AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABQAHIAbwBkAHUAYwB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEkAXwBqACwAIABEAE0ARABfAGoALAAgAEEALABcAG4AIAAgACAAIABJAF8AagAgACoAIAAoADEAIAAtACAARABNAEQAXwBqACkAIAAqACAAKAAxACAALQAgAEEAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAUwBfAGoAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcALwBoAGUAYQBkAC8AZABhAHkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAA1ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAFMAXwB7AGoAfQA9AEkAXwB7AGoAfQBcAFwAdABpAG0AZQBzACgAMQAtAEQATQBEAF8AewBqAH0AKQBcAFwAdABpAG0AZQBzACgAMQAtAEEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAUAByAG8AZAB1AGMAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAF8AagBcACIALABcACIAZAByAHkAIABtAGEAdAB0AGUAcgAgAGkAbgB0AGEAawBlACAAZgBvAHIAIABlAGEAYwBoACAAZwByAG8AdQBwACAAagAgADoAIABrAGcAIABEAE0ALwBoAGUAYQBkAC8AZABhAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQATQBEAF8AagBcACIALABcACIAZAByAHkAIABtAGEAdAB0AGUAcgAgAGQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAIABmAG8AcgAgAGUAYQBjAGgAIABnAHIAbwB1AHAAIABqACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBcACIALABcACIAYQBzAGgAIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAbQBhAG4AdQByAGUAIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAF8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANAAuADEAOgAgAEIAZQBlAGYAIABGAGUAZQBkAGwAbwB0AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA0AC4AMQAuADEALgAzACAATQBlAHQAaABvAGQAIAAxACAALQAgAE0AYQBuAHUAcgBlACAARABpAHIAZQBjAHQAIABOADIATwAgAEIAZQBlAGYAIABGAGUAZQBkAGwAbwB0AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBcAG4AVABvAHQAYQBsACAAYQBuAG4AdQBhAGwAIABkAGkAcgBlAGMAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAIABzAHkAcwB0AGUAbQBzAFwAbgBFAF8ATgAyAE8AZABpAHIAXABuAHQAIABOADIATwBcAG4ARQBfAHsATgAyAE8ALABkAGkAcgB9AD0AXABcAHMAdQBtAF8AewBqAH0AXABcAHMAdQBtAF8AewBtAH0AXABcAHMAdQBtAF8AewBUAH0AKABNAE4AXwB7AGoAbQBUAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAagBtAH0AXABcAHQAaQBtAGUAcwAgAEMAXwB7AE4AMgBPAH0AKQBcAFwAdABpAG0AZQBzADEAMABeAHsALQAzAH0AXABuAE0ATgBfAGoAbQBUACAAPQAgAG4AaQB0AHIAbwBnAGUAbgAgAHAAZQByACAAYwBhAHQAdABsAGUAIABnAHIAbwB1AHAALAAgAE0ATQBTACAAYQBuAGQAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADoAIABrAGcAIABOAFwAbgBFAEYAXwBqAG0AIAA9ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABNAE0AUwAgADoAIABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOAFwAbgBDAF8ATgAyAE8AIAA9ACAAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwAgADoAIAByAGEAdABpAG8AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAE4AXwBqAG0AVAAsACAARQBGAF8AagBtACwAIABDAF8ATgAyAE8ALABcAG4AIAAgACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgATQBOAF8AagBtAFQALAAgAEUARgBfAGoAbQAsACAAQwBfAE4AMgBPACkAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAbwB0AGEAbAAgAGEAbgBuAHUAYQBsACAAZABpAHIAZQBjAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAbQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0ACAAcwB5AHMAdABlAG0AcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAE4AMgBPAGQAaQByAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAxAC4AMQAuADMALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsATgAyAE8ALABkAGkAcgB9AD0AXABcAHMAdQBtAF8AewBqAH0AXABcAHMAdQBtAF8AewBtAH0AXABcAHMAdQBtAF8AewBUAH0AKABNAE4AXwB7AGoAbQBUAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAagBtAH0AXABcAHQAaQBtAGUAcwAgAEMAXwB7AE4AMgBPAH0AKQBcAFwAdABpAG0AZQBzADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBOAF8AagBtAFQAXAAiACwAXAAiAG4AaQB0AHIAbwBnAGUAbgAgAHAAZQByACAAYwBhAHQAdABsAGUAIABnAHIAbwB1AHAALAAgAE0ATQBTACAAYQBuAGQAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADoAIABrAGcAIABOAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBqAG0AXAAiACwAXAAiAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAATQBNAFMAIAA6ACAAawBnACAATgAyAE8ALQBOAC8AawBnACAATgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBfAE4AMgBPAFwAIgAsAFwAIgBmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzACAAOgAgAHIAYQB0AGkAbwBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAyAF8AUwB0AGEAZwBlADEATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBEAHIAeQBsAG8AdABcAG4ATgBpAHQAcgBvAGcAZQBuACAAaQBuACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAxACAATQBNAFMAXABuAE0ATgBfAGoAbQA1AFQAMQBcAG4AawBnACAATgBcAG4ATQBOAF8AewBqAG0APQA1ACwAVAA9ADEAfQA9AEEARQBfAHsAagB9AFwAXAB0AGkAbQBlAHMAIABNAE0AUwBfAHsAagBtAD0ANQAsAFQAPQAxAH0AXABuAEEARQBfAGoAIAA9ACAAdABvAHQAYQBsACAAbgBpAHQAcgBvAGcAZQBuACAAZQB4AGMAcgBlAHQAZQBkACAAYgB5ACAAZQBhAGMAaAAgAGMAYQB0AHQAbABlACAAZwByAG8AdQBwACAAOgAgAGsAZwAgAE4AXABuAE0ATQBTAF8AagBtADUAVAAxACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAaQBuACAAcAByAGkAbQBhAHIAeQAgAHMAeQBzAHQAZQBtACAAZAByAHkAbABvAHQAIABNAE0AUwAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMARAByAHkAbABvAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQBFAF8AagAsACAATQBNAFMAXwBqAG0ANQBUADEALABcAG4AIAAgACAAIABBAEUAXwBqACAAKgAgAE0ATQBTAF8AagBtADUAVAAxAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMARAByAHkAbABvAHQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMQAgAE0ATQBTAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAyAF8AUwB0AGEAZwBlADEATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBEAHIAeQBsAG8AdABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBOAF8AagBtADUAVAAxAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAyAF8AUwB0AGEAZwBlADEATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBEAHIAeQBsAG8AdABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADIAXwBTAHQAYQBnAGUAMQBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAEQAcgB5AGwAbwB0AF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAxAC4AMQAuADMALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAyAF8AUwB0AGEAZwBlADEATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBEAHIAeQBsAG8AdABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMARAByAHkAbABvAHQAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE4AXwB7AGoAbQA9ADUALABUAD0AMQB9AD0AQQBFAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAE0ATQBTAF8AewBqAG0APQA1ACwAVAA9ADEAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMARAByAHkAbABvAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBFAF8AagBcACIALABcACIAdABvAHQAYQBsACAAbgBpAHQAcgBvAGcAZQBuACAAZQB4AGMAcgBlAHQAZQBkACAAYgB5ACAAZQBhAGMAaAAgAGMAYQB0AHQAbABlACAAZwByAG8AdQBwACAAOgAgAGsAZwAgAE4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATQBTAF8AagBtADUAVAAxAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAGkAbgAgAHAAcgBpAG0AYQByAHkAIABzAHkAcwB0AGUAbQAgAGQAcgB5AGwAbwB0ACAATQBNAFMAIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADMAXwBBAG4AbgB1AGEAbABOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AXABuAEEAbgBuAHUAYQBsACAAbgBpAHQAcgBvAGcAZQBuACAAZQB4AGMAcgBlAHQAaQBvAG4AIABmAHIAbwBtACAAZQBhAGMAaAAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAGcAcgBvAHUAcABcAG4AQQBFAF8AagBcAG4AawBnACAATgBcAG4AQQBFAF8AewBqAH0APQBOAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAE4ARQBfAHsAagB9AFwAXAB0AGkAbQBlAHMAIABEAF8AewBqAH0AXABuAE4AXwBqACAAPQAgAG4AdQBtAGIAZQByACAAbwBmACAAYwBhAHQAdABsAGUAIABpAG4AIABlAGEAYwBoACAAZwByAG8AdQBwACAAOgAgAGgAZQBhAGQAXABuAE4ARQBfAGoAIAA9ACAAbgBpAHQAcgBvAGcAZQBuACAAZQB4AGMAcgBlAHQAaQBvAG4AIAA6ACAAawBnACAATgAvAGgAZQBhAGQALwBkAGEAeQBcAG4ARABfAGoAIAA9ACAAZAB1AHIAYQB0AGkAbwBuACAAbwBmACAAcwB0AGEAeQAgAG8AZgAgAGMAYQB0AHQAbABlACAAZwByAG8AdQBwACAAOgAgAGQAYQB5AHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMwBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABOAF8AagAsACAATgBFAF8AagAsACAARABfAGoALABcAG4AIAAgACAAIABOAF8AagAgACoAIABOAEUAXwBqACAAKgAgAEQAXwBqAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMwBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBuAG4AdQBhAGwAIABuAGkAdAByAG8AZwBlAG4AIABlAHgAYwByAGUAdABpAG8AbgAgAGYAcgBvAG0AIABlAGEAYwBoACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAAZwByAG8AdQBwAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAzAF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEUAXwBqAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAzAF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMwBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMQAuADEALgAzACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADMAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMwBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMwBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEARQBfAHsAagB9AD0ATgBfAHsAagB9AFwAXAB0AGkAbQBlAHMAIABOAEUAXwB7AGoAfQBcAFwAdABpAG0AZQBzACAARABfAHsAagB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAzAF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AXwBqAFwAIgAsAFwAIgBuAHUAbQBiAGUAcgAgAG8AZgAgAGMAYQB0AHQAbABlACAAaQBuACAAZQBhAGMAaAAgAGcAcgBvAHUAcAAgADoAIABoAGUAYQBkAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEUAXwBqAFwAIgAsAFwAIgBuAGkAdAByAG8AZwBlAG4AIABlAHgAYwByAGUAdABpAG8AbgAgADoAIABrAGcAIABOAC8AaABlAGEAZAAvAGQAYQB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAF8AagBcACIALABcACIAZAB1AHIAYQB0AGkAbwBuACAAbwBmACAAcwB0AGEAeQAgAG8AZgAgAGMAYQB0AHQAbABlACAAZwByAG8AdQBwACAAOgAgAGQAYQB5AHMAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANABfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBQAGUAcgBIAGUAYQBkAFwAbgBOAGkAdAByAG8AZwBlAG4AIABlAHgAYwByAGUAdABpAG8AbgAgAHAAZQByACAAaABlAGEAZAAgAHAAZQByACAAZABhAHkAXABuAE4ARQBfAGoAXABuAGsAZwAgAE4ALwBoAGUAYQBkAC8AZABhAHkAXABuAE4ARQBfAHsAagB9AD0ATgBJAF8AewBqAH0AXABcAHQAaQBtAGUAcwAoADEALQBOAFIAXwB7AGoAfQApAFwAbgBOAEkAXwBqACAAPQAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgB0AGEAawBlACAAOgAgAGsAZwAgAE4ALwBoAGUAYQBkAC8AZABhAHkAXABuAE4AUgBfAGoAIAA9ACAAbgBpAHQAcgBvAGcAZQBuACAAcgBlAHQAZQBuAHQAaQBvAG4AIABlAHgAcAByAGUAcwBzAGUAZAAgAGEAcwAgAGEAIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABpAG4AdABhAGsAZQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANABfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBQAGUAcgBIAGUAYQBkAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE4ASQBfAGoALAAgAE4AUgBfAGoALABcAG4AIAAgACAAIABOAEkAXwBqACAAKgAgACgAMQAgAC0AIABOAFIAXwBqACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA0AF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAFAAZQByAEgAZQBhAGQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwBnAGUAbgAgAGUAeABjAHIAZQB0AGkAbwBuACAAcABlAHIAIABoAGUAYQBkACAAcABlAHIAIABkAGEAeQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANABfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBQAGUAcgBIAGUAYQBkAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAEUAXwBqAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA0AF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAFAAZQByAEgAZQBhAGQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOAC8AaABlAGEAZAAvAGQAYQB5AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA0AF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAFAAZQByAEgAZQBhAGQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADEALgAxAC4AMwAsACAARQBxAHUAYQB0AGkAbwBuACAAKAA0ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADQAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AUABlAHIASABlAGEAZABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANABfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBQAGUAcgBIAGUAYQBkAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBFAF8AewBqAH0APQBOAEkAXwB7AGoAfQBcAFwAdABpAG0AZQBzACgAMQAtAE4AUgBfAHsAagB9ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADQAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AUABlAHIASABlAGEAZABfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEkAXwBqAFwAIgAsAFwAIgBuAGkAdAByAG8AZwBlAG4AIABpAG4AdABhAGsAZQAgADoAIABrAGcAIABOAC8AaABlAGEAZAAvAGQAYQB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAFIAXwBqAFwAIgAsAFwAIgBuAGkAdAByAG8AZwBlAG4AIAByAGUAdABlAG4AdABpAG8AbgAgAGUAeABwAHIAZQBzAHMAZQBkACAAYQBzACAAYQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAGkAbgB0AGEAawBlACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA1AF8ATgBpAHQAcgBvAGcAZQBuAEkAbgB0AGEAawBlAFwAbgBOAGkAdAByAG8AZwBlAG4AIABpAG4AdABhAGsAZQAgAG8AZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQBcAG4ATgBJAF8AagBcAG4AawBnACAATgAvAGgAZQBhAGQALwBkAGEAeQBcAG4ATgBJAF8AewBqAH0APQBJAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAEMAUABfAHsAagB9AFwAXABkAGkAdgAgADYALgAyADUAXABuAEkAXwBqACAAPQAgAGQAcgB5ACAAbQBhAHQAdABlAHIAIABpAG4AdABhAGsAZQAgADoAIABrAGcAIABEAE0ALwBoAGUAYQBkAC8AZABhAHkAXABuAEMAUABfAGoAIAA9ACAAYwByAHUAZABlACAAcAByAG8AdABlAGkAbgAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABmAGUAZQBkACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4ANgAuADIANQAgAD0AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAYwBvAG4AdgBlAHIAdABpAG4AZwAgAGMAcgB1AGQAZQAgAHAAcgBvAHQAZQBpAG4AIABpAG4AdABvACAAbgBpAHQAcgBvAGcAZQBuACAAOgAgAHIAYQB0AGkAbwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA1AF8ATgBpAHQAcgBvAGcAZQBuAEkAbgB0AGEAawBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEkAXwBqACwAIABDAFAAXwBqACwAXABuACAAIAAgACAASQBfAGoAIAAqACAAQwBQAF8AagAgAC8AIAA2AC4AMgA1AFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANQBfAE4AaQB0AHIAbwBnAGUAbgBJAG4AdABhAGsAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBpAHQAcgBvAGcAZQBuACAAaQBuAHQAYQBrAGUAIABvAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADUAXwBOAGkAdAByAG8AZwBlAG4ASQBuAHQAYQBrAGUAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4ASQBfAGoAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADUAXwBOAGkAdAByAG8AZwBlAG4ASQBuAHQAYQBrAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOAC8AaABlAGEAZAAvAGQAYQB5AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA1AF8ATgBpAHQAcgBvAGcAZQBuAEkAbgB0AGEAawBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAxAC4AMQAuADMALAAgAEUAcQB1AGEAdABpAG8AbgAgACgANQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA1AF8ATgBpAHQAcgBvAGcAZQBuAEkAbgB0AGEAawBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA1AF8ATgBpAHQAcgBvAGcAZQBuAEkAbgB0AGEAawBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBJAF8AewBqAH0APQBJAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAEMAUABfAHsAagB9AFwAXABkAGkAdgAgADYALgAyADUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADUAXwBOAGkAdAByAG8AZwBlAG4ASQBuAHQAYQBrAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBfAGoAXAAiACwAXAAiAGQAcgB5ACAAbQBhAHQAdABlAHIAIABpAG4AdABhAGsAZQAgADoAIABrAGcAIABEAE0ALwBoAGUAYQBkAC8AZABhAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAUABfAGoAXAAiACwAXAAiAGMAcgB1AGQAZQAgAHAAcgBvAHQAZQBpAG4AIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAZgBlAGUAZAAgADoAIABmAHIAYQBjAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiADYALgAyADUAXAAiACwAXAAiAGYAYQBjAHQAbwByACAAZgBvAHIAIABjAG8AbgB2AGUAcgB0AGkAbgBnACAAYwByAHUAZABlACAAcAByAG8AdABlAGkAbgAgAGkAbgB0AG8AIABuAGkAdAByAG8AZwBlAG4AIAA6ACAAcgBhAHQAaQBvAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADYAXwBTAHQAYQBnAGUAMgBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAFwAbgBOAGkAdAByAG8AZwBlAG4AIABpAG4AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADIAIABNAE0AUwBcAG4ATQBOAF8AagBtAFQAMgBcAG4AawBnACAATgBcAG4ATQBOAF8AewBqAG0ALABUAD0AMgB9AD0ATgBUAF8AewBqAG0ALABUAD0AMgB9AFwAXAB0AGkAbQBlAHMAIABNAE0AUwBfAHsAagBtACwAVAA9ADIAfQBcAG4ATgBUAF8AagBtAFQAMgAgAD0AIABuAGkAdAByAG8AZwBlAG4AIAB0AHIAYQBuAHMAZgBlAHIAcgBlAGQAIAB0AG8AIABzAGUAYwBvAG4AZABhAHIAeQAgAHQAcgBlAGEAdABtAGUAbgB0ACAATQBNAFMAIAA6ACAAawBnACAATgBcAG4ATQBNAFMAXwBqAG0AVAAyACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAaQBuACAAZQBhAGMAaAAgAHMAZQBjAG8AbgBkAGEAcgB5ACAAcwB5AHMAdABlAG0AIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADYAXwBTAHQAYQBnAGUAMgBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE4AVABfAGoAbQBUADIALAAgAE0ATQBTAF8AagBtAFQAMgAsAFwAbgAgACAAIAAgAE4AVABfAGoAbQBUADIAIAAqACAATQBNAFMAXwBqAG0AVAAyAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANgBfAFMAdABhAGcAZQAyAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMgAgAE0ATQBTAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA2AF8AUwB0AGEAZwBlADIATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBOAF8AagBtAFQAMgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANgBfAFMAdABhAGcAZQAyAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA2AF8AUwB0AGEAZwBlADIATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMQAuADEALgAzACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADYAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANgBfAFMAdABhAGcAZQAyAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADYAXwBTAHQAYQBnAGUAMgBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBOAF8AewBqAG0ALABUAD0AMgB9AD0ATgBUAF8AewBqAG0ALABUAD0AMgB9AFwAXAB0AGkAbQBlAHMAIABNAE0AUwBfAHsAagBtACwAVAA9ADIAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANgBfAFMAdABhAGcAZQAyAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBUAF8AagBtAFQAMgBcACIALABcACIAbgBpAHQAcgBvAGcAZQBuACAAdAByAGEAbgBzAGYAZQByAHIAZQBkACAAdABvACAAcwBlAGMAbwBuAGQAYQByAHkAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAE0ATQBTACAAOgAgAGsAZwAgAE4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATQBTAF8AagBtAFQAMgBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIABpAG4AIABlAGEAYwBoACAAcwBlAGMAbwBuAGQAYQByAHkAIABzAHkAcwB0AGUAbQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANwBfAE4AaQB0AHIAbwBnAGUAbgBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAVABvAFMAdABhAGcAZQAyAFwAbgBOAGkAdAByAG8AZwBlAG4AIAB0AHIAYQBuAHMAZgBlAHIAcgBlAGQAIAB0AG8AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADIAIABNAE0AUwBcAG4ATgBUAF8AagBtAFQAMgBcAG4AawBnACAATgBcAG4ATgBUAF8AewBqAG0ALABUAD0AMgB9AD0AKABNAE4AXwB7AGoAbQA9ADUALABUAD0AMQB9AFwAXAB0AGkAbQBlAHMAKAAxAC0ARgByAGEAYwBHAEEAUwBNAF8AewBtAD0ANQB9AC0ARQBGAF8AewBtAD0ANQB9ACkAKQAtAE0ATgBfAHsAagBtACwAVAA9ADMAfQBcAG4ATQBOAF8AagBtADUAVAAxACAAPQAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAE0ATQBTACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAxACAAOgAgAGsAZwAgAE4AXABuAEYAcgBhAGMARwBBAFMATQBfAG0ANQAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAZgByAG8AbQAgAGQAcgB5AGwAbwB0ACAATQBNAFMAIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAbgBFAEYAXwBtADUAIAA9ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABkAHIAeQBsAG8AdAAgAE0ATQBTACAAOgAgAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AIABkAGUAcABvAHMAaQB0AGUAZABcAG4ATQBOAF8AagBtAFQAMwAgAD0AIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABNAE0AUwAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMwAgADoAIABrAGcAIABOAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADcAXwBOAGkAdAByAG8AZwBlAG4AVAByAGEAbgBzAGYAZQByAHIAZQBkAFQAbwBTAHQAYQBnAGUAMgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAE4AXwBqAG0ANQBUADEALAAgAEYAcgBhAGMARwBBAFMATQBfAG0ANQAsACAARQBGAF8AbQA1ACwAIABNAE4AXwBqAG0AVAAzACwAXABuACAAIAAgACAAKABNAE4AXwBqAG0ANQBUADEAIAAqACAAKAAxACAALQAgAEYAcgBhAGMARwBBAFMATQBfAG0ANQAgAC0AIABFAEYAXwBtADUAKQApACAALQAgAE0ATgBfAGoAbQBUADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA3AF8ATgBpAHQAcgBvAGcAZQBuAFQAcgBhAG4AcwBmAGUAcgByAGUAZABUAG8AUwB0AGEAZwBlADIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwBnAGUAbgAgAHQAcgBhAG4AcwBmAGUAcgByAGUAZAAgAHQAbwAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMgAgAE0ATQBTAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA3AF8ATgBpAHQAcgBvAGcAZQBuAFQAcgBhAG4AcwBmAGUAcgByAGUAZABUAG8AUwB0AGEAZwBlADIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AVABfAGoAbQBUADIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADcAXwBOAGkAdAByAG8AZwBlAG4AVAByAGEAbgBzAGYAZQByAHIAZQBkAFQAbwBTAHQAYQBnAGUAMgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADcAXwBOAGkAdAByAG8AZwBlAG4AVAByAGEAbgBzAGYAZQByAHIAZQBkAFQAbwBTAHQAYQBnAGUAMgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMQAuADEALgAzACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADcAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANwBfAE4AaQB0AHIAbwBnAGUAbgBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAVABvAFMAdABhAGcAZQAyAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA3AF8ATgBpAHQAcgBvAGcAZQBuAFQAcgBhAG4AcwBmAGUAcgByAGUAZABUAG8AUwB0AGEAZwBlADIAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAFQAXwB7AGoAbQAsAFQAPQAyAH0APQAoAE0ATgBfAHsAagBtAD0ANQAsAFQAPQAxAH0AXABcAHQAaQBtAGUAcwAoADEALQBGAHIAYQBjAEcAQQBTAE0AXwB7AG0APQA1AH0ALQBFAEYAXwB7AG0APQA1AH0AKQApAC0ATQBOAF8AewBqAG0ALABUAD0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA3AF8ATgBpAHQAcgBvAGcAZQBuAFQAcgBhAG4AcwBmAGUAcgByAGUAZABUAG8AUwB0AGEAZwBlADIAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBOAF8AagBtADUAVAAxAFwAIgAsAFwAIgBuAGkAdAByAG8AZwBlAG4AIABpAG4AIABNAE0AUwAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMQAgADoAIABrAGcAIABOAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAEcAQQBTAE0AXwBtADUAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABmAHIAbwBtACAAZAByAHkAbABvAHQAIABNAE0AUwAgADoAIABmAHIAYQBjAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAG0ANQBcACIALABcACIAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABkAHIAeQBsAG8AdAAgAE0ATQBTACAAOgAgAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AIABkAGUAcABvAHMAaQB0AGUAZABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBOAF8AagBtAFQAMwBcACIALABcACIAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAATQBNAFMAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADMAIAA6ACAAawBnACAATgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA4AF8AUwB0AGEAZwBlADMATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBcAG4ATgBpAHQAcgBvAGcAZQBuACAAaQBuACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAzACAATQBNAFMAXABuAE0ATgBfAGoAbQAxAFQAMwBcAG4AawBnACAATgBcAG4ATQBOAF8AewBqAG0APQAxACwAVAA9ADMAfQA9AEEARQBfAHsAagB9AFwAXAB0AGkAbQBlAHMAIABNAE0AUwBfAHsAagBtAD0AMQAsAFQAPQAzAH0AXABuAEEARQBfAGoAIAA9ACAAdABvAHQAYQBsACAAbgBpAHQAcgBvAGcAZQBuACAAZQB4AGMAcgBlAHQAZQBkACAAYgB5ACAAZQBhAGMAaAAgAGMAYQB0AHQAbABlACAAZwByAG8AdQBwACAAOgAgAGsAZwAgAE4AXABuAE0ATQBTAF8AagBtADEAVAAzACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAdABvACAAdABlAHIAdABpAGEAcgB5ACAAYQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgAHMAeQBzAHQAZQBtACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA4AF8AUwB0AGEAZwBlADMATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAEUAXwBqACwAIABNAE0AUwBfAGoAbQAxAFQAMwAsAFwAbgAgACAAIAAgAEEARQBfAGoAIAAqACAATQBNAFMAXwBqAG0AMQBUADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA4AF8AUwB0AGEAZwBlADMATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBpAHQAcgBvAGcAZQBuACAAaQBuACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAzACAATQBNAFMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADgAXwBTAHQAYQBnAGUAMwBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE4AXwBqAG0AMQBUADMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADgAXwBTAHQAYQBnAGUAMwBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AOABfAFMAdABhAGcAZQAzAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADEALgAxAC4AMwAsACAARQBxAHUAYQB0AGkAbwBuACAAKAA4ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADgAXwBTAHQAYQBnAGUAMwBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA4AF8AUwB0AGEAZwBlADMATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATgBfAHsAagBtAD0AMQAsAFQAPQAzAH0APQBBAEUAXwB7AGoAfQBcAFwAdABpAG0AZQBzACAATQBNAFMAXwB7AGoAbQA9ADEALABUAD0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA4AF8AUwB0AGEAZwBlADMATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAEUAXwBqAFwAIgAsAFwAIgB0AG8AdABhAGwAIABuAGkAdAByAG8AZwBlAG4AIABlAHgAYwByAGUAdABlAGQAIABiAHkAIABlAGEAYwBoACAAYwBhAHQAdABsAGUAIABnAHIAbwB1AHAAIAA6ACAAawBnACAATgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBNAFMAXwBqAG0AMQBUADMAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAdABvACAAdABlAHIAdABpAGEAcgB5ACAAYQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgAHMAeQBzAHQAZQBtACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBhAG4AdQByAGUAQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADQALgAxADoAIABCAGUAZQBmACAARgBlAGUAZABsAG8AdABcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANAAuADEALgAxAC4AOQAgAE0AYQBuAHUAcgBlACAAQQBwAHAAbABpAGUAZAAgAHQAbwAgAFMAbwBpAGwAcwBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxAFwAbgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHMAbwBpAGwAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMQAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBNAE4AUwBvAGkAbABfAHMAYwBvAHAAZQAxAFwAbgBrAGcAIABOAFwAbgBNAE4AUwBvAGkAbABfAHsAcwBjAG8AcABlADEAfQA9AFwAXABzAHUAbQBfAHsAagB9AFwAXABzAHUAbQBfAHsAbQB9AFwAXABzAHUAbQBfAHsAVAB9ACgATQBOAF8AewBqAG0AVAA9ADIALAAzAH0AXABcAHQAaQBtAGUAcwAoADEALQBFAEYAXwB7AG0AVAA9ADIALAAzAH0ALQBGAHIAYQBjAEcAQQBTAE0AXwB7AG0AVAA9ADIALAAzAH0AKQApAFwAXAB0AGkAbQBlAHMAIABQAEYAXABuAE0ATgBfAGoAbQBUADIAMwAgAD0AIABtAGEAcwBzACAAbwBmACAATgAgAGkAbgAgAHMAZQBjAG8AbgBkAGEAcgB5ACAAYQBuAGQAIAB0AGUAcgB0AGkAYQByAHkAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAE0ATQBTACAAcwB0AGEAZwBlAHMAIABhAHMAIABjAGEAbABjAHUAbABhAHQAZQBkACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAIAA6ACAAawBnACAATgBcAG4ARQBGAF8AbQBUADIAMwAgAD0AIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGUAYQBjAGgAIABNAE0AUwAgADoAIABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOAFwAbgBGAHIAYQBjAEcAQQBTAE0AXwBtAFQAMgAzACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAGEAbgBpAG0AYQBsACAAdwBhAHMAdABlACAATgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGkAbgAgAGUAYQBjAGgAIABNAE0AUwAgAGYAbwByACAAZQBhAGMAaAAgAGMAYQB0AHQAbABlACAAZwByAG8AdQBwACAAOgAgACgAawBnACAATgBIADMALQBOACAAKwAgAE4ATwB4AC0ATgApAC8AawBnACAATgBcAG4AUABGACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHMAbwBpAGwAIAB3AGkAdABoAGkAbgAgAHQAaABlACAAZgBlAGUAZABsAG8AdAAgAGIAbwB1AG4AZABhAHIAeQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMQBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBOAF8AagBtAFQAMgAzACwAIABFAEYAXwBtAFQAMgAzACwAIABGAHIAYQBjAEcAQQBTAE0AXwBtAFQAMgAzACwAIABQAEYALABcAG4AIAAgACAAIAAoAE0ATgBfAGoAbQBUADIAMwAgACoAIAAoADEAIAAtACAARQBGAF8AbQBUADIAMwAgAC0AIABGAHIAYQBjAEcAQQBTAE0AXwBtAFQAMgAzACkAKQAgACoAIABQAEYAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA5AF8AXwAxAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABzAG8AaQBsAHMAIABmAG8AcgAgAHMAYwBvAHAAZQAgADEAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMQBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADEAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATgBTAG8AaQBsAF8AcwBjAG8AcABlADEAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMQBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADEAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADEALgAxAC4AOQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA5AF8AXwAxAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATgBTAG8AaQBsAF8AewBzAGMAbwBwAGUAMQB9AD0AXABcAHMAdQBtAF8AewBqAH0AXABcAHMAdQBtAF8AewBtAH0AXABcAHMAdQBtAF8AewBUAH0AKABNAE4AXwB7AGoAbQBUAD0AMgAsADMAfQBcAFwAdABpAG0AZQBzACgAMQAtAEUARgBfAHsAbQBUAD0AMgAsADMAfQAtAEYAcgBhAGMARwBBAFMATQBfAHsAbQBUAD0AMgAsADMAfQApACkAXABcAHQAaQBtAGUAcwAgAFAARgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMQBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADEAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBOAF8AagBtAFQAMgAzAFwAIgAsAFwAIgBtAGEAcwBzACAAbwBmACAATgAgAGkAbgAgAHMAZQBjAG8AbgBkAGEAcgB5ACAAYQBuAGQAIAB0AGUAcgB0AGkAYQByAHkAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAE0ATQBTACAAcwB0AGEAZwBlAHMAIABhAHMAIABjAGEAbABjAHUAbABhAHQAZQBkACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAIAA6ACAAawBnACAATgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AbQBUADIAMwBcACIALABcACIAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABlAGEAYwBoACAATQBNAFMAIAA6ACAAawBnACAATgAyAE8ALQBOAC8AawBnACAATgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBHAEEAUwBNAF8AbQBUADIAMwBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAYQBuAGkAbQBhAGwAIAB3AGEAcwB0AGUAIABOACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAaQBuACAAZQBhAGMAaAAgAE0ATQBTACAAZgBvAHIAIABlAGEAYwBoACAAYwBhAHQAdABsAGUAIABnAHIAbwB1AHAAIAA6ACAAKABrAGcAIABOAEgAMwAtAE4AIAArACAATgBPAHgALQBOACkALwBrAGcAIABOAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEYAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHMAbwBpAGwAIAB3AGkAdABoAGkAbgAgAHQAaABlACAAZgBlAGUAZABsAG8AdAAgAGIAbwB1AG4AZABhAHIAeQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADMAXABuAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzACAAZQBtAGkAcwBzAGkAbwBuAHMAXABuAE0ATgBTAG8AaQBsAF8AcwBjAG8AcABlADMAXABuAGsAZwAgAE4AXABuAE0ATgBTAG8AaQBsAF8AewBzAGMAbwBwAGUAMwB9AD0AXABcAHMAdQBtAF8AewBqAH0AXABcAHMAdQBtAF8AewBtAH0AXABcAHMAdQBtAF8AewBUAH0AKABNAE4AXwB7AGoAbQBUAD0AMgAsADMAfQBcAFwAdABpAG0AZQBzACgAMQAtAEUARgBfAHsAbQBUAD0AMgAsADMAfQAtAEYAcgBhAGMARwBBAFMATQBfAHsAbQBUAD0AMgAsADMAfQApACkAXABcAHQAaQBtAGUAcwAoADEALQBQAEYAKQBcAG4ATQBOAF8AagBtAFQAMgAzACAAPQAgAG0AYQBzAHMAIABvAGYAIABOACAAaQBuACAAcwBlAGMAbwBuAGQAYQByAHkAIABhAG4AZAAgAHQAZQByAHQAaQBhAHIAeQAgAHQAcgBlAGEAdABtAGUAbgB0ACAATQBNAFMAIABzAHQAYQBnAGUAcwAgAGEAcwAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABmAG8AcgAgAG0AYQBuAHUAcgBlACAAbQBhAG4AYQBnAGUAbQBlAG4AdAAgADoAIABrAGcAIABOAFwAbgBFAEYAXwBtAFQAMgAzACAAPQAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZQBhAGMAaAAgAE0ATQBTACAAOgAgAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AXABuAEYAcgBhAGMARwBBAFMATQBfAG0AVAAyADMAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAYQBuAGkAbQBhAGwAIAB3AGEAcwB0AGUAIABOACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAaQBuACAAZQBhAGMAaAAgAE0ATQBTACAAZgBvAHIAIABlAGEAYwBoACAAYwBhAHQAdABsAGUAIABnAHIAbwB1AHAAIAA6ACAAKABrAGcAIABOAEgAMwAtAE4AIAArACAATgBPAHgALQBOACkALwBrAGcAIABOAFwAbgBQAEYAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbAAgAHcAaQB0AGgAaQBuACAAdABoAGUAIABmAGUAZQBkAGwAbwB0ACAAYgBvAHUAbgBkAGEAcgB5ACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA5AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAE4AXwBqAG0AVAAyADMALAAgAEUARgBfAG0AVAAyADMALAAgAEYAcgBhAGMARwBBAFMATQBfAG0AVAAyADMALAAgAFAARgAsAFwAbgAgACAAIAAgACgATQBOAF8AagBtAFQAMgAzACAAKgAgACgAMQAgAC0AIABFAEYAXwBtAFQAMgAzACAALQAgAEYAcgBhAGMARwBBAFMATQBfAG0AVAAyADMAKQApACAAKgAgACgAMQAgAC0AIABQAEYAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHMAbwBpAGwAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA5AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBOAFMAbwBpAGwAXwBzAGMAbwBwAGUAMwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA5AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMQAuADEALgA5ACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADIAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBOAFMAbwBpAGwAXwB7AHMAYwBvAHAAZQAzAH0APQBcAFwAcwB1AG0AXwB7AGoAfQBcAFwAcwB1AG0AXwB7AG0AfQBcAFwAcwB1AG0AXwB7AFQAfQAoAE0ATgBfAHsAagBtAFQAPQAyACwAMwB9AFwAXAB0AGkAbQBlAHMAKAAxAC0ARQBGAF8AewBtAFQAPQAyACwAMwB9AC0ARgByAGEAYwBHAEEAUwBNAF8AewBtAFQAPQAyACwAMwB9ACkAKQBcAFwAdABpAG0AZQBzACgAMQAtAFAARgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA5AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAAMgAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE4AXwBqAG0AVAAyADMAXAAiACwAXAAiAG0AYQBzAHMAIABvAGYAIABOACAAaQBuACAAcwBlAGMAbwBuAGQAYQByAHkAIABhAG4AZAAgAHQAZQByAHQAaQBhAHIAeQAgAHQAcgBlAGEAdABtAGUAbgB0ACAATQBNAFMAIABzAHQAYQBnAGUAcwAgAGEAcwAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABmAG8AcgAgAG0AYQBuAHUAcgBlACAAbQBhAG4AYQBnAGUAbQBlAG4AdAAgADoAIABrAGcAIABOAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBtAFQAMgAzAFwAIgAsAFwAIgBuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGUAYQBjAGgAIABNAE0AUwAgADoAIABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAEcAQQBTAE0AXwBtAFQAMgAzAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABhAG4AaQBtAGEAbAAgAHcAYQBzAHQAZQAgAE4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABpAG4AIABlAGEAYwBoACAATQBNAFMAIABmAG8AcgAgAGUAYQBjAGgAIABjAGEAdAB0AGwAZQAgAGcAcgBvAHUAcAAgADoAIAAoAGsAZwAgAE4ASAAzAC0ATgAgACsAIABOAE8AeAAtAE4AKQAvAGsAZwAgAE4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAARgBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbAAgAHcAaQB0AGgAaQBuACAAdABoAGUAIABmAGUAZQBkAGwAbwB0ACAAYgBvAHUAbgBkAGEAcgB5ACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADQALgAxADoAIABCAGUAZQBmACAARgBlAGUAZABsAG8AdABcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANAAuADEALgAxAC4ANQAgAE0AZQB0AGgAbwBkACAAMQAgAC0AIABNAGEAbgB1AHIAZQAgAEEAdABtAG8AcwBwAGgAZQByAGkAYwAgAEQAZQBwAG8AcwBpAHQAaQBvAG4AIABCAGUAZQBmACAARgBlAGUAZABsAG8AdABcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADUAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMAXABuAFQAbwB0AGEAbAAgAGEAbgBuAHUAYQBsACAAYQB0AG0AbwBzAHAAaABlAHIAaQBjACAAZABlAHAAbwBzAGkAdABpAG8AbgAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAG0AYQBuAHUAcgBlACAAbQBhAG4AYQBnAGUAbQBlAG4AdABcAG4ARQBfAE4AMgBPAGEAZABcAG4AdAAgAE4AMgBPAFwAbgBFAF8AewBOADIATwAsAGEAZAB9AD0AKABNAE0AUwBfAHsAQQBUAE0ATwBTAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsATgAyAE8AfQBcAFwAdABpAG0AZQBzACAAQwBfAHsATgAyAE8AfQApAFwAXAB0AGkAbQBlAHMAMQAwAF4AewAtADMAfQBcAG4ATQBNAFMAXwBBAFQATQBPAFMAIAA9ACAAbQBhAHMAcwAgAG8AZgAgAE4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABmAHIAbwBtACAATQBNAFMAIAA6ACAAawBnACAATgBcAG4ARQBGAF8ATgAyAE8AIAA9ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABhAHQAbQBvAHMAcABoAGUAcgBpAGMAIABkAGUAcABvAHMAaQB0AGkAbwBuACAAOgAgAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AXABuAEMAXwBOADIATwAgAD0AIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzACAAOgAgAHIAYQB0AGkAbwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0ATQBTAF8AQQBUAE0ATwBTACwAIABFAEYAXwBOADIATwAsACAAQwBfAE4AMgBPACwAXABuACAAIAAgACAAKABNAE0AUwBfAEEAVABNAE8AUwAgACoAIABFAEYAXwBOADIATwAgACoAIABDAF8ATgAyAE8AKQAgACoAIAAxADAAIABeACAALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABvAHQAYQBsACAAYQBuAG4AdQBhAGwAIABhAHQAbQBvAHMAcABoAGUAcgBpAGMAIABkAGUAcABvAHMAaQB0AGkAbwBuACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAbQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8ATgAyAE8AYQBkAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAxAC4AMQAuADUALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsATgAyAE8ALABhAGQAfQA9ACgATQBNAFMAXwB7AEEAVABNAE8AUwB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AE4AMgBPAH0AXABcAHQAaQBtAGUAcwAgAEMAXwB7AE4AMgBPAH0AKQBcAFwAdABpAG0AZQBzADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADUAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBNAFMAXwBBAFQATQBPAFMAXAAiACwAXAAiAG0AYQBzAHMAIABvAGYAIABOACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAZgByAG8AbQAgAE0ATQBTACAAOgAgAGsAZwAgAE4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAE4AMgBPAFwAIgAsAFwAIgBuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGEAdABtAG8AcwBwAGgAZQByAGkAYwAgAGQAZQBwAG8AcwBpAHQAaQBvAG4AIAA6ACAAawBnACAATgAyAE8ALQBOAC8AawBnACAATgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBfAE4AMgBPAFwAIgAsAFwAIgBmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzACAAOgAgAHIAYQB0AGkAbwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAagBcACIALAAgAFwAIgBwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGkAXAAiACwAIABcACIAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgByAFwAIgAsACAAXAAiAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMgBfAFYAbwBsAGEAdABpAGwAaQBzAGUAZABOAGkAdAByAG8AZwBlAG4ARgByAG8AbQBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AFwAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQAIABuAGkAdAByAG8AZwBlAG4AIABmAHIAbwBtACAAbQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0AFwAbgBNAE0AUwBfAEEAVABNAE8AUwBcAG4AawBnACAATgBcAG4ATQBNAFMAXwB7AEEAVABNAE8AUwB9AD0AXABcAHMAdQBtAF8AewBqAH0AXABcAHMAdQBtAF8AewBtAH0AXABcAHMAdQBtAF8AewBUAH0AKABNAE4AXwB7AGoAbQBUAH0AXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMARwBBAFMATQBfAHsAbQBUAH0AKQBcAG4ATQBOAF8AagBtAFQAIAA9ACAAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAAZQBhAGMAaAAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAATQBNAFMAIAAoAGUAeABjAGwAdQBkAGkAbgBnACAATQBOAF8AaQBqAG0AMQAzAFQAMgApACAAOgAgAGsAZwAgAE4AXABuAEYAcgBhAGMARwBBAFMATQBfAG0AVAAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAaQBuACAAZQBhAGMAaAAgAE0ATQBTACAAOgAgACgAawBnACAATgBIADMALQBOACAAKwAgAE4ATwB4AC0ATgApAC8AawBnACAATgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAyAF8AVgBvAGwAYQB0AGkAbABpAHMAZQBkAE4AaQB0AHIAbwBnAGUAbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBOAF8AagBtAFQALAAgAEYAcgBhAGMARwBBAFMATQBfAG0AVAAsAFwAbgAgACAAIAAgAE0ATgBfAGoAbQBUACAAKgAgAEYAcgBhAGMARwBBAFMATQBfAG0AVABcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADUAXwBfADIAXwBWAG8AbABhAHQAaQBsAGkAcwBlAGQATgBpAHQAcgBvAGcAZQBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBvAGwAYQB0AGkAbABpAHMAZQBkACAAbgBpAHQAcgBvAGcAZQBuACAAZgByAG8AbQAgAG0AYQBuAHUAcgBlACAAbQBhAG4AYQBnAGUAbQBlAG4AdABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMgBfAFYAbwBsAGEAdABpAGwAaQBzAGUAZABOAGkAdAByAG8AZwBlAG4ARgByAG8AbQBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE0AUwBfAEEAVABNAE8AUwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMgBfAFYAbwBsAGEAdABpAGwAaQBzAGUAZABOAGkAdAByAG8AZwBlAG4ARgByAG8AbQBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMgBfAFYAbwBsAGEAdABpAGwAaQBzAGUAZABOAGkAdAByAG8AZwBlAG4ARgByAG8AbQBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAxAC4AMQAuADUALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAyAF8AVgBvAGwAYQB0AGkAbABpAHMAZQBkAE4AaQB0AHIAbwBnAGUAbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADUAXwBfADIAXwBWAG8AbABhAHQAaQBsAGkAcwBlAGQATgBpAHQAcgBvAGcAZQBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATQBTAF8AewBBAFQATQBPAFMAfQA9AFwAXABzAHUAbQBfAHsAagB9AFwAXABzAHUAbQBfAHsAbQB9AFwAXABzAHUAbQBfAHsAVAB9ACgATQBOAF8AewBqAG0AVAB9AFwAXAB0AGkAbQBlAHMAIABGAHIAYQBjAEcAQQBTAE0AXwB7AG0AVAB9ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADUAXwBfADIAXwBWAG8AbABhAHQAaQBsAGkAcwBlAGQATgBpAHQAcgBvAGcAZQBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE4AXwBqAG0AVABcACIALABcACIAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAAZQBhAGMAaAAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAATQBNAFMAIAAoAGUAeABjAGwAdQBkAGkAbgBnACAATQBOAF8AaQBqAG0AMQAzAFQAMgApACAAOgAgAGsAZwAgAE4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMARwBBAFMATQBfAG0AVABcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGkAbgAgAGUAYQBjAGgAIABNAE0AUwAgADoAIAAoAGsAZwAgAE4ASAAzAC0ATgAgACsAIABOAE8AeAAtAE4AKQAvAGsAZwAgAE4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuACIAfQBdACwAIgBwAHIAbwBqAGUAYwB0AE4AYQBtAGUAcwAiADoAWwAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFYAYQBpAHIAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAIgAsACIAQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBIAGEAcgB2AGUAcwB0AEkAbgBkAGUAeAAiACwAIgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBSAGUAcwBpAGQAdQBlAEMAcgBvAHAAUgBhAHQAaQBvACIALAAiAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEMAYQBsAGMAdQBsAGEAdABlAEYAcgBhAGMAdABpAG8AbgBSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFYAUwBMAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBWAFMATABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AVgBTAEwAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBWAFMATABfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBWAFMATABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBWAFMATABfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0ATQBTAG0AMQBUADMAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0ATQBTAG0AMQBUADMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0ATQBTAG0AMQBUADMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAE0AUwBtADEAVAAzAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0ATQBTAG0AMQBUADMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBNAFMAbQAxAFQAMwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFMAdABhAGcAZQAxAE0ATQBTAE8AcAB0AGkAbwBuAHMAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFMAdABhAGcAZQAyAE0ATQBTAE8AcAB0AGkAbwBuAHMAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFMAdABhAGcAZQAzAE0ATQBTAE8AcAB0AGkAbwBuAHMAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwBlAHMAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAG4AaQBtAGEAbABDAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBuAGkAbQBhAGwAQwBoAGEAcgBhAGMAdABlAHIAaQBzAHQAaQBjAHMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAG4AaQBtAGEAbABDAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAG4AaQBtAGEAbABDAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAG4AaQBtAGEAbABDAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAaQBlAHQAUAByAG8AcABlAHIAdABpAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARABpAGUAdABQAHIAbwBwAGUAcgB0AGkAZQBzAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARABpAGUAdABQAHIAbwBwAGUAcgB0AGkAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAaQBlAHQAUAByAG8AcABlAHIAdABpAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAGkAZQB0AFAAcgBvAHAAZQByAHQAaQBlAHMAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAEMARgBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBDAEYAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAEMARgBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAEMARgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAEMARgBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARgByAGEAYwBOAFYAbwBsAGEAdABpAGwAaQBzAGUAZABfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARgByAGEAYwBOAFYAbwBsAGEAdABpAGwAaQBzAGUAZABfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEYAcgBhAGMATgBWAG8AbABhAHQAaQBsAGkAcwBlAGQAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARgByAGEAYwBOAFYAbwBsAGEAdABpAGwAaQBzAGUAZABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBGAHIAYQBjAE4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAF8ARABhAHQAYQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBVAG4AaQB0ACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMgBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBEAHIAeQBsAG8AdAAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAyAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEQAcgB5AGwAbwB0AF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADIAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARAByAHkAbABvAHQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMgBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBEAHIAeQBsAG8AdABfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMgBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBEAHIAeQBsAG8AdABfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADIAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARAByAHkAbABvAHQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAyAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEQAcgB5AGwAbwB0AF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAyAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEQAcgB5AGwAbwB0AF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANABfAFMAdABhAGcAZQAzAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA0AF8AUwB0AGEAZwBlADMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuAF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADQAXwBTAHQAYQBnAGUAMwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANABfAFMAdABhAGcAZQAzAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANABfAFMAdABhAGcAZQAzAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADQAXwBTAHQAYQBnAGUAMwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA0AF8AUwB0AGEAZwBlADMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA0AF8AUwB0AGEAZwBlADMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAUAByAG8AZAB1AGMAdABpAG8AbgAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA1AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAUAByAG8AZAB1AGMAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAUAByAG8AZAB1AGMAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA1AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA1AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABQAHIAbwBkAHUAYwB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8AXwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBfAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAF8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8AXwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8AXwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAF8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBfAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBfAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8AXwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMARAByAHkAbABvAHQAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8AXwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMARAByAHkAbABvAHQAXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8AXwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMARAByAHkAbABvAHQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8AXwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMARAByAHkAbABvAHQAXwBVAG4AaQB0ACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAF8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADIAXwBTAHQAYQBnAGUAMQBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAEQAcgB5AGwAbwB0AF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8AXwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMARAByAHkAbABvAHQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBfAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAyAF8AUwB0AGEAZwBlADEATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBEAHIAeQBsAG8AdABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8AXwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMARAByAHkAbABvAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBfAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAzAF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAF8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADMAXwBBAG4AbgB1AGEAbABOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8AXwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMwBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBfAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAzAF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBfAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAzAF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8AXwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMwBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAF8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADMAXwBBAG4AbgB1AGEAbABOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAF8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADMAXwBBAG4AbgB1AGEAbABOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBfAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA0AF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAFAAZQByAEgAZQBhAGQAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8AXwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANABfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBQAGUAcgBIAGUAYQBkAF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAF8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADQAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AUABlAHIASABlAGEAZABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBfAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA0AF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAFAAZQByAEgAZQBhAGQAXwBVAG4AaQB0ACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAF8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADQAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AUABlAHIASABlAGEAZABfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAF8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADQAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AUABlAHIASABlAGEAZABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAF8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADQAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AUABlAHIASABlAGEAZABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8AXwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANABfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBQAGUAcgBIAGUAYQBkAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8AXwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANQBfAE4AaQB0AHIAbwBnAGUAbgBJAG4AdABhAGsAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBfAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA1AF8ATgBpAHQAcgBvAGcAZQBuAEkAbgB0AGEAawBlAF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAF8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADUAXwBOAGkAdAByAG8AZwBlAG4ASQBuAHQAYQBrAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8AXwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANQBfAE4AaQB0AHIAbwBnAGUAbgBJAG4AdABhAGsAZQBfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8AXwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANQBfAE4AaQB0AHIAbwBnAGUAbgBJAG4AdABhAGsAZQBfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAF8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADUAXwBOAGkAdAByAG8AZwBlAG4ASQBuAHQAYQBrAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBfAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA1AF8ATgBpAHQAcgBvAGcAZQBuAEkAbgB0AGEAawBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBfAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA1AF8ATgBpAHQAcgBvAGcAZQBuAEkAbgB0AGEAawBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8AXwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANgBfAFMAdABhAGcAZQAyAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8AXwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANgBfAFMAdABhAGcAZQAyAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8AXwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANgBfAFMAdABhAGcAZQAyAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8AXwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANgBfAFMAdABhAGcAZQAyAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBVAG4AaQB0ACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAF8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADYAXwBTAHQAYQBnAGUAMgBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8AXwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANgBfAFMAdABhAGcAZQAyAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBfAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA2AF8AUwB0AGEAZwBlADIATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8AXwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANgBfAFMAdABhAGcAZQAyAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBfAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA3AF8ATgBpAHQAcgBvAGcAZQBuAFQAcgBhAG4AcwBmAGUAcgByAGUAZABUAG8AUwB0AGEAZwBlADIAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8AXwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANwBfAE4AaQB0AHIAbwBnAGUAbgBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAVABvAFMAdABhAGcAZQAyAF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAF8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADcAXwBOAGkAdAByAG8AZwBlAG4AVAByAGEAbgBzAGYAZQByAHIAZQBkAFQAbwBTAHQAYQBnAGUAMgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBfAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA3AF8ATgBpAHQAcgBvAGcAZQBuAFQAcgBhAG4AcwBmAGUAcgByAGUAZABUAG8AUwB0AGEAZwBlADIAXwBVAG4AaQB0ACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAF8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADcAXwBOAGkAdAByAG8AZwBlAG4AVAByAGEAbgBzAGYAZQByAHIAZQBkAFQAbwBTAHQAYQBnAGUAMgBfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAF8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADcAXwBOAGkAdAByAG8AZwBlAG4AVAByAGEAbgBzAGYAZQByAHIAZQBkAFQAbwBTAHQAYQBnAGUAMgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAF8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADcAXwBOAGkAdAByAG8AZwBlAG4AVAByAGEAbgBzAGYAZQByAHIAZQBkAFQAbwBTAHQAYQBnAGUAMgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8AXwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANwBfAE4AaQB0AHIAbwBnAGUAbgBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAVABvAFMAdABhAGcAZQAyAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8AXwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AOABfAFMAdABhAGcAZQAzAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8AXwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AOABfAFMAdABhAGcAZQAzAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8AXwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AOABfAFMAdABhAGcAZQAzAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8AXwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AOABfAFMAdABhAGcAZQAzAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBVAG4AaQB0ACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAF8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADgAXwBTAHQAYQBnAGUAMwBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8AXwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AOABfAFMAdABhAGcAZQAzAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBfAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA4AF8AUwB0AGEAZwBlADMATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8AXwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AOABfAFMAdABhAGcAZQAzAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGEAbgB1AHIAZQBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AYQBuAHUAcgBlAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMQBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADEAXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBhAG4AdQByAGUAQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA5AF8AXwAxAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGEAbgB1AHIAZQBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxAF8AVQBuAGkAdAAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGEAbgB1AHIAZQBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBhAG4AdQByAGUAQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA5AF8AXwAxAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AYQBuAHUAcgBlAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMQBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADEAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AYQBuAHUAcgBlAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMQBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADEAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGEAbgB1AHIAZQBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAzACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AYQBuAHUAcgBlAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADMAXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBhAG4AdQByAGUAQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA5AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGEAbgB1AHIAZQBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAzAF8AVQBuAGkAdAAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGEAbgB1AHIAZQBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBhAG4AdQByAGUAQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA5AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AYQBuAHUAcgBlAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AYQBuAHUAcgBlAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADMAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4AcwAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4AcwBfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADUAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAyAF8AVgBvAGwAYQB0AGkAbABpAHMAZQBkAE4AaQB0AHIAbwBnAGUAbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADUAXwBfADIAXwBWAG8AbABhAHQAaQBsAGkAcwBlAGQATgBpAHQAcgBvAGcAZQBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAFQAaQB0AGwAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMgBfAFYAbwBsAGEAdABpAGwAaQBzAGUAZABOAGkAdAByAG8AZwBlAG4ARgByAG8AbQBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8AVgBhAHIAaQBhAGIAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAyAF8AVgBvAGwAYQB0AGkAbABpAHMAZQBkAE4AaQB0AHIAbwBnAGUAbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBVAG4AaQB0ACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAyAF8AVgBvAGwAYQB0AGkAbABpAHMAZQBkAE4AaQB0AHIAbwBnAGUAbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBTAG8AdQByAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMgBfAFYAbwBsAGEAdABpAGwAaQBzAGUAZABOAGkAdAByAG8AZwBlAG4ARgByAG8AbQBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADUAXwBfADIAXwBWAG8AbABhAHQAaQBsAGkAcwBlAGQATgBpAHQAcgBvAGcAZQBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADUAXwBfADIAXwBWAG8AbABhAHQAaQBsAGkAcwBlAGQATgBpAHQAcgBvAGcAZQBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAEEAcgBnAHUAbQBlAG4AdABzACIAXQAsACIAbABvAGMAYQBsAGUAIgA6AHsAIgBsAGkAcwB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAcgBvAHcAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBjAG8AbAB1AG0AbgBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUABvAHMAaQB0AGkAbwBuAHMAIgA6AFsAMwBdACwAIgBkAGUAYwBpAG0AYQBsAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiAC4AIgAsACIAZABhAHQAZQBPAHIAZABlAHIAIgA6ACIARABNAFkAIgAsACIAYwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsACIAOgAiACQAIgAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbABMAGUAYQBkACIAOgB0AHIAdQBlACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAZQBwAEIAeQBTAHAAYQBjAGUAIgA6AGYAYQBsAHMAZQAsACIAcgBvAHcATABlAHQAdABlAHIAIgA6ACIAUgAiACwAIgBjAG8AbAB1AG0AbgBMAGUAdAB0AGUAcgAiADoAIgBDACIALAAiAHIAYwBMAGUAZgB0AEIAcgBhAGMAawBlAHQAIgA6ACIAWwAiACwAIgByAGMAUgBpAGcAaAB0AEIAcgBhAGMAawBlAHQAIgA6ACIAXQAiACwAIgBzAHQAYQB0AGUAbQBlAG4AdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGwAbwBjAGEAbABlAE4AYQBtAGUAIgA6ACIAZQBuAC0AdQBzACIAfQB9AA==</AFEJSONBlob>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{809E3D44-A88D-4EBF-A307-6B8CE77A3361}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -27521,7 +27490,23 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -27530,12 +27515,4 @@
     <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>